--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED10D6E-D4E4-4D1C-9B10-31E8495922AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5C5CF5-3BDB-4B96-8660-375FD34ED2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$118</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="186">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -461,9 +461,6 @@
     <t>Colombres Sur</t>
   </si>
   <si>
-    <t>Punitorios mal cobrados</t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
@@ -495,75 +492,24 @@
     <t>Servicio de fumigacion - Ortega Daniel - Mes de Octubre - Se adeudaba</t>
   </si>
   <si>
-    <t>Ticket - Pago en efectivo</t>
-  </si>
-  <si>
-    <t>Transf 16/01</t>
-  </si>
-  <si>
-    <t>Ferreteria Beta - Buje reduccion</t>
-  </si>
-  <si>
-    <t>Sanitarios Viamonte - Boya de tergopol y flotante presion 32BCE</t>
-  </si>
-  <si>
-    <t>Transf 09/1</t>
-  </si>
-  <si>
-    <t>Transf 08/01</t>
-  </si>
-  <si>
-    <t>Debito 08/01</t>
-  </si>
-  <si>
     <t>Loschi Bruno - Mantenimiento bimestral</t>
   </si>
   <si>
-    <t>Transf 15/01</t>
-  </si>
-  <si>
-    <t>Debito 13/01</t>
-  </si>
-  <si>
-    <t>Electricidad Alsina SA - Timer 24V - Arreglo extractor (terraza)</t>
-  </si>
-  <si>
-    <t>Transf 26/01</t>
-  </si>
-  <si>
     <t>Transf 25/01</t>
   </si>
   <si>
-    <t>Cuello natalia (Destapacion) - Tramo interno 13B</t>
-  </si>
-  <si>
     <t>Transf 30/01</t>
   </si>
   <si>
-    <t>Debito 04/01</t>
-  </si>
-  <si>
     <t>Mes de descanso</t>
   </si>
   <si>
     <t>PABLO GARCIA - MATIAS EZEQUIEL GARCIA</t>
   </si>
   <si>
-    <t>Lireria - Sobres para entrega de expensas</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de contactora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transf 30/01 </t>
-  </si>
-  <si>
     <t>Deposito sin identificar del - 15/01</t>
   </si>
   <si>
-    <t>QUEDO PENDIENTE PARA FEBR3R0 PASAR UN EDESUR DE EN3RO</t>
-  </si>
-  <si>
     <t>Los depositos sin identificar del 15/01 son de sergio</t>
   </si>
   <si>
@@ -579,9 +525,6 @@
     <t>Frank Matias Wallace - Mantenimiento ascensor FEBRERO</t>
   </si>
   <si>
-    <t>Alterini Guido - Mantenimiento de FEBRERO - Maceton y tierra fertil 25dm</t>
-  </si>
-  <si>
     <t>Articulos de limpieza -  Mes de FEBRERO</t>
   </si>
   <si>
@@ -594,9 +537,6 @@
     <t xml:space="preserve">Papelera Corpa </t>
   </si>
   <si>
-    <t>Cerrajeria Ayram - 1 Micro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mozart SRL - Recarga de matafuegos </t>
   </si>
   <si>
@@ -604,6 +544,51 @@
   </si>
   <si>
     <t>Transf 11/02</t>
+  </si>
+  <si>
+    <t>Transf 04/02</t>
+  </si>
+  <si>
+    <t>Debito 04/02</t>
+  </si>
+  <si>
+    <t>Debito 12/02</t>
+  </si>
+  <si>
+    <t>Cerrajeria Ayram - 1 Microllavero - Sr. Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transf 10/02 </t>
+  </si>
+  <si>
+    <t>Vacaciones abonadas - Trabajadas</t>
+  </si>
+  <si>
+    <t>Transf 20/02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelanto vacaciones </t>
+  </si>
+  <si>
+    <t>Transf 18/02</t>
+  </si>
+  <si>
+    <t>Transf 23/02</t>
+  </si>
+  <si>
+    <t>Escribania Romanatti - Digitalizacion para presentar en ARCA</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferreteria Beta - Compra de acoples </t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes anterior</t>
+  </si>
+  <si>
+    <t>Punitorios mal cobrados 4A</t>
   </si>
 </sst>
 </file>
@@ -617,7 +602,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,6 +790,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1249,7 +1241,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1438,7 +1430,6 @@
     <xf numFmtId="44" fontId="20" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="12" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1453,52 +1444,64 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="13" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="13" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="13" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="14" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="14" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1514,46 +1517,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1568,54 +1571,26 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1970,20 +1945,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L122"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1991,7 +1966,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1999,84 +1974,84 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="192" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="159" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="192"/>
+      <c r="B4" s="159"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="192"/>
-      <c r="B5" s="192"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="159"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="192"/>
-      <c r="B6" s="192"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="159"/>
+      <c r="B6" s="159"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="192"/>
-      <c r="B7" s="192"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="159"/>
+      <c r="B7" s="159"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="191" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="191"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="191"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="193" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="156" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="156"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="156"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="160" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="193"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="193"/>
-      <c r="B17" s="193"/>
-      <c r="C17" s="193"/>
-      <c r="D17" s="193"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="160"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="160"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="160"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="160"/>
+      <c r="B16" s="160"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="160"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="160"/>
+      <c r="B17" s="160"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2084,7 +2059,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2092,887 +2067,884 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="137">
-        <v>1774070.07</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C23" s="137"/>
       <c r="D23" s="80"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="137">
-        <f>-732912.7</f>
-        <v>-732912.7</v>
-      </c>
+      <c r="C24" s="137"/>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="137">
-        <v>0.63</v>
-      </c>
+      <c r="C25" s="137"/>
       <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>178</v>
+      </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="137"/>
+      <c r="C26" s="137">
+        <v>422400</v>
+      </c>
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="106">
         <f>SUM(C23:C26)</f>
-        <v>1041158.0000000001</v>
-      </c>
-      <c r="D27" s="81"/>
-      <c r="F27" s="189" t="s">
-        <v>145</v>
-      </c>
-      <c r="G27" s="190"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="137">
-        <v>1301013.8899999999</v>
-      </c>
-      <c r="D28" s="113"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>422400</v>
+      </c>
+      <c r="D27" s="47"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="80"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="137">
-        <v>-282970.53000000003</v>
-      </c>
-      <c r="D29" s="113"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C29" s="137"/>
+      <c r="D29" s="80"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="137">
-        <v>0.64</v>
-      </c>
-      <c r="D30" s="113"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C30" s="137"/>
+      <c r="D30" s="80"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="113"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C31" s="137"/>
+      <c r="D31" s="80"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="112"/>
-      <c r="C32" s="48">
+      <c r="B32" s="47"/>
+      <c r="C32" s="106">
         <f>SUM(C28:C31)</f>
-        <v>1018043.9999999999</v>
+        <v>0</v>
       </c>
       <c r="D32" s="81"/>
-    </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="82">
-        <f>C27+C32</f>
-        <v>2059202</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="26" t="s">
+      <c r="F32" s="154" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="155"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="137"/>
+      <c r="D33" s="113"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="113"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="113"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="192">
+        <v>633951.69999999995</v>
+      </c>
+      <c r="D36" s="113"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="112"/>
+      <c r="C37" s="48">
+        <f>SUM(C33:C36)</f>
+        <v>633951.69999999995</v>
+      </c>
+      <c r="D37" s="81"/>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="82">
+        <f>C32+C37+C27</f>
+        <v>1056351.7</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="83"/>
-      <c r="F34" s="14"/>
-    </row>
-    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="56" t="s">
+      <c r="B39" s="26"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="83"/>
+      <c r="F39" s="14"/>
+    </row>
+    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="215">
+      <c r="B40" s="5"/>
+      <c r="C40" s="153">
         <v>135000</v>
       </c>
-      <c r="D35" s="124" t="s">
-        <v>190</v>
-      </c>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="115" t="s">
+      <c r="D40" s="124" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="115" t="s">
         <v>131</v>
       </c>
-      <c r="B36" s="107" t="s">
+      <c r="B41" s="107" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="153">
+        <v>211800</v>
+      </c>
+      <c r="D41" s="124" t="s">
+        <v>155</v>
+      </c>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="82">
+        <f>SUM(C40:C41)</f>
+        <v>346800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="25"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="57"/>
+    </row>
+    <row r="44" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="157" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="158"/>
+      <c r="C44" s="138" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="123"/>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="157" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="158"/>
+      <c r="C45" s="204">
+        <v>4203</v>
+      </c>
+      <c r="D45" s="123"/>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="25"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="84">
+        <f>SUM(C44:C45)</f>
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="144"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="85"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="80" t="s">
+        <v>132</v>
+      </c>
+      <c r="B48" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="151">
+        <v>1421002.83</v>
+      </c>
+      <c r="D48" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="116"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="152">
+        <v>16423.96</v>
+      </c>
+      <c r="D49" s="123" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" s="152">
+        <v>147815.6</v>
+      </c>
+      <c r="D50" s="123" t="str">
+        <f>D49</f>
+        <v>Debito 12/02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="152">
+        <v>399207.23</v>
+      </c>
+      <c r="D51" s="121" t="str">
+        <f>D50</f>
+        <v>Debito 12/02</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" s="144"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="84">
+        <f>SUM(C48:C51)</f>
+        <v>1984449.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="144"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="85"/>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="80"/>
+      <c r="C54" s="152">
+        <v>554680.11</v>
+      </c>
+      <c r="D54" s="120" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="80"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="120"/>
+    </row>
+    <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="80"/>
+      <c r="C56" s="152">
+        <v>20460.259999999998</v>
+      </c>
+      <c r="D56" s="120" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="80"/>
+      <c r="C57" s="152">
+        <v>864000.26</v>
+      </c>
+      <c r="D57" s="120" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="166" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" s="167"/>
+      <c r="C58" s="152">
+        <v>204149</v>
+      </c>
+      <c r="D58" s="120" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="164" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="165"/>
+      <c r="C59" s="145">
+        <v>0</v>
+      </c>
+      <c r="D59" s="122"/>
+    </row>
+    <row r="60" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="157" t="s">
+        <v>152</v>
+      </c>
+      <c r="B60" s="158"/>
+      <c r="C60" s="152">
+        <v>35200</v>
+      </c>
+      <c r="D60" s="122" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="137">
-        <v>211800</v>
-      </c>
-      <c r="D36" s="124" t="s">
+    </row>
+    <row r="61" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="25"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="84">
+        <f>SUM(C54:C60)</f>
+        <v>1678489.63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="25"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="87"/>
+    </row>
+    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="147" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="146"/>
+      <c r="C63" s="152">
+        <v>51919.14</v>
+      </c>
+      <c r="D63" s="118" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="157" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="18" t="s">
+      <c r="B64" s="158"/>
+      <c r="C64" s="152">
+        <v>753830.53</v>
+      </c>
+      <c r="D64" s="120" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="191" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" s="143"/>
+      <c r="C65" s="152">
+        <v>10000</v>
+      </c>
+      <c r="D65" s="142" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="191" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" s="143"/>
+      <c r="C66" s="152">
+        <v>8760.52</v>
+      </c>
+      <c r="D66" s="122" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="157" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="158"/>
+      <c r="C67" s="152">
+        <v>34000</v>
+      </c>
+      <c r="D67" s="122" t="s">
+        <v>182</v>
+      </c>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+    </row>
+    <row r="68" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B68" s="165"/>
+      <c r="C68" s="139">
+        <v>0</v>
+      </c>
+      <c r="D68" s="122"/>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="90">
+        <f>SUM(C63:C68)</f>
+        <v>858510.19000000006</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" s="148"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="87"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="80"/>
+      <c r="C71" s="152">
+        <v>65343</v>
+      </c>
+      <c r="D71" s="91"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="80"/>
+      <c r="C72" s="152">
+        <v>149249.14000000001</v>
+      </c>
+      <c r="D72" s="89"/>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="82">
-        <f>SUM(C35:C36)</f>
-        <v>346800</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="57"/>
-    </row>
-    <row r="39" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="185" t="s">
-        <v>127</v>
-      </c>
-      <c r="B39" s="186"/>
-      <c r="C39" s="139" t="s">
-        <v>170</v>
-      </c>
-      <c r="D39" s="123"/>
-    </row>
-    <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="185" t="s">
-        <v>128</v>
-      </c>
-      <c r="B40" s="186"/>
-      <c r="C40" s="145">
-        <v>4203</v>
-      </c>
-      <c r="D40" s="123" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="25"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="84">
-        <f>SUM(C39:C40)</f>
-        <v>4203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" s="146"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="85"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="80" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="C43" s="212">
-        <v>1421002.83</v>
-      </c>
-      <c r="D43" s="123" t="s">
-        <v>160</v>
-      </c>
-      <c r="F43" s="116"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="C44" s="213">
-        <v>16423.96</v>
-      </c>
-      <c r="D44" s="123" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B45" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" s="213">
-        <v>147815.6</v>
-      </c>
-      <c r="D45" s="123" t="str">
-        <f>D44</f>
-        <v>Debito 13/01</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="C46" s="213">
-        <v>399207.23</v>
-      </c>
-      <c r="D46" s="121" t="str">
-        <f>D45</f>
-        <v>Debito 13/01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="146"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="84">
-        <f>SUM(C43:C46)</f>
-        <v>1984449.62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="146"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="85"/>
-    </row>
-    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="95" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" s="80"/>
-      <c r="C49" s="213">
-        <v>554680.11</v>
-      </c>
-      <c r="D49" s="120" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="80" t="s">
-        <v>125</v>
-      </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="213">
-        <v>20460.259999999998</v>
-      </c>
-      <c r="D50" s="120" t="s">
-        <v>159</v>
-      </c>
-      <c r="F50" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="80" t="s">
-        <v>138</v>
-      </c>
-      <c r="B51" s="80"/>
-      <c r="C51" s="213">
-        <v>864000.26</v>
-      </c>
-      <c r="D51" s="120" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="187" t="s">
-        <v>181</v>
-      </c>
-      <c r="B52" s="188"/>
-      <c r="C52" s="147">
-        <v>204149</v>
-      </c>
-      <c r="D52" s="120" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="183" t="s">
-        <v>161</v>
-      </c>
-      <c r="B53" s="184"/>
-      <c r="C53" s="147">
-        <v>100000</v>
-      </c>
-      <c r="D53" s="122" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="185" t="s">
-        <v>153</v>
-      </c>
-      <c r="B54" s="186"/>
-      <c r="C54" s="147">
-        <v>35200</v>
-      </c>
-      <c r="D54" s="122" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="84">
-        <f>SUM(C49:C54)</f>
-        <v>1778489.63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="25"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="87"/>
-    </row>
-    <row r="57" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="148" t="s">
-        <v>156</v>
-      </c>
-      <c r="B57" s="149"/>
-      <c r="C57" s="147">
-        <v>11850</v>
-      </c>
-      <c r="D57" s="118" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="148" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" s="149"/>
-      <c r="C58" s="147">
-        <v>5400</v>
-      </c>
-      <c r="D58" s="118" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="150" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" s="151"/>
-      <c r="C59" s="147">
-        <v>184942.62</v>
-      </c>
-      <c r="D59" s="118" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="185" t="s">
-        <v>182</v>
-      </c>
-      <c r="B60" s="186"/>
-      <c r="C60" s="147">
-        <v>250000</v>
-      </c>
-      <c r="D60" s="118" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="150" t="s">
-        <v>164</v>
-      </c>
-      <c r="B61" s="149"/>
-      <c r="C61" s="147">
-        <v>96111.67</v>
-      </c>
-      <c r="D61" s="118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="185" t="s">
-        <v>188</v>
-      </c>
-      <c r="B62" s="186"/>
-      <c r="C62" s="213">
-        <v>753830.53</v>
-      </c>
-      <c r="D62" s="120" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="214" t="s">
-        <v>187</v>
-      </c>
-      <c r="B63" s="144"/>
-      <c r="C63" s="213">
-        <v>10000</v>
-      </c>
-      <c r="D63" s="143" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="185" t="s">
-        <v>173</v>
-      </c>
-      <c r="B64" s="186"/>
-      <c r="C64" s="147">
-        <v>180000</v>
-      </c>
-      <c r="D64" s="143" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="185" t="s">
-        <v>186</v>
-      </c>
-      <c r="B65" s="186"/>
-      <c r="C65" s="213">
-        <v>34000</v>
-      </c>
-      <c r="D65" s="122" t="s">
-        <v>155</v>
-      </c>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39"/>
-    </row>
-    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="183" t="s">
-        <v>183</v>
-      </c>
-      <c r="B66" s="184"/>
-      <c r="C66" s="140">
-        <v>0</v>
-      </c>
-      <c r="D66" s="122"/>
-    </row>
-    <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="90">
-        <f>SUM(C57:C66)</f>
-        <v>1526134.82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B68" s="152"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="87"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="80" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="80"/>
-      <c r="C69" s="147">
-        <v>65343</v>
-      </c>
-      <c r="D69" s="91"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="147">
-        <f>1270.8+130081.56+168.5+1080+1392+150+600+950+1062</f>
-        <v>136754.85999999999</v>
-      </c>
-      <c r="D70" s="89"/>
-    </row>
-    <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B71" s="44"/>
-      <c r="C71" s="92"/>
-      <c r="D71" s="84">
-        <f>SUM(C69:C70)</f>
-        <v>202097.86</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="80"/>
-      <c r="D72" s="93"/>
-    </row>
-    <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="180" t="s">
-        <v>144</v>
-      </c>
-      <c r="B73" s="181"/>
-      <c r="C73" s="182"/>
-      <c r="D73" s="94">
+      <c r="B73" s="44"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="84">
+        <f>SUM(C71:C72)</f>
+        <v>214592.14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="93"/>
+    </row>
+    <row r="75" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="161" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="162"/>
+      <c r="C75" s="163"/>
+      <c r="D75" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1"/>
-      <c r="C74" s="95"/>
-      <c r="D74" s="96"/>
-      <c r="E74" s="39"/>
-    </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1"/>
+      <c r="C76" s="95"/>
+      <c r="D76" s="96"/>
+      <c r="E76" s="39"/>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="97"/>
-      <c r="D75" s="98">
-        <f>(SUM(D28:D73))</f>
-        <v>9197947.0800000019</v>
-      </c>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C76" s="95"/>
-      <c r="D76" s="95"/>
-      <c r="F76" s="117"/>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="95"/>
-      <c r="D77" s="95"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="11" t="s">
+      <c r="B77" s="10"/>
+      <c r="C77" s="97"/>
+      <c r="D77" s="98">
+        <f>(SUM(D33:D75))</f>
+        <v>7439966.4300000006</v>
+      </c>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C78" s="95"/>
+      <c r="D78" s="95"/>
+      <c r="F78" s="117"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C79" s="95"/>
+      <c r="D79" s="95"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B78" s="12"/>
-      <c r="C78" s="99"/>
-      <c r="D78" s="100"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="178"/>
-      <c r="B79" s="179"/>
-      <c r="C79" s="88"/>
-      <c r="D79" s="86"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="178"/>
-      <c r="B80" s="179"/>
-      <c r="C80" s="88"/>
-      <c r="D80" s="86"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="103"/>
-      <c r="B81" s="104"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="99"/>
+      <c r="D80" s="100"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="171"/>
+      <c r="B81" s="172"/>
       <c r="C81" s="88"/>
       <c r="D81" s="86"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="42"/>
-      <c r="B82" s="41"/>
-      <c r="C82" s="49"/>
-      <c r="D82" s="49">
-        <f>SUM(C79:C81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="20" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="171"/>
+      <c r="B82" s="172"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="86"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="103"/>
+      <c r="B83" s="104"/>
+      <c r="C83" s="88"/>
+      <c r="D83" s="86"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="42"/>
+      <c r="B84" s="41"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49">
+        <f>SUM(C81:C83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B85" s="20"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="125">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
+      <c r="B87" s="20"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="125"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="10"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="58">
-        <f>D82+D85</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="78" t="s">
+      <c r="B89" s="10"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="58">
+        <f>D84+D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="B89" s="79">
-        <f>D75</f>
-        <v>9197947.0800000019</v>
-      </c>
-      <c r="C89" s="39"/>
-    </row>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="78" t="s">
+      <c r="B91" s="79">
+        <f>D77</f>
+        <v>7439966.4300000006</v>
+      </c>
+      <c r="C91" s="39"/>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B90" s="79">
-        <f>D75-D73</f>
-        <v>7901376.9300000016</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="78" t="s">
+      <c r="B92" s="79">
+        <f>D77-D75</f>
+        <v>6143396.2800000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B91" s="79">
-        <f>D87-D85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="78" t="s">
+      <c r="B93" s="79">
+        <f>D89-D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="79">
-        <f>D87</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="177" t="s">
+      <c r="B94" s="79">
+        <f>D89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="170" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" s="170"/>
+      <c r="C97" s="170"/>
+      <c r="D97" s="170"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="170"/>
+      <c r="B98" s="170"/>
+      <c r="C98" s="170"/>
+      <c r="D98" s="170"/>
+    </row>
+    <row r="99" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="170"/>
+      <c r="B99" s="170"/>
+      <c r="C99" s="170"/>
+      <c r="D99" s="170"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B101" s="35"/>
+    </row>
+    <row r="102" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" s="105">
+        <v>5322816.5199999996</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B103" s="36">
+        <f>PRORRATEO!H34</f>
+        <v>11998798.140000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B104" s="89">
+        <f>B117</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B105" s="119">
+        <v>-10167</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="B95" s="177"/>
-      <c r="C95" s="177"/>
-      <c r="D95" s="177"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="177"/>
-      <c r="B96" s="177"/>
-      <c r="C96" s="177"/>
-      <c r="D96" s="177"/>
-    </row>
-    <row r="97" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="177"/>
-      <c r="B97" s="177"/>
-      <c r="C97" s="177"/>
-      <c r="D97" s="177"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B99" s="35"/>
-    </row>
-    <row r="100" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B100" s="105">
-        <v>5322816.5199999996</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B101" s="36">
-        <f>PRORRATEO!H34</f>
-        <v>10051349.09</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B102" s="89">
-        <f>B114</f>
+      <c r="B106" s="119">
+        <v>-240000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B107" s="119">
+        <v>-260000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B108" s="119">
+        <f>-B92</f>
+        <v>-6143396.2800000003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109" s="89">
+        <f>-(B93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" s="105">
+        <f>SUM(B102:B109)</f>
+        <v>11168051.379999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="37"/>
+      <c r="C111" s="39"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" s="169" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" s="169"/>
+    </row>
+    <row r="114" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="169"/>
+      <c r="B114" s="169"/>
+    </row>
+    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="101" t="s">
+        <v>158</v>
+      </c>
+      <c r="B115" s="29">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="101" t="s">
+        <v>158</v>
+      </c>
+      <c r="B116" s="29">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="102">
+        <f>SUM(B115:B116)</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B103" s="119"/>
-    </row>
-    <row r="104" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B104" s="119">
-        <v>-31400</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B105" s="119">
-        <f>-B90</f>
-        <v>-7901376.9300000016</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B106" s="89">
-        <f>-(B91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B107" s="105">
-        <f>SUM(B100:B106)</f>
-        <v>7941388.6799999978</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="37"/>
-      <c r="C108" s="39"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="B110" s="176"/>
-    </row>
-    <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="176"/>
-      <c r="B111" s="176"/>
-    </row>
-    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="101" t="s">
-        <v>175</v>
-      </c>
-      <c r="B112" s="29">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="101" t="s">
-        <v>175</v>
-      </c>
-      <c r="B113" s="29">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B114" s="102">
-        <f>SUM(B112:B113)</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L115" s="8"/>
-    </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="175"/>
-      <c r="B116" s="175"/>
-      <c r="C116" s="175"/>
-      <c r="D116" s="175"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="175"/>
-      <c r="B117" s="175"/>
-      <c r="C117" s="175"/>
-      <c r="D117" s="175"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="175"/>
-      <c r="B118" s="175"/>
-      <c r="C118" s="175"/>
-      <c r="D118" s="175"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="175"/>
-      <c r="B119" s="175"/>
-      <c r="C119" s="175"/>
-      <c r="D119" s="175"/>
+    <row r="118" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L118" s="8"/>
+    </row>
+    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="168"/>
+      <c r="B119" s="168"/>
+      <c r="C119" s="168"/>
+      <c r="D119" s="168"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="168"/>
+      <c r="B120" s="168"/>
+      <c r="C120" s="168"/>
+      <c r="D120" s="168"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="168"/>
+      <c r="B121" s="168"/>
+      <c r="C121" s="168"/>
+      <c r="D121" s="168"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="168"/>
+      <c r="B122" s="168"/>
+      <c r="C122" s="168"/>
+      <c r="D122" s="168"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="F27:G27"/>
+  <mergeCells count="18">
+    <mergeCell ref="A119:D122"/>
+    <mergeCell ref="A113:B114"/>
+    <mergeCell ref="A97:D99"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A116:D119"/>
-    <mergeCell ref="A110:B111"/>
-    <mergeCell ref="A95:D97"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2983,167 +2955,167 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="200" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
+      <c r="B1" s="173" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="141">
+      <c r="O2" s="140">
         <v>10000000</v>
       </c>
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="201"/>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="201"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="201"/>
-      <c r="I3" s="201"/>
-      <c r="J3" s="201"/>
-      <c r="K3" s="201"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="142">
+      <c r="O3" s="141">
         <v>1000000</v>
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="194" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="196" t="s">
+      <c r="B4" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="C4" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="198" t="s">
+      <c r="D4" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="198" t="s">
+      <c r="E4" s="177" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="198" t="s">
+      <c r="F4" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="198" t="s">
+      <c r="G4" s="177" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="198" t="s">
+      <c r="H4" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="198" t="s">
+      <c r="I4" s="177" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="205" t="s">
+      <c r="K4" s="179" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="179" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="205" t="s">
+      <c r="M4" s="179" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="210" t="s">
+      <c r="N4" s="185" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="202" t="s">
+      <c r="P4" s="175" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="195"/>
-      <c r="B5" s="197"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="199"/>
-      <c r="E5" s="204"/>
-      <c r="F5" s="199"/>
-      <c r="G5" s="199"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="204"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="206"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="206"/>
-      <c r="N5" s="211"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="188"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="183"/>
+      <c r="K5" s="180"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="186"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="203"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="176"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3161,11 +3133,11 @@
         <v>4.57</v>
       </c>
       <c r="G6" s="60">
-        <v>507700.01</v>
-      </c>
-      <c r="H6" s="61">
+        <v>502700.01</v>
+      </c>
+      <c r="H6" s="193">
         <f>G6</f>
-        <v>507700.01</v>
+        <v>502700.01</v>
       </c>
       <c r="I6" s="62"/>
       <c r="J6" s="63">
@@ -3199,55 +3171,55 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="164">
+      <c r="B7" s="196">
         <v>2</v>
       </c>
-      <c r="C7" s="164" t="s">
+      <c r="C7" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="164" t="s">
+      <c r="D7" s="196" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="165"/>
-      <c r="F7" s="166">
+      <c r="E7" s="203"/>
+      <c r="F7" s="197">
         <v>3.07</v>
       </c>
-      <c r="G7" s="167">
-        <v>909166.02</v>
-      </c>
-      <c r="H7" s="167">
-        <f>177000+307000+160000+226497.02+38669</f>
-        <v>909166.02</v>
-      </c>
-      <c r="I7" s="168"/>
-      <c r="J7" s="169">
+      <c r="G7" s="61">
+        <v>347831.02</v>
+      </c>
+      <c r="H7" s="193">
+        <f>G7</f>
+        <v>347831.02</v>
+      </c>
+      <c r="I7" s="62"/>
+      <c r="J7" s="198">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="169">
+      <c r="K7" s="198">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="170">
+      <c r="L7" s="199">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
         <v>30699.999999999996</v>
       </c>
-      <c r="M7" s="170">
+      <c r="M7" s="199">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="171">
-        <v>0</v>
-      </c>
-      <c r="O7" s="172">
+      <c r="N7" s="200">
+        <v>0</v>
+      </c>
+      <c r="O7" s="201">
         <f t="shared" si="0"/>
         <v>337700.02</v>
       </c>
-      <c r="P7" s="173">
+      <c r="P7" s="202">
         <f t="shared" si="1"/>
         <v>347831.02</v>
       </c>
@@ -3256,10 +3228,10 @@
         <v>0.02</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3270,24 +3242,27 @@
         <v>53</v>
       </c>
       <c r="D8" s="127" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" s="128"/>
       <c r="F8" s="129">
         <v>4.55</v>
       </c>
       <c r="G8" s="130">
-        <v>500500.03</v>
-      </c>
-      <c r="H8" s="130"/>
+        <v>1015765.03</v>
+      </c>
+      <c r="H8" s="194">
+        <f>400000+500500</f>
+        <v>900500</v>
+      </c>
       <c r="I8" s="131"/>
       <c r="J8" s="132">
         <f t="shared" si="2"/>
-        <v>500500.03</v>
+        <v>115265.03000000003</v>
       </c>
       <c r="K8" s="132">
         <f t="shared" si="3"/>
-        <v>14764.750885000001</v>
+        <v>3400.3183850000009</v>
       </c>
       <c r="L8" s="133">
         <f t="shared" si="4"/>
@@ -3302,18 +3277,18 @@
       </c>
       <c r="O8" s="135">
         <f t="shared" si="0"/>
-        <v>1015765.03</v>
+        <v>619165.03</v>
       </c>
       <c r="P8" s="136">
         <f t="shared" si="1"/>
-        <v>1046238.03</v>
+        <v>637740.03</v>
       </c>
       <c r="Q8" s="39">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3331,15 +3306,15 @@
         <v>3.05</v>
       </c>
       <c r="G9" s="60">
-        <v>304495.03999999998</v>
-      </c>
-      <c r="H9" s="61">
-        <v>325500.03999999998</v>
+        <v>323930.03999999998</v>
+      </c>
+      <c r="H9" s="193">
+        <v>350000</v>
       </c>
       <c r="I9" s="62"/>
       <c r="J9" s="63">
         <f t="shared" si="2"/>
-        <v>-21005</v>
+        <v>-26069.960000000021</v>
       </c>
       <c r="K9" s="63">
         <f t="shared" si="3"/>
@@ -3358,11 +3333,11 @@
       </c>
       <c r="O9" s="66">
         <f t="shared" si="0"/>
-        <v>314495.03999999998</v>
+        <v>309430.03999999998</v>
       </c>
       <c r="P9" s="67">
         <f t="shared" si="1"/>
-        <v>323930.03999999998</v>
+        <v>318713.03999999998</v>
       </c>
       <c r="Q9" s="39">
         <f t="shared" si="6"/>
@@ -3373,7 +3348,7 @@
       </c>
       <c r="S9" s="39"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3391,20 +3366,17 @@
         <v>4.55</v>
       </c>
       <c r="G10" s="60">
-        <v>509693.05</v>
-      </c>
-      <c r="H10" s="61">
-        <f>400000+95000</f>
-        <v>495000</v>
-      </c>
+        <v>515626.05</v>
+      </c>
+      <c r="H10" s="61"/>
       <c r="I10" s="62"/>
       <c r="J10" s="63">
         <f t="shared" si="2"/>
-        <v>14693.049999999988</v>
+        <v>515626.05</v>
       </c>
       <c r="K10" s="63">
         <f t="shared" si="3"/>
-        <v>433.44497499999966</v>
+        <v>15210.968475000001</v>
       </c>
       <c r="L10" s="64">
         <f t="shared" si="4"/>
@@ -3419,11 +3391,11 @@
       </c>
       <c r="O10" s="66">
         <f t="shared" si="0"/>
-        <v>515626.05</v>
+        <v>1031337.05</v>
       </c>
       <c r="P10" s="67">
         <f t="shared" si="1"/>
-        <v>531095.05000000005</v>
+        <v>1062277.05</v>
       </c>
       <c r="Q10" s="39">
         <f t="shared" si="6"/>
@@ -3431,7 +3403,7 @@
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3449,11 +3421,11 @@
         <v>3.05</v>
       </c>
       <c r="G11" s="60">
-        <v>326350.06</v>
-      </c>
-      <c r="H11" s="61">
+        <v>335500.06</v>
+      </c>
+      <c r="H11" s="193">
         <f>G11</f>
-        <v>326350.06</v>
+        <v>335500.06</v>
       </c>
       <c r="I11" s="62"/>
       <c r="J11" s="63">
@@ -3488,54 +3460,57 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="154">
+      <c r="B12" s="196">
         <v>7</v>
       </c>
-      <c r="C12" s="154" t="s">
+      <c r="C12" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="154" t="s">
+      <c r="D12" s="196" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="154"/>
-      <c r="F12" s="155">
+      <c r="E12" s="196"/>
+      <c r="F12" s="197">
         <v>4.55</v>
       </c>
-      <c r="G12" s="156">
-        <v>496500.07</v>
-      </c>
-      <c r="H12" s="156"/>
-      <c r="I12" s="157"/>
-      <c r="J12" s="158">
+      <c r="G12" s="61">
+        <v>1011647.07</v>
+      </c>
+      <c r="H12" s="193">
+        <f>240000+260000+501000+10647</f>
+        <v>1011647</v>
+      </c>
+      <c r="I12" s="62"/>
+      <c r="J12" s="198">
         <f t="shared" si="2"/>
-        <v>496500.07</v>
-      </c>
-      <c r="K12" s="158">
+        <v>6.9999999948777258E-2</v>
+      </c>
+      <c r="K12" s="198">
         <f t="shared" si="3"/>
-        <v>14646.752065000001</v>
-      </c>
-      <c r="L12" s="159">
+        <v>2.0649999984889292E-3</v>
+      </c>
+      <c r="L12" s="199">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M12" s="159">
+      <c r="M12" s="199">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="160">
-        <v>0</v>
-      </c>
-      <c r="O12" s="161">
+      <c r="N12" s="200">
+        <v>0</v>
+      </c>
+      <c r="O12" s="201">
         <f t="shared" si="0"/>
-        <v>1011647.07</v>
-      </c>
-      <c r="P12" s="162">
+        <v>500500.07</v>
+      </c>
+      <c r="P12" s="202">
         <f t="shared" si="1"/>
-        <v>1041996.07</v>
+        <v>515515.07</v>
       </c>
       <c r="Q12" s="39">
         <f t="shared" si="6"/>
@@ -3544,7 +3519,7 @@
       <c r="R12" s="117"/>
       <c r="S12" s="116"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3562,15 +3537,15 @@
         <v>3.05</v>
       </c>
       <c r="G13" s="60">
-        <v>326592.08</v>
-      </c>
-      <c r="H13" s="61">
-        <v>336390.08</v>
+        <v>325702.08</v>
+      </c>
+      <c r="H13" s="193">
+        <v>335473</v>
       </c>
       <c r="I13" s="62"/>
       <c r="J13" s="63">
         <f t="shared" si="2"/>
-        <v>-9798</v>
+        <v>-9770.9199999999837</v>
       </c>
       <c r="K13" s="63">
         <f t="shared" si="3"/>
@@ -3589,18 +3564,18 @@
       </c>
       <c r="O13" s="66">
         <f t="shared" si="0"/>
-        <v>325702.08</v>
+        <v>325729.08</v>
       </c>
       <c r="P13" s="67">
         <f t="shared" si="1"/>
-        <v>335473.08</v>
+        <v>335501.08</v>
       </c>
       <c r="Q13" s="39">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3618,15 +3593,15 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="G14" s="60">
-        <v>487200.09</v>
-      </c>
-      <c r="H14" s="153">
-        <v>490000</v>
+        <v>498800.09</v>
+      </c>
+      <c r="H14" s="195">
+        <v>514000</v>
       </c>
       <c r="I14" s="62"/>
       <c r="J14" s="63">
         <f t="shared" si="2"/>
-        <v>-2799.9099999999744</v>
+        <v>-15199.909999999974</v>
       </c>
       <c r="K14" s="63">
         <f t="shared" si="3"/>
@@ -3645,21 +3620,21 @@
       </c>
       <c r="O14" s="66">
         <f t="shared" si="0"/>
-        <v>498800.09</v>
+        <v>486400.09</v>
       </c>
       <c r="P14" s="67">
         <f t="shared" si="1"/>
-        <v>513764.09</v>
+        <v>500992.09</v>
       </c>
       <c r="Q14" s="39">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="R14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3679,7 +3654,7 @@
       <c r="G15" s="60">
         <v>335500.09999999998</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="193">
         <f>G15</f>
         <v>335500.09999999998</v>
       </c>
@@ -3716,10 +3691,10 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3737,15 +3712,16 @@
         <v>4.55</v>
       </c>
       <c r="G16" s="60">
-        <v>500500.11</v>
-      </c>
-      <c r="H16" s="61">
-        <v>515515.11</v>
+        <v>485485.11</v>
+      </c>
+      <c r="H16" s="193">
+        <f>G16</f>
+        <v>485485.11</v>
       </c>
       <c r="I16" s="62"/>
       <c r="J16" s="63">
         <f t="shared" si="2"/>
-        <v>-15015</v>
+        <v>0</v>
       </c>
       <c r="K16" s="63">
         <f t="shared" si="3"/>
@@ -3764,18 +3740,18 @@
       </c>
       <c r="O16" s="66">
         <f t="shared" si="0"/>
-        <v>485485.11</v>
+        <v>500500.11</v>
       </c>
       <c r="P16" s="67">
         <f t="shared" si="1"/>
-        <v>500050.11</v>
+        <v>515515.11</v>
       </c>
       <c r="Q16" s="39">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3793,19 +3769,20 @@
         <v>3.05</v>
       </c>
       <c r="G17" s="60">
-        <v>719605.12</v>
-      </c>
-      <c r="H17" s="61">
+        <v>762336.12</v>
+      </c>
+      <c r="H17" s="193">
+        <f>300000+5000</f>
         <v>305000</v>
       </c>
       <c r="I17" s="62"/>
       <c r="J17" s="63">
         <f t="shared" si="2"/>
-        <v>414605.12</v>
+        <v>457336.12</v>
       </c>
       <c r="K17" s="63">
         <f t="shared" si="3"/>
-        <v>12230.851040000001</v>
+        <v>13491.41554</v>
       </c>
       <c r="L17" s="64">
         <f t="shared" si="4"/>
@@ -3820,18 +3797,18 @@
       </c>
       <c r="O17" s="66">
         <f t="shared" si="0"/>
-        <v>762336.12</v>
+        <v>806328.12</v>
       </c>
       <c r="P17" s="67">
         <f t="shared" si="1"/>
-        <v>785206.12</v>
+        <v>830518.12</v>
       </c>
       <c r="Q17" s="39">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3849,11 +3826,11 @@
         <v>4.55</v>
       </c>
       <c r="G18" s="60">
-        <v>487210.13</v>
-      </c>
-      <c r="H18" s="61">
+        <v>500500.13</v>
+      </c>
+      <c r="H18" s="193">
         <f>G18</f>
-        <v>487210.13</v>
+        <v>500500.13</v>
       </c>
       <c r="I18" s="62"/>
       <c r="J18" s="63">
@@ -3888,7 +3865,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3908,7 +3885,7 @@
       <c r="G19" s="60">
         <v>349800.14</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="193">
         <f>G19</f>
         <v>349800.14</v>
       </c>
@@ -3945,7 +3922,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3965,7 +3942,7 @@
       <c r="G20" s="60">
         <v>500500.15</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="193">
         <f>G20</f>
         <v>500500.15</v>
       </c>
@@ -4002,7 +3979,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -4020,15 +3997,15 @@
         <v>3.17</v>
       </c>
       <c r="G21" s="60">
-        <v>339454.16</v>
-      </c>
-      <c r="H21" s="61">
-        <v>340000</v>
+        <v>348154.16</v>
+      </c>
+      <c r="H21" s="193">
+        <v>350000</v>
       </c>
       <c r="I21" s="62"/>
       <c r="J21" s="63">
         <f t="shared" si="2"/>
-        <v>-545.84000000002561</v>
+        <v>-1845.8400000000256</v>
       </c>
       <c r="K21" s="63">
         <f t="shared" si="3"/>
@@ -4047,22 +4024,22 @@
       </c>
       <c r="O21" s="66">
         <f t="shared" si="0"/>
-        <v>348154.16</v>
+        <v>346854.16</v>
       </c>
       <c r="P21" s="67">
         <f t="shared" si="1"/>
-        <v>358599.16</v>
+        <v>357260.16</v>
       </c>
       <c r="Q21" s="39">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="R21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S21" s="38"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4080,17 +4057,20 @@
         <v>4.55</v>
       </c>
       <c r="G22" s="61">
-        <v>500500.17</v>
-      </c>
-      <c r="H22" s="61"/>
+        <v>1015765.17</v>
+      </c>
+      <c r="H22" s="193">
+        <f>1046238.17</f>
+        <v>1046238.17</v>
+      </c>
       <c r="I22" s="62"/>
       <c r="J22" s="63">
         <f t="shared" si="2"/>
-        <v>500500.17</v>
+        <v>-30473</v>
       </c>
       <c r="K22" s="63">
         <f t="shared" si="3"/>
-        <v>14764.755015000001</v>
+        <v>0</v>
       </c>
       <c r="L22" s="64">
         <f t="shared" si="4"/>
@@ -4105,18 +4085,18 @@
       </c>
       <c r="O22" s="66">
         <f t="shared" si="0"/>
-        <v>1015765.17</v>
+        <v>470027.17</v>
       </c>
       <c r="P22" s="67">
         <f t="shared" si="1"/>
-        <v>1046238.17</v>
+        <v>484128.17</v>
       </c>
       <c r="Q22" s="39">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4136,7 +4116,7 @@
       <c r="G23" s="60">
         <v>348700.18</v>
       </c>
-      <c r="H23" s="61">
+      <c r="H23" s="193">
         <f>G23</f>
         <v>348700.18</v>
       </c>
@@ -4173,7 +4153,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4191,11 +4171,11 @@
         <v>4.55</v>
       </c>
       <c r="G24" s="60">
-        <v>515515.19</v>
-      </c>
-      <c r="H24" s="61">
+        <v>500500.19</v>
+      </c>
+      <c r="H24" s="193">
         <f>G24</f>
-        <v>515515.19</v>
+        <v>500500.19</v>
       </c>
       <c r="I24" s="62"/>
       <c r="J24" s="63">
@@ -4230,7 +4210,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4250,7 +4230,7 @@
       <c r="G25" s="61">
         <v>348700.2</v>
       </c>
-      <c r="H25" s="61">
+      <c r="H25" s="193">
         <f>G25</f>
         <v>348700.2</v>
       </c>
@@ -4290,7 +4270,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4310,7 +4290,7 @@
       <c r="G26" s="60">
         <v>500500.21</v>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="193">
         <f>G26</f>
         <v>500500.21</v>
       </c>
@@ -4347,7 +4327,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4365,16 +4345,16 @@
         <v>3.17</v>
       </c>
       <c r="G27" s="60">
-        <v>-135619.78</v>
-      </c>
-      <c r="H27" s="61">
+        <v>-168789.78</v>
+      </c>
+      <c r="H27" s="193">
         <f>381870.22</f>
         <v>381870.22</v>
       </c>
       <c r="I27" s="62"/>
       <c r="J27" s="63">
         <f t="shared" si="2"/>
-        <v>-517490</v>
+        <v>-550660</v>
       </c>
       <c r="K27" s="63">
         <f t="shared" si="3"/>
@@ -4393,18 +4373,18 @@
       </c>
       <c r="O27" s="66">
         <f t="shared" si="0"/>
-        <v>-168789.78</v>
+        <v>-201959.78</v>
       </c>
       <c r="P27" s="67">
         <f t="shared" si="1"/>
-        <v>-173853.78</v>
+        <v>-208018.78</v>
       </c>
       <c r="Q27" s="39">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4422,11 +4402,11 @@
         <v>4.66</v>
       </c>
       <c r="G28" s="60">
-        <v>498620.23</v>
-      </c>
-      <c r="H28" s="61">
+        <v>512600.23</v>
+      </c>
+      <c r="H28" s="193">
         <f>G28</f>
-        <v>498620.23</v>
+        <v>512600.23</v>
       </c>
       <c r="I28" s="62"/>
       <c r="J28" s="63">
@@ -4461,7 +4441,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4481,7 +4461,7 @@
       <c r="G29" s="60">
         <v>353100.24</v>
       </c>
-      <c r="H29" s="61">
+      <c r="H29" s="193">
         <f>G29</f>
         <v>353100.24</v>
       </c>
@@ -4518,7 +4498,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4536,15 +4516,16 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="G30" s="60">
-        <v>515900.25</v>
-      </c>
-      <c r="H30" s="61">
-        <v>531377.25</v>
+        <v>500423.25</v>
+      </c>
+      <c r="H30" s="193">
+        <f>G30</f>
+        <v>500423.25</v>
       </c>
       <c r="I30" s="62"/>
       <c r="J30" s="63">
         <f t="shared" si="2"/>
-        <v>-15477</v>
+        <v>0</v>
       </c>
       <c r="K30" s="63">
         <f t="shared" si="3"/>
@@ -4563,11 +4544,11 @@
       </c>
       <c r="O30" s="66">
         <f t="shared" si="0"/>
-        <v>500423.25</v>
+        <v>515900.25</v>
       </c>
       <c r="P30" s="67">
         <f t="shared" si="1"/>
-        <v>515436.25</v>
+        <v>531377.25</v>
       </c>
       <c r="Q30" s="39">
         <f t="shared" si="6"/>
@@ -4577,7 +4558,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4595,11 +4576,11 @@
         <v>3.02</v>
       </c>
       <c r="G31" s="60">
-        <v>332200.26</v>
-      </c>
-      <c r="H31" s="61">
+        <v>363600.26</v>
+      </c>
+      <c r="H31" s="193">
         <f>G31</f>
-        <v>332200.26</v>
+        <v>363600.26</v>
       </c>
       <c r="I31" s="62"/>
       <c r="J31" s="63">
@@ -4638,7 +4619,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4656,16 +4637,15 @@
         <v>0.16</v>
       </c>
       <c r="G32" s="60">
-        <v>17133.27</v>
-      </c>
-      <c r="H32" s="61">
-        <f>G32</f>
-        <v>17133.27</v>
+        <v>17600.27</v>
+      </c>
+      <c r="H32" s="193">
+        <v>18128.27</v>
       </c>
       <c r="I32" s="62"/>
       <c r="J32" s="63">
         <f>G32-H32</f>
-        <v>0</v>
+        <v>-528</v>
       </c>
       <c r="K32" s="63">
         <f t="shared" si="3"/>
@@ -4684,18 +4664,18 @@
       </c>
       <c r="O32" s="66">
         <f t="shared" si="0"/>
-        <v>17600.27</v>
+        <v>17072.27</v>
       </c>
       <c r="P32" s="67">
         <f t="shared" si="1"/>
-        <v>18128.27</v>
+        <v>17584.27</v>
       </c>
       <c r="Q32" s="39">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4741,7 +4721,7 @@
       </c>
       <c r="Q33" s="39"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="73"/>
       <c r="C34" s="74"/>
       <c r="D34" s="75"/>
@@ -4752,11 +4732,11 @@
       </c>
       <c r="G34" s="45">
         <f>SUM(G6:G33)</f>
-        <v>11396016.780000001</v>
+        <v>12452477.779999999</v>
       </c>
       <c r="H34" s="52">
         <f>SUM(H6:H33)</f>
-        <v>10051349.09</v>
+        <v>11998798.140000001</v>
       </c>
       <c r="I34" s="52">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4778,106 +4758,111 @@
       </c>
       <c r="O34" s="77">
         <f>SUM(O6:O32)</f>
-        <v>12432911.779999999</v>
+        <v>11517185.780000001</v>
       </c>
       <c r="P34" s="77">
         <f>SUM(P6:P32)</f>
-        <v>12805899.780000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11862701.780000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="175" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="175"/>
-      <c r="F37" s="175"/>
-      <c r="G37" s="175"/>
-      <c r="H37" s="175"/>
-      <c r="I37" s="175"/>
-      <c r="J37" s="175"/>
-      <c r="K37" s="175"/>
-      <c r="L37" s="175"/>
-      <c r="M37" s="175"/>
-      <c r="N37" s="175"/>
-      <c r="O37" s="175"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="175"/>
-      <c r="E38" s="175"/>
-      <c r="F38" s="175"/>
-      <c r="G38" s="175"/>
-      <c r="H38" s="175"/>
-      <c r="I38" s="175"/>
-      <c r="J38" s="175"/>
-      <c r="K38" s="175"/>
-      <c r="L38" s="175"/>
-      <c r="M38" s="175"/>
-      <c r="N38" s="175"/>
-      <c r="O38" s="175"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="175"/>
-      <c r="E39" s="175"/>
-      <c r="F39" s="175"/>
-      <c r="G39" s="175"/>
-      <c r="H39" s="175"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="175"/>
-      <c r="L39" s="175"/>
-      <c r="M39" s="175"/>
-      <c r="N39" s="175"/>
-      <c r="O39" s="175"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="175"/>
-      <c r="E40" s="175"/>
-      <c r="F40" s="175"/>
-      <c r="G40" s="175"/>
-      <c r="H40" s="175"/>
-      <c r="I40" s="175"/>
-      <c r="J40" s="175"/>
-      <c r="K40" s="175"/>
-      <c r="L40" s="175"/>
-      <c r="M40" s="175"/>
-      <c r="N40" s="175"/>
-      <c r="O40" s="175"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="175"/>
-      <c r="E41" s="175"/>
-      <c r="F41" s="175"/>
-      <c r="G41" s="175"/>
-      <c r="H41" s="175"/>
-      <c r="I41" s="175"/>
-      <c r="J41" s="175"/>
-      <c r="K41" s="175"/>
-      <c r="L41" s="175"/>
-      <c r="M41" s="175"/>
-      <c r="N41" s="175"/>
-      <c r="O41" s="175"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="175"/>
-      <c r="E42" s="175"/>
-      <c r="F42" s="175"/>
-      <c r="G42" s="175"/>
-      <c r="H42" s="175"/>
-      <c r="I42" s="175"/>
-      <c r="J42" s="175"/>
-      <c r="K42" s="175"/>
-      <c r="L42" s="175"/>
-      <c r="M42" s="175"/>
-      <c r="N42" s="175"/>
-      <c r="O42" s="175"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="168" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" s="168"/>
+      <c r="F37" s="168"/>
+      <c r="G37" s="168"/>
+      <c r="H37" s="168"/>
+      <c r="I37" s="168"/>
+      <c r="J37" s="168"/>
+      <c r="K37" s="168"/>
+      <c r="L37" s="168"/>
+      <c r="M37" s="168"/>
+      <c r="N37" s="168"/>
+      <c r="O37" s="168"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="168"/>
+      <c r="E38" s="168"/>
+      <c r="F38" s="168"/>
+      <c r="G38" s="168"/>
+      <c r="H38" s="168"/>
+      <c r="I38" s="168"/>
+      <c r="J38" s="168"/>
+      <c r="K38" s="168"/>
+      <c r="L38" s="168"/>
+      <c r="M38" s="168"/>
+      <c r="N38" s="168"/>
+      <c r="O38" s="168"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="168"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="168"/>
+      <c r="G39" s="168"/>
+      <c r="H39" s="168"/>
+      <c r="I39" s="168"/>
+      <c r="J39" s="168"/>
+      <c r="K39" s="168"/>
+      <c r="L39" s="168"/>
+      <c r="M39" s="168"/>
+      <c r="N39" s="168"/>
+      <c r="O39" s="168"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="168"/>
+      <c r="E40" s="168"/>
+      <c r="F40" s="168"/>
+      <c r="G40" s="168"/>
+      <c r="H40" s="168"/>
+      <c r="I40" s="168"/>
+      <c r="J40" s="168"/>
+      <c r="K40" s="168"/>
+      <c r="L40" s="168"/>
+      <c r="M40" s="168"/>
+      <c r="N40" s="168"/>
+      <c r="O40" s="168"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="168"/>
+      <c r="E41" s="168"/>
+      <c r="F41" s="168"/>
+      <c r="G41" s="168"/>
+      <c r="H41" s="168"/>
+      <c r="I41" s="168"/>
+      <c r="J41" s="168"/>
+      <c r="K41" s="168"/>
+      <c r="L41" s="168"/>
+      <c r="M41" s="168"/>
+      <c r="N41" s="168"/>
+      <c r="O41" s="168"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="168"/>
+      <c r="E42" s="168"/>
+      <c r="F42" s="168"/>
+      <c r="G42" s="168"/>
+      <c r="H42" s="168"/>
+      <c r="I42" s="168"/>
+      <c r="J42" s="168"/>
+      <c r="K42" s="168"/>
+      <c r="L42" s="168"/>
+      <c r="M42" s="168"/>
+      <c r="N42" s="168"/>
+      <c r="O42" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4890,11 +4875,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4904,16 +4884,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C3:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="163" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="174" t="s">
-        <v>178</v>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="149" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="150" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\COLOMBRES\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5C5CF5-3BDB-4B96-8660-375FD34ED2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AEEF9C-2713-40AD-91EE-CA53622B2CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$118</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$133</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="190">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -589,6 +589,18 @@
   </si>
   <si>
     <t>Punitorios mal cobrados 4A</t>
+  </si>
+  <si>
+    <t>Mes de FEBRERO</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>Guenaga Gonzalo Federico</t>
+  </si>
+  <si>
+    <t>Agregar cuota alimentaria</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1253,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1460,117 +1472,6 @@
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1591,6 +1492,118 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1945,20 +1958,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L122"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L137"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1966,7 +1979,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1974,7 +1987,7 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="109" t="s">
         <v>151</v>
       </c>
@@ -1982,76 +1995,76 @@
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="159" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="185" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="159"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="159"/>
-      <c r="B5" s="159"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="185"/>
+      <c r="B5" s="185"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="159"/>
-      <c r="B6" s="159"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="185"/>
+      <c r="B6" s="185"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="159"/>
-      <c r="B7" s="159"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="185"/>
+      <c r="B7" s="185"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="156" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="184" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="156"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="156"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="160" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="184"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="184"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="186" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="160"/>
-      <c r="D14" s="160"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="160"/>
-      <c r="B15" s="160"/>
-      <c r="C15" s="160"/>
-      <c r="D15" s="160"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="160"/>
-      <c r="B16" s="160"/>
-      <c r="C16" s="160"/>
-      <c r="D16" s="160"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="160"/>
-      <c r="B17" s="160"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="186"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="186"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="186"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="186"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="186"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="186"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="186"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="186"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2059,7 +2072,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2067,884 +2080,1041 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="137"/>
+      <c r="C23" s="137">
+        <v>1497939.7</v>
+      </c>
       <c r="D23" s="80"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G23" s="205">
+        <v>293034.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="137"/>
+      <c r="C24" s="137">
+        <v>-618836.34</v>
+      </c>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="137"/>
+      <c r="C25" s="137">
+        <v>0.64</v>
+      </c>
       <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="137">
+      <c r="C26" s="153">
         <v>422400</v>
       </c>
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="106">
         <f>SUM(C23:C26)</f>
-        <v>422400</v>
+        <v>1301504</v>
       </c>
       <c r="D27" s="47"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="137"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="137">
+        <v>1232039.3</v>
+      </c>
       <c r="D28" s="80"/>
       <c r="G28" s="14"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="137"/>
+      <c r="C29" s="137">
+        <v>-267968.53999999998</v>
+      </c>
       <c r="D29" s="80"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="137"/>
+      <c r="C30" s="137">
+        <v>0.24</v>
+      </c>
       <c r="D30" s="80"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="137"/>
+      <c r="C31" s="155">
+        <v>633951.69999999995</v>
+      </c>
       <c r="D31" s="80"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="106">
         <f>SUM(C28:C31)</f>
-        <v>0</v>
+        <v>1598022.7</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="154" t="s">
+      <c r="F32" s="182" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="155"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G32" s="183"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C33" s="137"/>
+      <c r="C33" s="137">
+        <v>554812.06999999995</v>
+      </c>
       <c r="D33" s="113"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="137"/>
+      <c r="C34" s="137">
+        <v>-120671.62</v>
+      </c>
       <c r="D34" s="113"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="137"/>
+      <c r="C35" s="137">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="D35" s="113"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>176</v>
-      </c>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="192">
-        <v>633951.69999999995</v>
-      </c>
+      <c r="C36" s="155"/>
       <c r="D36" s="113"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B37" s="112"/>
       <c r="C37" s="48">
         <f>SUM(C33:C36)</f>
-        <v>633951.69999999995</v>
+        <v>434140.99999999994</v>
       </c>
       <c r="D37" s="81"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="82">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="137"/>
+      <c r="D38" s="80"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="80"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="80"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="80"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="47"/>
+      <c r="C42" s="106">
+        <f>SUM(C38:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="47"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="137"/>
+      <c r="D43" s="113"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="113"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="113"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="155"/>
+      <c r="D46" s="113"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="112"/>
+      <c r="C47" s="48">
+        <f>SUM(C43:C46)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="81"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="137"/>
+      <c r="D48" s="113"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="137"/>
+      <c r="D49" s="113"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="113"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="155"/>
+      <c r="D51" s="113"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="112"/>
+      <c r="C52" s="48">
+        <f>SUM(C48:C51)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="81"/>
+    </row>
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="82">
         <f>C32+C37+C27</f>
-        <v>1056351.7</v>
-      </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+        <v>3333667.7</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="83"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="56" t="s">
+      <c r="B54" s="26"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="83"/>
+      <c r="F54" s="14"/>
+    </row>
+    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="153">
+      <c r="B55" s="5"/>
+      <c r="C55" s="153">
         <v>135000</v>
       </c>
-      <c r="D40" s="124" t="s">
+      <c r="D55" s="124" t="s">
         <v>170</v>
       </c>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="115" t="s">
+      <c r="G55" s="14"/>
+    </row>
+    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="115" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="107" t="s">
+      <c r="B56" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="C41" s="153">
+      <c r="C56" s="153">
         <v>211800</v>
       </c>
-      <c r="D41" s="124" t="s">
+      <c r="D56" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
+      <c r="G56" s="14"/>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="82">
-        <f>SUM(C40:C41)</f>
+      <c r="B57" s="18"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="82">
+        <f>SUM(C55:C56)</f>
         <v>346800</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="24" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="57"/>
-    </row>
-    <row r="44" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="157" t="s">
+      <c r="B58" s="25"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="57"/>
+    </row>
+    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="178" t="s">
         <v>127</v>
       </c>
-      <c r="B44" s="158"/>
-      <c r="C44" s="138" t="s">
+      <c r="B59" s="179"/>
+      <c r="C59" s="138" t="s">
         <v>156</v>
       </c>
-      <c r="D44" s="123"/>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="157" t="s">
+      <c r="D59" s="123"/>
+    </row>
+    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="178" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="158"/>
-      <c r="C45" s="204">
+      <c r="B60" s="179"/>
+      <c r="C60" s="167">
         <v>4203</v>
       </c>
-      <c r="D45" s="123"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="25" t="s">
+      <c r="D60" s="123"/>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="25" t="s">
         <v>1</v>
-      </c>
-      <c r="B46" s="25"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="84">
-        <f>SUM(C44:C45)</f>
-        <v>4203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="144"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="85"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="80" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="151">
-        <v>1421002.83</v>
-      </c>
-      <c r="D48" s="120" t="s">
-        <v>172</v>
-      </c>
-      <c r="F48" s="116"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B49" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="C49" s="152">
-        <v>16423.96</v>
-      </c>
-      <c r="D49" s="123" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="80" t="s">
-        <v>134</v>
-      </c>
-      <c r="B50" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="C50" s="152">
-        <v>147815.6</v>
-      </c>
-      <c r="D50" s="123" t="str">
-        <f>D49</f>
-        <v>Debito 12/02</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="80" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="152">
-        <v>399207.23</v>
-      </c>
-      <c r="D51" s="121" t="str">
-        <f>D50</f>
-        <v>Debito 12/02</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="144"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="84">
-        <f>SUM(C48:C51)</f>
-        <v>1984449.62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="144"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="85"/>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B54" s="80"/>
-      <c r="C54" s="152">
-        <v>554680.11</v>
-      </c>
-      <c r="D54" s="120" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B55" s="80"/>
-      <c r="C55" s="152"/>
-      <c r="D55" s="120"/>
-    </row>
-    <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="80" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="152">
-        <v>20460.259999999998</v>
-      </c>
-      <c r="D56" s="120" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="80" t="s">
-        <v>138</v>
-      </c>
-      <c r="B57" s="80"/>
-      <c r="C57" s="152">
-        <v>864000.26</v>
-      </c>
-      <c r="D57" s="120" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="166" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" s="167"/>
-      <c r="C58" s="152">
-        <v>204149</v>
-      </c>
-      <c r="D58" s="120" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="164" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" s="165"/>
-      <c r="C59" s="145">
-        <v>0</v>
-      </c>
-      <c r="D59" s="122"/>
-    </row>
-    <row r="60" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
-        <v>152</v>
-      </c>
-      <c r="B60" s="158"/>
-      <c r="C60" s="152">
-        <v>35200</v>
-      </c>
-      <c r="D60" s="122" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="25" t="s">
-        <v>3</v>
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="30"/>
       <c r="D61" s="84">
-        <f>SUM(C54:C60)</f>
-        <v>1678489.63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f>SUM(C59:C60)</f>
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B62" s="25"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="87"/>
-    </row>
-    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="147" t="s">
-        <v>181</v>
-      </c>
-      <c r="B63" s="146"/>
-      <c r="C63" s="152">
-        <v>51919.14</v>
-      </c>
-      <c r="D63" s="118" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="157" t="s">
-        <v>168</v>
-      </c>
-      <c r="B64" s="158"/>
+        <v>35</v>
+      </c>
+      <c r="B62" s="144"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="85"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="80" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" s="151">
+        <v>1421002.83</v>
+      </c>
+      <c r="D63" s="120" t="s">
+        <v>172</v>
+      </c>
+      <c r="F63" s="116"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="80" t="s">
+        <v>166</v>
+      </c>
       <c r="C64" s="152">
-        <v>753830.53</v>
-      </c>
-      <c r="D64" s="120" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="191" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="143"/>
+        <v>16423.96</v>
+      </c>
+      <c r="D64" s="123" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="80" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="80" t="s">
+        <v>166</v>
+      </c>
       <c r="C65" s="152">
-        <v>10000</v>
-      </c>
-      <c r="D65" s="142" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="191" t="s">
-        <v>183</v>
-      </c>
-      <c r="B66" s="143"/>
+        <v>147815.6</v>
+      </c>
+      <c r="D65" s="123" t="str">
+        <f>D64</f>
+        <v>Debito 12/02</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="B66" s="80" t="s">
+        <v>166</v>
+      </c>
       <c r="C66" s="152">
-        <v>8760.52</v>
-      </c>
-      <c r="D66" s="122" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="157" t="s">
-        <v>167</v>
-      </c>
-      <c r="B67" s="158"/>
-      <c r="C67" s="152">
-        <v>34000</v>
-      </c>
-      <c r="D67" s="122" t="s">
-        <v>182</v>
-      </c>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-    </row>
-    <row r="68" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="164" t="s">
-        <v>164</v>
-      </c>
-      <c r="B68" s="165"/>
-      <c r="C68" s="139">
-        <v>0</v>
-      </c>
-      <c r="D68" s="122"/>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="90">
-        <f>SUM(C63:C68)</f>
-        <v>858510.19000000006</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="148"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="87"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>399207.23</v>
+      </c>
+      <c r="D66" s="121" t="str">
+        <f>D65</f>
+        <v>Debito 12/02</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" s="144"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="84">
+        <f>SUM(C63:C66)</f>
+        <v>1984449.62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="144"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="85"/>
+    </row>
+    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="80"/>
+      <c r="C69" s="152">
+        <v>554680.11</v>
+      </c>
+      <c r="D69" s="120" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="80"/>
+      <c r="C70" s="152"/>
+      <c r="D70" s="120"/>
+    </row>
+    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="80" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B71" s="80"/>
       <c r="C71" s="152">
-        <v>65343</v>
-      </c>
-      <c r="D71" s="91"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>20460.259999999998</v>
+      </c>
+      <c r="D71" s="120" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="80" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B72" s="80"/>
       <c r="C72" s="152">
+        <v>864000.26</v>
+      </c>
+      <c r="D72" s="120" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="180" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" s="181"/>
+      <c r="C73" s="152">
+        <v>204149</v>
+      </c>
+      <c r="D73" s="120" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="176" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="177"/>
+      <c r="C74" s="145">
+        <v>0</v>
+      </c>
+      <c r="D74" s="122"/>
+    </row>
+    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="178" t="s">
+        <v>152</v>
+      </c>
+      <c r="B75" s="179"/>
+      <c r="C75" s="152">
+        <v>35200</v>
+      </c>
+      <c r="D75" s="122" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="25"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="84">
+        <f>SUM(C69:C75)</f>
+        <v>1678489.63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" s="25"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="87"/>
+    </row>
+    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="147" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" s="146"/>
+      <c r="C78" s="152">
+        <v>51919.14</v>
+      </c>
+      <c r="D78" s="118" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="178" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" s="179"/>
+      <c r="C79" s="152">
+        <v>753830.53</v>
+      </c>
+      <c r="D79" s="120" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="154" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" s="143"/>
+      <c r="C80" s="152">
+        <v>10000</v>
+      </c>
+      <c r="D80" s="142" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="154" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="143"/>
+      <c r="C81" s="152">
+        <v>8760.52</v>
+      </c>
+      <c r="D81" s="122" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="178" t="s">
+        <v>167</v>
+      </c>
+      <c r="B82" s="179"/>
+      <c r="C82" s="152">
+        <v>34000</v>
+      </c>
+      <c r="D82" s="122" t="s">
+        <v>182</v>
+      </c>
+      <c r="E82" s="39"/>
+      <c r="F82" s="39"/>
+    </row>
+    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="176" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="177"/>
+      <c r="C83" s="139">
+        <v>0</v>
+      </c>
+      <c r="D83" s="122"/>
+    </row>
+    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="90">
+        <f>SUM(C78:C83)</f>
+        <v>858510.19000000006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B85" s="148"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="87"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="B86" s="80"/>
+      <c r="C86" s="152">
+        <v>65343</v>
+      </c>
+      <c r="D86" s="91"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="B87" s="80"/>
+      <c r="C87" s="152">
         <v>149249.14000000001</v>
       </c>
-      <c r="D72" s="89"/>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="44" t="s">
+      <c r="D87" s="89"/>
+    </row>
+    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="92"/>
-      <c r="D73" s="84">
-        <f>SUM(C71:C72)</f>
+      <c r="B88" s="44"/>
+      <c r="C88" s="92"/>
+      <c r="D88" s="84">
+        <f>SUM(C86:C87)</f>
         <v>214592.14</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="93"/>
-    </row>
-    <row r="75" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="161" t="s">
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="80"/>
+      <c r="D89" s="93"/>
+    </row>
+    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="173" t="s">
         <v>143</v>
       </c>
-      <c r="B75" s="162"/>
-      <c r="C75" s="163"/>
-      <c r="D75" s="94">
+      <c r="B90" s="174"/>
+      <c r="C90" s="175"/>
+      <c r="D90" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-      <c r="C76" s="95"/>
-      <c r="D76" s="96"/>
-      <c r="E76" s="39"/>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
+    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="1"/>
+      <c r="C91" s="95"/>
+      <c r="D91" s="96"/>
+      <c r="E91" s="39"/>
+    </row>
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="97"/>
-      <c r="D77" s="98">
-        <f>(SUM(D33:D75))</f>
-        <v>7439966.4300000006</v>
-      </c>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C78" s="95"/>
-      <c r="D78" s="95"/>
-      <c r="F78" s="117"/>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="95"/>
-      <c r="D79" s="95"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="B92" s="10"/>
+      <c r="C92" s="97"/>
+      <c r="D92" s="98">
+        <f>(SUM(D33:D90))</f>
+        <v>9717282.4300000016</v>
+      </c>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C93" s="95"/>
+      <c r="D93" s="95"/>
+      <c r="F93" s="117"/>
+    </row>
+    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C94" s="95"/>
+      <c r="D94" s="95"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="12"/>
-      <c r="C80" s="99"/>
-      <c r="D80" s="100"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="171"/>
-      <c r="B81" s="172"/>
-      <c r="C81" s="88"/>
-      <c r="D81" s="86"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="171"/>
-      <c r="B82" s="172"/>
-      <c r="C82" s="88"/>
-      <c r="D82" s="86"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="103"/>
-      <c r="B83" s="104"/>
-      <c r="C83" s="88"/>
-      <c r="D83" s="86"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="42"/>
-      <c r="B84" s="41"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49">
-        <f>SUM(C81:C83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="20" t="s">
+      <c r="B95" s="12"/>
+      <c r="C95" s="99"/>
+      <c r="D95" s="100"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="171"/>
+      <c r="B96" s="172"/>
+      <c r="C96" s="88"/>
+      <c r="D96" s="86"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="171"/>
+      <c r="B97" s="172"/>
+      <c r="C97" s="88"/>
+      <c r="D97" s="86"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="103"/>
+      <c r="B98" s="104"/>
+      <c r="C98" s="88"/>
+      <c r="D98" s="86"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="42"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="49">
+        <f>SUM(C96:C98)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B87" s="20"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="125"/>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
+      <c r="B102" s="20"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="125"/>
+    </row>
+    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="58">
-        <f>D84+D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="78" t="s">
+      <c r="B104" s="10"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="58">
+        <f>D99+D102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="B91" s="79">
-        <f>D77</f>
-        <v>7439966.4300000006</v>
-      </c>
-      <c r="C91" s="39"/>
-    </row>
-    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="78" t="s">
+      <c r="B106" s="79">
+        <f>D92</f>
+        <v>9717282.4300000016</v>
+      </c>
+      <c r="C106" s="39"/>
+    </row>
+    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B92" s="79">
-        <f>D77-D75</f>
-        <v>6143396.2800000003</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="78" t="s">
+      <c r="B107" s="79">
+        <f>D92-D90</f>
+        <v>8420712.2800000012</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B93" s="79">
-        <f>D89-D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="78" t="s">
+      <c r="B108" s="79">
+        <f>D104-D102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="79">
-        <f>D89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="170" t="s">
+      <c r="B109" s="79">
+        <f>D104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="170" t="s">
         <v>165</v>
       </c>
-      <c r="B97" s="170"/>
-      <c r="C97" s="170"/>
-      <c r="D97" s="170"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="170"/>
-      <c r="B98" s="170"/>
-      <c r="C98" s="170"/>
-      <c r="D98" s="170"/>
-    </row>
-    <row r="99" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="170"/>
-      <c r="B99" s="170"/>
-      <c r="C99" s="170"/>
-      <c r="D99" s="170"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="15" t="s">
+      <c r="B112" s="170"/>
+      <c r="C112" s="170"/>
+      <c r="D112" s="170"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="170"/>
+      <c r="B113" s="170"/>
+      <c r="C113" s="170"/>
+      <c r="D113" s="170"/>
+    </row>
+    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="170"/>
+      <c r="B114" s="170"/>
+      <c r="C114" s="170"/>
+      <c r="D114" s="170"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B101" s="35"/>
-    </row>
-    <row r="102" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="23" t="s">
+      <c r="B116" s="35"/>
+    </row>
+    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B102" s="105">
+      <c r="B117" s="105">
         <v>5322816.5199999996</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B103" s="36">
+      <c r="B118" s="36">
         <f>PRORRATEO!H34</f>
         <v>11998798.140000001</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="89">
-        <f>B117</f>
+      <c r="B119" s="89">
+        <f>B132</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B105" s="119">
+      <c r="B120" s="119">
         <v>-10167</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="B106" s="119">
+      <c r="B121" s="119">
         <v>-240000</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="17" t="s">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="B107" s="119">
+      <c r="B122" s="119">
         <v>-260000</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="34" t="s">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B108" s="119">
-        <f>-B92</f>
-        <v>-6143396.2800000003</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="17" t="s">
+      <c r="B123" s="119">
+        <f>-B107</f>
+        <v>-8420712.2800000012</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B109" s="89">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="22" t="s">
+      <c r="B124" s="89">
+        <f>-(B108)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B110" s="105">
-        <f>SUM(B102:B109)</f>
-        <v>11168051.379999999</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="37"/>
-      <c r="C111" s="39"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="169" t="s">
+      <c r="B125" s="105">
+        <f>SUM(B117:B124)</f>
+        <v>8890735.379999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B126" s="37"/>
+      <c r="C126" s="39"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="169" t="s">
         <v>78</v>
       </c>
-      <c r="B113" s="169"/>
-    </row>
-    <row r="114" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="169"/>
-      <c r="B114" s="169"/>
-    </row>
-    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="101" t="s">
+      <c r="B128" s="169"/>
+    </row>
+    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="169"/>
+      <c r="B129" s="169"/>
+    </row>
+    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="B115" s="29">
+      <c r="B130" s="29">
         <v>240000</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="101" t="s">
+    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="B116" s="29">
+      <c r="B131" s="29">
         <v>260000</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="40" t="s">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B117" s="102">
-        <f>SUM(B115:B116)</f>
+      <c r="B132" s="102">
+        <f>SUM(B130:B131)</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L118" s="8"/>
-    </row>
-    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="168"/>
-      <c r="B119" s="168"/>
-      <c r="C119" s="168"/>
-      <c r="D119" s="168"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="168"/>
-      <c r="B120" s="168"/>
-      <c r="C120" s="168"/>
-      <c r="D120" s="168"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="168"/>
-      <c r="B121" s="168"/>
-      <c r="C121" s="168"/>
-      <c r="D121" s="168"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="168"/>
-      <c r="B122" s="168"/>
-      <c r="C122" s="168"/>
-      <c r="D122" s="168"/>
+    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L133" s="8"/>
+    </row>
+    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="168"/>
+      <c r="B134" s="168"/>
+      <c r="C134" s="168"/>
+      <c r="D134" s="168"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="168"/>
+      <c r="B135" s="168"/>
+      <c r="C135" s="168"/>
+      <c r="D135" s="168"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="168"/>
+      <c r="B136" s="168"/>
+      <c r="C136" s="168"/>
+      <c r="D136" s="168"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" s="168"/>
+      <c r="B137" s="168"/>
+      <c r="C137" s="168"/>
+      <c r="D137" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A119:D122"/>
-    <mergeCell ref="A113:B114"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A134:D137"/>
+    <mergeCell ref="A128:B129"/>
+    <mergeCell ref="A112:D114"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2955,61 +3125,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="173" t="s">
+      <c r="B1" s="193" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3021,18 +3191,18 @@
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="174"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
+      <c r="B3" s="194"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="194"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3043,79 +3213,79 @@
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="187" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="177" t="s">
+      <c r="C4" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="177" t="s">
+      <c r="D4" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="177" t="s">
+      <c r="E4" s="191" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="177" t="s">
+      <c r="F4" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="177" t="s">
+      <c r="G4" s="191" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="177" t="s">
+      <c r="H4" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="177" t="s">
+      <c r="I4" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="182" t="s">
+      <c r="J4" s="200" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="179" t="s">
+      <c r="K4" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="L4" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="179" t="s">
+      <c r="M4" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="185" t="s">
+      <c r="N4" s="203" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="175" t="s">
+      <c r="P4" s="195" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="188"/>
       <c r="B5" s="190"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="181"/>
-      <c r="G5" s="181"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="184"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="186"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="197"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
+      <c r="I5" s="197"/>
+      <c r="J5" s="201"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="202"/>
+      <c r="M5" s="199"/>
+      <c r="N5" s="204"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="176"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="196"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3135,7 +3305,7 @@
       <c r="G6" s="60">
         <v>502700.01</v>
       </c>
-      <c r="H6" s="193">
+      <c r="H6" s="156">
         <f>G6</f>
         <v>502700.01</v>
       </c>
@@ -3171,55 +3341,55 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="196">
+      <c r="B7" s="159">
         <v>2</v>
       </c>
-      <c r="C7" s="196" t="s">
+      <c r="C7" s="159" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="196" t="s">
+      <c r="D7" s="159" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="203"/>
-      <c r="F7" s="197">
+      <c r="E7" s="166"/>
+      <c r="F7" s="160">
         <v>3.07</v>
       </c>
       <c r="G7" s="61">
         <v>347831.02</v>
       </c>
-      <c r="H7" s="193">
+      <c r="H7" s="156">
         <f>G7</f>
         <v>347831.02</v>
       </c>
       <c r="I7" s="62"/>
-      <c r="J7" s="198">
+      <c r="J7" s="161">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="198">
+      <c r="K7" s="161">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="199">
+      <c r="L7" s="162">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
         <v>30699.999999999996</v>
       </c>
-      <c r="M7" s="199">
+      <c r="M7" s="162">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="200">
-        <v>0</v>
-      </c>
-      <c r="O7" s="201">
+      <c r="N7" s="163">
+        <v>0</v>
+      </c>
+      <c r="O7" s="164">
         <f t="shared" si="0"/>
         <v>337700.02</v>
       </c>
-      <c r="P7" s="202">
+      <c r="P7" s="165">
         <f t="shared" si="1"/>
         <v>347831.02</v>
       </c>
@@ -3231,7 +3401,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3251,7 +3421,7 @@
       <c r="G8" s="130">
         <v>1015765.03</v>
       </c>
-      <c r="H8" s="194">
+      <c r="H8" s="157">
         <f>400000+500500</f>
         <v>900500</v>
       </c>
@@ -3288,7 +3458,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3308,7 +3478,7 @@
       <c r="G9" s="60">
         <v>323930.03999999998</v>
       </c>
-      <c r="H9" s="193">
+      <c r="H9" s="156">
         <v>350000</v>
       </c>
       <c r="I9" s="62"/>
@@ -3348,7 +3518,7 @@
       </c>
       <c r="S9" s="39"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3403,7 +3573,7 @@
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3423,7 +3593,7 @@
       <c r="G11" s="60">
         <v>335500.06</v>
       </c>
-      <c r="H11" s="193">
+      <c r="H11" s="156">
         <f>G11</f>
         <v>335500.06</v>
       </c>
@@ -3460,55 +3630,55 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="196">
+      <c r="B12" s="159">
         <v>7</v>
       </c>
-      <c r="C12" s="196" t="s">
+      <c r="C12" s="159" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="159" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="196"/>
-      <c r="F12" s="197">
+      <c r="E12" s="159"/>
+      <c r="F12" s="160">
         <v>4.55</v>
       </c>
       <c r="G12" s="61">
         <v>1011647.07</v>
       </c>
-      <c r="H12" s="193">
+      <c r="H12" s="156">
         <f>240000+260000+501000+10647</f>
         <v>1011647</v>
       </c>
       <c r="I12" s="62"/>
-      <c r="J12" s="198">
+      <c r="J12" s="161">
         <f t="shared" si="2"/>
         <v>6.9999999948777258E-2</v>
       </c>
-      <c r="K12" s="198">
+      <c r="K12" s="161">
         <f t="shared" si="3"/>
         <v>2.0649999984889292E-3</v>
       </c>
-      <c r="L12" s="199">
+      <c r="L12" s="162">
         <f t="shared" si="4"/>
         <v>45500</v>
       </c>
-      <c r="M12" s="199">
+      <c r="M12" s="162">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="200">
-        <v>0</v>
-      </c>
-      <c r="O12" s="201">
+      <c r="N12" s="163">
+        <v>0</v>
+      </c>
+      <c r="O12" s="164">
         <f t="shared" si="0"/>
         <v>500500.07</v>
       </c>
-      <c r="P12" s="202">
+      <c r="P12" s="165">
         <f t="shared" si="1"/>
         <v>515515.07</v>
       </c>
@@ -3519,7 +3689,7 @@
       <c r="R12" s="117"/>
       <c r="S12" s="116"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3539,7 +3709,7 @@
       <c r="G13" s="60">
         <v>325702.08</v>
       </c>
-      <c r="H13" s="193">
+      <c r="H13" s="156">
         <v>335473</v>
       </c>
       <c r="I13" s="62"/>
@@ -3575,7 +3745,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3595,7 +3765,7 @@
       <c r="G14" s="60">
         <v>498800.09</v>
       </c>
-      <c r="H14" s="195">
+      <c r="H14" s="158">
         <v>514000</v>
       </c>
       <c r="I14" s="62"/>
@@ -3634,7 +3804,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3654,7 +3824,7 @@
       <c r="G15" s="60">
         <v>335500.09999999998</v>
       </c>
-      <c r="H15" s="193">
+      <c r="H15" s="156">
         <f>G15</f>
         <v>335500.09999999998</v>
       </c>
@@ -3694,7 +3864,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3714,7 +3884,7 @@
       <c r="G16" s="60">
         <v>485485.11</v>
       </c>
-      <c r="H16" s="193">
+      <c r="H16" s="156">
         <f>G16</f>
         <v>485485.11</v>
       </c>
@@ -3751,7 +3921,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3771,7 +3941,7 @@
       <c r="G17" s="60">
         <v>762336.12</v>
       </c>
-      <c r="H17" s="193">
+      <c r="H17" s="156">
         <f>300000+5000</f>
         <v>305000</v>
       </c>
@@ -3808,7 +3978,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3828,7 +3998,7 @@
       <c r="G18" s="60">
         <v>500500.13</v>
       </c>
-      <c r="H18" s="193">
+      <c r="H18" s="156">
         <f>G18</f>
         <v>500500.13</v>
       </c>
@@ -3865,7 +4035,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3885,7 +4055,7 @@
       <c r="G19" s="60">
         <v>349800.14</v>
       </c>
-      <c r="H19" s="193">
+      <c r="H19" s="156">
         <f>G19</f>
         <v>349800.14</v>
       </c>
@@ -3922,7 +4092,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3942,7 +4112,7 @@
       <c r="G20" s="60">
         <v>500500.15</v>
       </c>
-      <c r="H20" s="193">
+      <c r="H20" s="156">
         <f>G20</f>
         <v>500500.15</v>
       </c>
@@ -3979,7 +4149,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3999,7 +4169,7 @@
       <c r="G21" s="60">
         <v>348154.16</v>
       </c>
-      <c r="H21" s="193">
+      <c r="H21" s="156">
         <v>350000</v>
       </c>
       <c r="I21" s="62"/>
@@ -4039,7 +4209,7 @@
       </c>
       <c r="S21" s="38"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4059,7 +4229,7 @@
       <c r="G22" s="61">
         <v>1015765.17</v>
       </c>
-      <c r="H22" s="193">
+      <c r="H22" s="156">
         <f>1046238.17</f>
         <v>1046238.17</v>
       </c>
@@ -4096,7 +4266,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4116,7 +4286,7 @@
       <c r="G23" s="60">
         <v>348700.18</v>
       </c>
-      <c r="H23" s="193">
+      <c r="H23" s="156">
         <f>G23</f>
         <v>348700.18</v>
       </c>
@@ -4153,7 +4323,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4173,7 +4343,7 @@
       <c r="G24" s="60">
         <v>500500.19</v>
       </c>
-      <c r="H24" s="193">
+      <c r="H24" s="156">
         <f>G24</f>
         <v>500500.19</v>
       </c>
@@ -4210,7 +4380,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4230,7 +4400,7 @@
       <c r="G25" s="61">
         <v>348700.2</v>
       </c>
-      <c r="H25" s="193">
+      <c r="H25" s="156">
         <f>G25</f>
         <v>348700.2</v>
       </c>
@@ -4270,7 +4440,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4290,7 +4460,7 @@
       <c r="G26" s="60">
         <v>500500.21</v>
       </c>
-      <c r="H26" s="193">
+      <c r="H26" s="156">
         <f>G26</f>
         <v>500500.21</v>
       </c>
@@ -4327,7 +4497,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4347,7 +4517,7 @@
       <c r="G27" s="60">
         <v>-168789.78</v>
       </c>
-      <c r="H27" s="193">
+      <c r="H27" s="156">
         <f>381870.22</f>
         <v>381870.22</v>
       </c>
@@ -4384,7 +4554,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4404,7 +4574,7 @@
       <c r="G28" s="60">
         <v>512600.23</v>
       </c>
-      <c r="H28" s="193">
+      <c r="H28" s="156">
         <f>G28</f>
         <v>512600.23</v>
       </c>
@@ -4441,7 +4611,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4461,7 +4631,7 @@
       <c r="G29" s="60">
         <v>353100.24</v>
       </c>
-      <c r="H29" s="193">
+      <c r="H29" s="156">
         <f>G29</f>
         <v>353100.24</v>
       </c>
@@ -4498,7 +4668,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4518,7 +4688,7 @@
       <c r="G30" s="60">
         <v>500423.25</v>
       </c>
-      <c r="H30" s="193">
+      <c r="H30" s="156">
         <f>G30</f>
         <v>500423.25</v>
       </c>
@@ -4558,7 +4728,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4578,7 +4748,7 @@
       <c r="G31" s="60">
         <v>363600.26</v>
       </c>
-      <c r="H31" s="193">
+      <c r="H31" s="156">
         <f>G31</f>
         <v>363600.26</v>
       </c>
@@ -4619,7 +4789,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4639,7 +4809,7 @@
       <c r="G32" s="60">
         <v>17600.27</v>
       </c>
-      <c r="H32" s="193">
+      <c r="H32" s="156">
         <v>18128.27</v>
       </c>
       <c r="I32" s="62"/>
@@ -4675,7 +4845,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4721,7 +4891,7 @@
       </c>
       <c r="Q33" s="39"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="73"/>
       <c r="C34" s="74"/>
       <c r="D34" s="75"/>
@@ -4765,12 +4935,12 @@
         <v>11862701.780000001</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D37" s="168" t="s">
         <v>147</v>
       </c>
@@ -4786,7 +4956,7 @@
       <c r="N37" s="168"/>
       <c r="O37" s="168"/>
     </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D38" s="168"/>
       <c r="E38" s="168"/>
       <c r="F38" s="168"/>
@@ -4800,7 +4970,7 @@
       <c r="N38" s="168"/>
       <c r="O38" s="168"/>
     </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="168"/>
       <c r="E39" s="168"/>
       <c r="F39" s="168"/>
@@ -4814,7 +4984,7 @@
       <c r="N39" s="168"/>
       <c r="O39" s="168"/>
     </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D40" s="168"/>
       <c r="E40" s="168"/>
       <c r="F40" s="168"/>
@@ -4828,7 +4998,7 @@
       <c r="N40" s="168"/>
       <c r="O40" s="168"/>
     </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="168"/>
       <c r="E41" s="168"/>
       <c r="F41" s="168"/>
@@ -4842,7 +5012,7 @@
       <c r="N41" s="168"/>
       <c r="O41" s="168"/>
     </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="168"/>
       <c r="E42" s="168"/>
       <c r="F42" s="168"/>
@@ -4858,11 +5028,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4875,6 +5040,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4884,14 +5054,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C3:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" s="149" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C6" s="150" t="s">
         <v>160</v>
       </c>

--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AEEF9C-2713-40AD-91EE-CA53622B2CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2BC3FE-FA50-4EAE-A8F3-E279A4CB2F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="188">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -464,9 +464,6 @@
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
-    <t>ellos cobran a mes vencido</t>
-  </si>
-  <si>
     <t>MAGRO LAUTARO - MAGRO DANIELA</t>
   </si>
   <si>
@@ -592,9 +589,6 @@
   </si>
   <si>
     <t>Mes de FEBRERO</t>
-  </si>
-  <si>
-    <t>Gonzalo</t>
   </si>
   <si>
     <t>Guenaga Gonzalo Federico</t>
@@ -1492,6 +1486,43 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1507,46 +1538,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1561,49 +1592,12 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1989,75 +1983,75 @@
     </row>
     <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="185" t="s">
+      <c r="A4" s="172" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="185"/>
+      <c r="B4" s="172"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="185"/>
-      <c r="B5" s="185"/>
+      <c r="A5" s="172"/>
+      <c r="B5" s="172"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="185"/>
-      <c r="B6" s="185"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="172"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="185"/>
-      <c r="B7" s="185"/>
+      <c r="A7" s="172"/>
+      <c r="B7" s="172"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="184" t="s">
-        <v>161</v>
+      <c r="B9" s="169" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="184"/>
+      <c r="B10" s="169"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="184"/>
+      <c r="B11" s="169"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="186" t="s">
+      <c r="A14" s="173" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="186"/>
-      <c r="C14" s="186"/>
-      <c r="D14" s="186"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="186"/>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
+      <c r="A15" s="173"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="173"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="186"/>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
+      <c r="A16" s="173"/>
+      <c r="B16" s="173"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="186"/>
-      <c r="B17" s="186"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="186"/>
+      <c r="A17" s="173"/>
+      <c r="B17" s="173"/>
+      <c r="C17" s="173"/>
+      <c r="D17" s="173"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2085,16 +2079,16 @@
         <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="137">
         <v>1497939.7</v>
       </c>
       <c r="D23" s="80"/>
       <c r="E23" t="s">
-        <v>189</v>
-      </c>
-      <c r="G23" s="205">
+        <v>187</v>
+      </c>
+      <c r="G23" s="168">
         <v>293034.45</v>
       </c>
     </row>
@@ -2121,7 +2115,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="153">
@@ -2147,7 +2141,7 @@
         <v>129</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="137">
         <v>1232039.3</v>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="155">
@@ -2198,24 +2192,22 @@
         <v>1598022.7</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="182" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="183"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F32" s="204"/>
+      <c r="G32" s="205"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C33" s="137">
         <v>554812.06999999995</v>
       </c>
       <c r="D33" s="113"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
@@ -2225,7 +2217,7 @@
       </c>
       <c r="D34" s="113"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
@@ -2235,13 +2227,13 @@
       </c>
       <c r="D35" s="113"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="155"/>
       <c r="D36" s="113"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>82</v>
       </c>
@@ -2252,108 +2244,130 @@
       </c>
       <c r="D37" s="81"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C38" s="137"/>
+        <v>185</v>
+      </c>
+      <c r="C38" s="137">
+        <v>1578850.12</v>
+      </c>
       <c r="D38" s="80"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="137"/>
+      <c r="C39" s="137">
+        <v>-810662.45</v>
+      </c>
       <c r="D39" s="80"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="137"/>
+      <c r="C40" s="137">
+        <v>0.33</v>
+      </c>
       <c r="D40" s="80"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="168">
+        <v>256062.56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="137"/>
       <c r="D41" s="80"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B42" s="47"/>
       <c r="C42" s="106">
         <f>SUM(C38:C41)</f>
-        <v>0</v>
+        <v>768188.00000000012</v>
       </c>
       <c r="D42" s="47"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C43" s="137"/>
+        <v>185</v>
+      </c>
+      <c r="C43" s="137">
+        <v>1433185.66</v>
+      </c>
       <c r="D43" s="113"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="137"/>
+      <c r="C44" s="137">
+        <v>-311717.88</v>
+      </c>
       <c r="D44" s="113"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="137"/>
+      <c r="C45" s="137">
+        <v>0.22</v>
+      </c>
       <c r="D45" s="113"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="155"/>
       <c r="D46" s="113"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
         <v>82</v>
       </c>
       <c r="B47" s="112"/>
       <c r="C47" s="48">
         <f>SUM(C43:C46)</f>
-        <v>0</v>
+        <v>1121467.9999999998</v>
       </c>
       <c r="D47" s="81"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" s="137"/>
+        <v>185</v>
+      </c>
+      <c r="C48" s="137">
+        <v>1388921.91</v>
+      </c>
       <c r="D48" s="113"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="137"/>
+      <c r="C49" s="137">
+        <v>-302090.52</v>
+      </c>
       <c r="D49" s="113"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2361,7 +2375,9 @@
         <v>83</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="137"/>
+      <c r="C50" s="137">
+        <v>0.61</v>
+      </c>
       <c r="D50" s="113"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2377,7 +2393,7 @@
       <c r="B52" s="112"/>
       <c r="C52" s="48">
         <f>SUM(C48:C51)</f>
-        <v>0</v>
+        <v>1086832</v>
       </c>
       <c r="D52" s="81"/>
     </row>
@@ -2388,8 +2404,8 @@
       <c r="B53" s="18"/>
       <c r="C53" s="19"/>
       <c r="D53" s="82">
-        <f>C32+C37+C27</f>
-        <v>3333667.7</v>
+        <f>C32+C37+C27+C42+C47+C52</f>
+        <v>6310155.7000000002</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -2412,7 +2428,7 @@
         <v>135000</v>
       </c>
       <c r="D55" s="124" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G55" s="14"/>
     </row>
@@ -2421,13 +2437,13 @@
         <v>131</v>
       </c>
       <c r="B56" s="107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C56" s="153">
         <v>211800</v>
       </c>
       <c r="D56" s="124" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G56" s="14"/>
     </row>
@@ -2451,20 +2467,20 @@
       <c r="D58" s="57"/>
     </row>
     <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="178" t="s">
+      <c r="A59" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="179"/>
+      <c r="B59" s="171"/>
       <c r="C59" s="138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D59" s="123"/>
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="178" t="s">
+      <c r="A60" s="170" t="s">
         <v>128</v>
       </c>
-      <c r="B60" s="179"/>
+      <c r="B60" s="171"/>
       <c r="C60" s="167">
         <v>4203</v>
       </c>
@@ -2494,13 +2510,13 @@
         <v>132</v>
       </c>
       <c r="B63" s="80" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" s="151">
         <v>1421002.83</v>
       </c>
       <c r="D63" s="120" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F63" s="116"/>
     </row>
@@ -2509,13 +2525,13 @@
         <v>133</v>
       </c>
       <c r="B64" s="80" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C64" s="152">
         <v>16423.96</v>
       </c>
       <c r="D64" s="123" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,7 +2539,7 @@
         <v>134</v>
       </c>
       <c r="B65" s="80" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C65" s="152">
         <v>147815.6</v>
@@ -2538,7 +2554,7 @@
         <v>135</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C66" s="152">
         <v>399207.23</v>
@@ -2576,7 +2592,7 @@
         <v>554680.11</v>
       </c>
       <c r="D69" s="120" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2596,7 +2612,7 @@
         <v>20460.259999999998</v>
       </c>
       <c r="D71" s="120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2608,41 +2624,41 @@
         <v>864000.26</v>
       </c>
       <c r="D72" s="120" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="180" t="s">
-        <v>163</v>
-      </c>
-      <c r="B73" s="181"/>
+      <c r="A73" s="179" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="180"/>
       <c r="C73" s="152">
         <v>204149</v>
       </c>
       <c r="D73" s="120" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="176" t="s">
-        <v>153</v>
-      </c>
-      <c r="B74" s="177"/>
+      <c r="A74" s="177" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="178"/>
       <c r="C74" s="145">
         <v>0</v>
       </c>
       <c r="D74" s="122"/>
     </row>
     <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="178" t="s">
-        <v>152</v>
-      </c>
-      <c r="B75" s="179"/>
+      <c r="A75" s="170" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" s="171"/>
       <c r="C75" s="152">
         <v>35200</v>
       </c>
       <c r="D75" s="122" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2666,71 +2682,71 @@
     </row>
     <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="147" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B78" s="146"/>
       <c r="C78" s="152">
         <v>51919.14</v>
       </c>
       <c r="D78" s="118" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="178" t="s">
-        <v>168</v>
-      </c>
-      <c r="B79" s="179"/>
+      <c r="A79" s="170" t="s">
+        <v>167</v>
+      </c>
+      <c r="B79" s="171"/>
       <c r="C79" s="152">
         <v>753830.53</v>
       </c>
       <c r="D79" s="120" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="154" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B80" s="143"/>
       <c r="C80" s="152">
         <v>10000</v>
       </c>
       <c r="D80" s="142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="154" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B81" s="143"/>
       <c r="C81" s="152">
         <v>8760.52</v>
       </c>
       <c r="D81" s="122" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="178" t="s">
-        <v>167</v>
-      </c>
-      <c r="B82" s="179"/>
+      <c r="A82" s="170" t="s">
+        <v>166</v>
+      </c>
+      <c r="B82" s="171"/>
       <c r="C82" s="152">
         <v>34000</v>
       </c>
       <c r="D82" s="122" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E82" s="39"/>
       <c r="F82" s="39"/>
     </row>
     <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="176" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" s="177"/>
+      <c r="A83" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="178"/>
       <c r="C83" s="139">
         <v>0</v>
       </c>
@@ -2793,11 +2809,11 @@
       <c r="D89" s="93"/>
     </row>
     <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="173" t="s">
+      <c r="A90" s="174" t="s">
         <v>143</v>
       </c>
-      <c r="B90" s="174"/>
-      <c r="C90" s="175"/>
+      <c r="B90" s="175"/>
+      <c r="C90" s="176"/>
       <c r="D90" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
@@ -2817,7 +2833,7 @@
       <c r="C92" s="97"/>
       <c r="D92" s="98">
         <f>(SUM(D33:D90))</f>
-        <v>9717282.4300000016</v>
+        <v>12693770.43</v>
       </c>
       <c r="E92" s="39"/>
       <c r="F92" s="39"/>
@@ -2840,14 +2856,14 @@
       <c r="D95" s="100"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="171"/>
-      <c r="B96" s="172"/>
+      <c r="A96" s="184"/>
+      <c r="B96" s="185"/>
       <c r="C96" s="88"/>
       <c r="D96" s="86"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="171"/>
-      <c r="B97" s="172"/>
+      <c r="A97" s="184"/>
+      <c r="B97" s="185"/>
       <c r="C97" s="88"/>
       <c r="D97" s="86"/>
     </row>
@@ -2895,7 +2911,7 @@
       </c>
       <c r="B106" s="79">
         <f>D92</f>
-        <v>9717282.4300000016</v>
+        <v>12693770.43</v>
       </c>
       <c r="C106" s="39"/>
     </row>
@@ -2905,7 +2921,7 @@
       </c>
       <c r="B107" s="79">
         <f>D92-D90</f>
-        <v>8420712.2800000012</v>
+        <v>11397200.279999999</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2927,24 +2943,24 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="170" t="s">
-        <v>165</v>
-      </c>
-      <c r="B112" s="170"/>
-      <c r="C112" s="170"/>
-      <c r="D112" s="170"/>
+      <c r="A112" s="183" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="183"/>
+      <c r="C112" s="183"/>
+      <c r="D112" s="183"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="170"/>
-      <c r="B113" s="170"/>
-      <c r="C113" s="170"/>
-      <c r="D113" s="170"/>
+      <c r="A113" s="183"/>
+      <c r="B113" s="183"/>
+      <c r="C113" s="183"/>
+      <c r="D113" s="183"/>
     </row>
     <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="170"/>
-      <c r="B114" s="170"/>
-      <c r="C114" s="170"/>
-      <c r="D114" s="170"/>
+      <c r="A114" s="183"/>
+      <c r="B114" s="183"/>
+      <c r="C114" s="183"/>
+      <c r="D114" s="183"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="15" t="s">
@@ -2980,7 +2996,7 @@
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B120" s="119">
         <v>-10167</v>
@@ -2988,7 +3004,7 @@
     </row>
     <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B121" s="119">
         <v>-240000</v>
@@ -2996,7 +3012,7 @@
     </row>
     <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B122" s="119">
         <v>-260000</v>
@@ -3008,7 +3024,7 @@
       </c>
       <c r="B123" s="119">
         <f>-B107</f>
-        <v>-8420712.2800000012</v>
+        <v>-11397200.279999999</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -3026,7 +3042,7 @@
       </c>
       <c r="B125" s="105">
         <f>SUM(B117:B124)</f>
-        <v>8890735.379999999</v>
+        <v>5914247.3800000008</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3034,18 +3050,18 @@
       <c r="C126" s="39"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="169" t="s">
+      <c r="A128" s="182" t="s">
         <v>78</v>
       </c>
-      <c r="B128" s="169"/>
+      <c r="B128" s="182"/>
     </row>
     <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="169"/>
-      <c r="B129" s="169"/>
+      <c r="A129" s="182"/>
+      <c r="B129" s="182"/>
     </row>
     <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="101" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B130" s="29">
         <v>240000</v>
@@ -3053,7 +3069,7 @@
     </row>
     <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="101" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B131" s="29">
         <v>260000</v>
@@ -3072,37 +3088,36 @@
       <c r="L133" s="8"/>
     </row>
     <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="168"/>
-      <c r="B134" s="168"/>
-      <c r="C134" s="168"/>
-      <c r="D134" s="168"/>
+      <c r="A134" s="181"/>
+      <c r="B134" s="181"/>
+      <c r="C134" s="181"/>
+      <c r="D134" s="181"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="168"/>
-      <c r="B135" s="168"/>
-      <c r="C135" s="168"/>
-      <c r="D135" s="168"/>
+      <c r="A135" s="181"/>
+      <c r="B135" s="181"/>
+      <c r="C135" s="181"/>
+      <c r="D135" s="181"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="168"/>
-      <c r="B136" s="168"/>
-      <c r="C136" s="168"/>
-      <c r="D136" s="168"/>
+      <c r="A136" s="181"/>
+      <c r="B136" s="181"/>
+      <c r="C136" s="181"/>
+      <c r="D136" s="181"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="168"/>
-      <c r="B137" s="168"/>
-      <c r="C137" s="168"/>
-      <c r="D137" s="168"/>
+      <c r="A137" s="181"/>
+      <c r="B137" s="181"/>
+      <c r="C137" s="181"/>
+      <c r="D137" s="181"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A134:D137"/>
+    <mergeCell ref="A128:B129"/>
+    <mergeCell ref="A112:D114"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A82:B82"/>
@@ -3110,11 +3125,12 @@
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A134:D137"/>
-    <mergeCell ref="A128:B129"/>
-    <mergeCell ref="A112:D114"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A14:D17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3150,18 +3166,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="193" t="s">
-        <v>146</v>
-      </c>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
+      <c r="B1" s="186" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="186"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -3170,16 +3186,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="193"/>
-      <c r="G2" s="193"/>
-      <c r="H2" s="193"/>
-      <c r="I2" s="193"/>
-      <c r="J2" s="193"/>
-      <c r="K2" s="193"/>
+      <c r="B2" s="186"/>
+      <c r="C2" s="186"/>
+      <c r="D2" s="186"/>
+      <c r="E2" s="186"/>
+      <c r="F2" s="186"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="186"/>
+      <c r="K2" s="186"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3193,16 +3209,16 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="194"/>
-      <c r="K3" s="194"/>
+      <c r="B3" s="187"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="187"/>
+      <c r="E3" s="187"/>
+      <c r="F3" s="187"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="187"/>
+      <c r="J3" s="187"/>
+      <c r="K3" s="187"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3214,76 +3230,76 @@
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="187" t="s">
+      <c r="A4" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="189" t="s">
+      <c r="B4" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="191" t="s">
+      <c r="C4" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="191" t="s">
+      <c r="D4" s="190" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="191" t="s">
+      <c r="E4" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="191" t="s">
+      <c r="F4" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="191" t="s">
+      <c r="G4" s="190" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="191" t="s">
+      <c r="H4" s="190" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="191" t="s">
+      <c r="I4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="200" t="s">
+      <c r="J4" s="195" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="198" t="s">
+      <c r="L4" s="192" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="198" t="s">
+      <c r="M4" s="192" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="203" t="s">
+      <c r="N4" s="198" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="195" t="s">
+      <c r="P4" s="188" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="188"/>
-      <c r="B5" s="190"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="197"/>
-      <c r="J5" s="201"/>
-      <c r="K5" s="199"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="199"/>
-      <c r="N5" s="204"/>
+      <c r="A5" s="201"/>
+      <c r="B5" s="203"/>
+      <c r="C5" s="194"/>
+      <c r="D5" s="194"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="194"/>
+      <c r="G5" s="194"/>
+      <c r="H5" s="194"/>
+      <c r="I5" s="191"/>
+      <c r="J5" s="196"/>
+      <c r="K5" s="193"/>
+      <c r="L5" s="197"/>
+      <c r="M5" s="193"/>
+      <c r="N5" s="199"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="196"/>
+      <c r="P5" s="189"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -3398,7 +3414,7 @@
         <v>0.02</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3412,7 +3428,7 @@
         <v>53</v>
       </c>
       <c r="D8" s="127" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E8" s="128"/>
       <c r="F8" s="129">
@@ -3801,7 +3817,7 @@
         <v>0.09</v>
       </c>
       <c r="R14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -3861,7 +3877,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -4205,7 +4221,7 @@
         <v>0.16</v>
       </c>
       <c r="R21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S21" s="38"/>
     </row>
@@ -4941,93 +4957,98 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="168" t="s">
-        <v>147</v>
-      </c>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
-      <c r="M37" s="168"/>
-      <c r="N37" s="168"/>
-      <c r="O37" s="168"/>
+      <c r="D37" s="181" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="181"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="181"/>
+      <c r="H37" s="181"/>
+      <c r="I37" s="181"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="181"/>
+      <c r="L37" s="181"/>
+      <c r="M37" s="181"/>
+      <c r="N37" s="181"/>
+      <c r="O37" s="181"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="168"/>
-      <c r="E38" s="168"/>
-      <c r="F38" s="168"/>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
-      <c r="I38" s="168"/>
-      <c r="J38" s="168"/>
-      <c r="K38" s="168"/>
-      <c r="L38" s="168"/>
-      <c r="M38" s="168"/>
-      <c r="N38" s="168"/>
-      <c r="O38" s="168"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="181"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="181"/>
+      <c r="J38" s="181"/>
+      <c r="K38" s="181"/>
+      <c r="L38" s="181"/>
+      <c r="M38" s="181"/>
+      <c r="N38" s="181"/>
+      <c r="O38" s="181"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="168"/>
-      <c r="K39" s="168"/>
-      <c r="L39" s="168"/>
-      <c r="M39" s="168"/>
-      <c r="N39" s="168"/>
-      <c r="O39" s="168"/>
+      <c r="D39" s="181"/>
+      <c r="E39" s="181"/>
+      <c r="F39" s="181"/>
+      <c r="G39" s="181"/>
+      <c r="H39" s="181"/>
+      <c r="I39" s="181"/>
+      <c r="J39" s="181"/>
+      <c r="K39" s="181"/>
+      <c r="L39" s="181"/>
+      <c r="M39" s="181"/>
+      <c r="N39" s="181"/>
+      <c r="O39" s="181"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="168"/>
-      <c r="E40" s="168"/>
-      <c r="F40" s="168"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
-      <c r="I40" s="168"/>
-      <c r="J40" s="168"/>
-      <c r="K40" s="168"/>
-      <c r="L40" s="168"/>
-      <c r="M40" s="168"/>
-      <c r="N40" s="168"/>
-      <c r="O40" s="168"/>
+      <c r="D40" s="181"/>
+      <c r="E40" s="181"/>
+      <c r="F40" s="181"/>
+      <c r="G40" s="181"/>
+      <c r="H40" s="181"/>
+      <c r="I40" s="181"/>
+      <c r="J40" s="181"/>
+      <c r="K40" s="181"/>
+      <c r="L40" s="181"/>
+      <c r="M40" s="181"/>
+      <c r="N40" s="181"/>
+      <c r="O40" s="181"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="168"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="168"/>
-      <c r="I41" s="168"/>
-      <c r="J41" s="168"/>
-      <c r="K41" s="168"/>
-      <c r="L41" s="168"/>
-      <c r="M41" s="168"/>
-      <c r="N41" s="168"/>
-      <c r="O41" s="168"/>
+      <c r="D41" s="181"/>
+      <c r="E41" s="181"/>
+      <c r="F41" s="181"/>
+      <c r="G41" s="181"/>
+      <c r="H41" s="181"/>
+      <c r="I41" s="181"/>
+      <c r="J41" s="181"/>
+      <c r="K41" s="181"/>
+      <c r="L41" s="181"/>
+      <c r="M41" s="181"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="181"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="168"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="168"/>
-      <c r="H42" s="168"/>
-      <c r="I42" s="168"/>
-      <c r="J42" s="168"/>
-      <c r="K42" s="168"/>
-      <c r="L42" s="168"/>
-      <c r="M42" s="168"/>
-      <c r="N42" s="168"/>
-      <c r="O42" s="168"/>
+      <c r="D42" s="181"/>
+      <c r="E42" s="181"/>
+      <c r="F42" s="181"/>
+      <c r="G42" s="181"/>
+      <c r="H42" s="181"/>
+      <c r="I42" s="181"/>
+      <c r="J42" s="181"/>
+      <c r="K42" s="181"/>
+      <c r="L42" s="181"/>
+      <c r="M42" s="181"/>
+      <c r="N42" s="181"/>
+      <c r="O42" s="181"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -5040,11 +5061,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5058,12 +5074,12 @@
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" s="149" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C6" s="150" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2BC3FE-FA50-4EAE-A8F3-E279A4CB2F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7C1E63-AE58-4620-8082-6766F71134F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,28 @@
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$133</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="188">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -413,9 +426,6 @@
     <t>Banco Supervielle  - Gastos bancarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Allianz Argentina - Póliza 250230755635 - Integral consorcio </t>
-  </si>
-  <si>
     <t xml:space="preserve">Allianz Argentina - Póliza 240170531675 - Vida colectivo </t>
   </si>
   <si>
@@ -498,9 +508,6 @@
     <t>Transf 30/01</t>
   </si>
   <si>
-    <t>Mes de descanso</t>
-  </si>
-  <si>
     <t>PABLO GARCIA - MATIAS EZEQUIEL GARCIA</t>
   </si>
   <si>
@@ -594,7 +601,13 @@
     <t>Guenaga Gonzalo Federico</t>
   </si>
   <si>
-    <t>Agregar cuota alimentaria</t>
+    <t>Seguro Mercantil Andina - Sra Patricia Reemplazo vacaciones Diego</t>
+  </si>
+  <si>
+    <t>Debito 25/02</t>
+  </si>
+  <si>
+    <t>2-A - MAGRO LAUTARO - MAGRO DANIELA - CUOTA 1/6 PLAN DE PAGOS</t>
   </si>
 </sst>
 </file>
@@ -602,13 +615,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -796,13 +809,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1244,10 +1250,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1255,21 +1261,21 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1277,40 +1283,40 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1321,68 +1327,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1393,7 +1399,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1407,15 +1413,15 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1428,20 +1434,17 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="12" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1451,7 +1454,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1463,30 +1466,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="25" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1580,6 +1584,15 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1592,15 +1605,13 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1953,19 +1964,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L137"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.6328125" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1973,7 +1984,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1981,84 +1992,84 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="172" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="168" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="172"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="172"/>
-      <c r="B5" s="172"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="168"/>
+      <c r="B5" s="168"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="172"/>
-      <c r="B6" s="172"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="168"/>
+      <c r="B6" s="168"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="172"/>
-      <c r="B7" s="172"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="168"/>
+      <c r="B7" s="168"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="169" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="169"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="169"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="173" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="165" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="165"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="165"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="169" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="173"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="173"/>
-      <c r="B15" s="173"/>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="173"/>
-      <c r="B16" s="173"/>
-      <c r="C16" s="173"/>
-      <c r="D16" s="173"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="173"/>
-      <c r="B17" s="173"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="169"/>
+      <c r="C14" s="169"/>
+      <c r="D14" s="169"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="169"/>
+      <c r="B15" s="169"/>
+      <c r="C15" s="169"/>
+      <c r="D15" s="169"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="169"/>
+      <c r="B16" s="169"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="169"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="169"/>
+      <c r="B17" s="169"/>
+      <c r="C17" s="169"/>
+      <c r="D17" s="169"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2066,7 +2077,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2074,25 +2085,20 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C23" s="137">
         <v>1497939.7</v>
       </c>
       <c r="D23" s="80"/>
-      <c r="E23" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="168">
-        <v>293034.45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="160"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
@@ -2102,7 +2108,7 @@
       </c>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -2113,18 +2119,18 @@
       <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="153">
+      <c r="C26" s="137">
         <v>422400</v>
       </c>
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
@@ -2136,12 +2142,12 @@
       <c r="D27" s="47"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C28" s="137">
         <v>1232039.3</v>
@@ -2149,7 +2155,7 @@
       <c r="D28" s="80"/>
       <c r="G28" s="14"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
@@ -2160,7 +2166,7 @@
       <c r="D29" s="80"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -2171,18 +2177,18 @@
       <c r="D30" s="80"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="155">
+      <c r="C31" s="151">
         <v>633951.69999999995</v>
       </c>
       <c r="D31" s="80"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
@@ -2192,22 +2198,22 @@
         <v>1598022.7</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="205"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F32" s="163"/>
+      <c r="G32" s="164"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C33" s="137">
         <v>554812.06999999995</v>
       </c>
       <c r="D33" s="113"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
@@ -2217,7 +2223,7 @@
       </c>
       <c r="D34" s="113"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
@@ -2227,13 +2233,13 @@
       </c>
       <c r="D35" s="113"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="155"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="113"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="47" t="s">
         <v>82</v>
       </c>
@@ -2244,19 +2250,19 @@
       </c>
       <c r="D37" s="81"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C38" s="137">
         <v>1578850.12</v>
       </c>
       <c r="D38" s="80"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>84</v>
       </c>
@@ -2266,7 +2272,7 @@
       </c>
       <c r="D39" s="80"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>83</v>
       </c>
@@ -2275,20 +2281,15 @@
         <v>0.33</v>
       </c>
       <c r="D40" s="80"/>
-      <c r="E40" t="s">
-        <v>187</v>
-      </c>
-      <c r="G40" s="168">
-        <v>256062.56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G40" s="160"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="137"/>
       <c r="D41" s="80"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="47" t="s">
         <v>82</v>
       </c>
@@ -2299,19 +2300,19 @@
       </c>
       <c r="D42" s="47"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C43" s="137">
         <v>1433185.66</v>
       </c>
       <c r="D43" s="113"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
@@ -2321,7 +2322,7 @@
       </c>
       <c r="D44" s="113"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>83</v>
       </c>
@@ -2331,13 +2332,13 @@
       </c>
       <c r="D45" s="113"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="155"/>
+      <c r="C46" s="151"/>
       <c r="D46" s="113"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="47" t="s">
         <v>82</v>
       </c>
@@ -2348,19 +2349,19 @@
       </c>
       <c r="D47" s="81"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C48" s="137">
         <v>1388921.91</v>
       </c>
       <c r="D48" s="113"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>81</v>
       </c>
@@ -2370,7 +2371,7 @@
       </c>
       <c r="D49" s="113"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>83</v>
       </c>
@@ -2380,13 +2381,13 @@
       </c>
       <c r="D50" s="113"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="155"/>
+      <c r="C51" s="151"/>
       <c r="D51" s="113"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="47" t="s">
         <v>82</v>
       </c>
@@ -2397,7 +2398,7 @@
       </c>
       <c r="D52" s="81"/>
     </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="18" t="s">
         <v>0</v>
       </c>
@@ -2410,7 +2411,7 @@
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="26" t="s">
         <v>38</v>
       </c>
@@ -2419,35 +2420,35 @@
       <c r="D54" s="83"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="56" t="s">
         <v>39</v>
       </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="153">
+      <c r="C55" s="137">
         <v>135000</v>
       </c>
       <c r="D55" s="124" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="115" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B56" s="107" t="s">
-        <v>161</v>
-      </c>
-      <c r="C56" s="153">
+        <v>159</v>
+      </c>
+      <c r="C56" s="137">
         <v>211800</v>
       </c>
       <c r="D56" s="124" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="18" t="s">
         <v>34</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>346800</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="24" t="s">
         <v>77</v>
       </c>
@@ -2466,27 +2467,29 @@
       <c r="C58" s="28"/>
       <c r="D58" s="57"/>
     </row>
-    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="170" t="s">
+    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="166" t="s">
+        <v>185</v>
+      </c>
+      <c r="B59" s="167"/>
+      <c r="C59" s="203">
+        <v>10864.97</v>
+      </c>
+      <c r="D59" s="161" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="166" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="171"/>
-      <c r="C59" s="138" t="s">
-        <v>155</v>
-      </c>
-      <c r="D59" s="123"/>
-    </row>
-    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="170" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="171"/>
-      <c r="C60" s="167">
+      <c r="B60" s="167"/>
+      <c r="C60" s="204">
         <v>4203</v>
       </c>
       <c r="D60" s="123"/>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="25" t="s">
         <v>1</v>
       </c>
@@ -2494,54 +2497,54 @@
       <c r="C61" s="30"/>
       <c r="D61" s="84">
         <f>SUM(C59:C60)</f>
-        <v>4203</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15067.97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B62" s="144"/>
+      <c r="B62" s="143"/>
       <c r="C62" s="31"/>
       <c r="D62" s="85"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="B63" s="80" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="138">
+        <v>1421002.83</v>
+      </c>
+      <c r="D63" s="120" t="s">
+        <v>169</v>
+      </c>
+      <c r="F63" s="116"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="C63" s="151">
-        <v>1421002.83</v>
-      </c>
-      <c r="D63" s="120" t="s">
-        <v>171</v>
-      </c>
-      <c r="F63" s="116"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="80" t="s">
+      <c r="B64" s="80" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" s="144">
+        <v>16423.96</v>
+      </c>
+      <c r="D64" s="123" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="80" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="C64" s="152">
-        <v>16423.96</v>
-      </c>
-      <c r="D64" s="123" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="80" t="s">
-        <v>134</v>
-      </c>
       <c r="B65" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="C65" s="152">
+        <v>163</v>
+      </c>
+      <c r="C65" s="144">
         <v>147815.6</v>
       </c>
       <c r="D65" s="123" t="str">
@@ -2549,14 +2552,14 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="C66" s="152">
+        <v>163</v>
+      </c>
+      <c r="C66" s="144">
         <v>399207.23</v>
       </c>
       <c r="D66" s="121" t="str">
@@ -2564,104 +2567,104 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="144"/>
+      <c r="B67" s="143"/>
       <c r="C67" s="32"/>
       <c r="D67" s="84">
         <f>SUM(C63:C66)</f>
         <v>1984449.62</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B68" s="144"/>
+      <c r="B68" s="143"/>
       <c r="C68" s="31"/>
       <c r="D68" s="85"/>
     </row>
-    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B69" s="80"/>
-      <c r="C69" s="152">
+      <c r="C69" s="144">
         <v>554680.11</v>
       </c>
       <c r="D69" s="120" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B70" s="80"/>
-      <c r="C70" s="152"/>
+      <c r="C70" s="144"/>
       <c r="D70" s="120"/>
     </row>
-    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="80" t="s">
         <v>125</v>
       </c>
       <c r="B71" s="80"/>
-      <c r="C71" s="152">
+      <c r="C71" s="144">
         <v>20460.259999999998</v>
       </c>
       <c r="D71" s="120" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B72" s="80"/>
-      <c r="C72" s="152">
+      <c r="C72" s="144">
         <v>864000.26</v>
       </c>
       <c r="D72" s="120" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="179" t="s">
-        <v>162</v>
-      </c>
-      <c r="B73" s="180"/>
-      <c r="C73" s="152">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="175" t="s">
+        <v>160</v>
+      </c>
+      <c r="B73" s="176"/>
+      <c r="C73" s="144">
         <v>204149</v>
       </c>
       <c r="D73" s="120" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="177" t="s">
-        <v>152</v>
-      </c>
-      <c r="B74" s="178"/>
-      <c r="C74" s="145">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="173" t="s">
+        <v>151</v>
+      </c>
+      <c r="B74" s="174"/>
+      <c r="C74" s="144">
         <v>0</v>
       </c>
       <c r="D74" s="122"/>
     </row>
-    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="170" t="s">
-        <v>151</v>
-      </c>
-      <c r="B75" s="171"/>
-      <c r="C75" s="152">
+    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="166" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="167"/>
+      <c r="C75" s="144">
         <v>35200</v>
       </c>
       <c r="D75" s="122" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="25" t="s">
         <v>3</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>1678489.63</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="24" t="s">
         <v>36</v>
       </c>
@@ -2680,79 +2683,79 @@
       <c r="C77" s="30"/>
       <c r="D77" s="87"/>
     </row>
-    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="147" t="s">
+    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="146" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="145"/>
+      <c r="C78" s="144">
+        <v>51919.14</v>
+      </c>
+      <c r="D78" s="118" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="166" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" s="167"/>
+      <c r="C79" s="144">
+        <v>753830.53</v>
+      </c>
+      <c r="D79" s="120" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="150" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="142"/>
+      <c r="C80" s="144">
+        <v>10000</v>
+      </c>
+      <c r="D80" s="141" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="150" t="s">
         <v>180</v>
       </c>
-      <c r="B78" s="146"/>
-      <c r="C78" s="152">
-        <v>51919.14</v>
-      </c>
-      <c r="D78" s="118" t="s">
+      <c r="B81" s="142"/>
+      <c r="C81" s="144">
+        <v>8760.52</v>
+      </c>
+      <c r="D81" s="122" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="170" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="171"/>
-      <c r="C79" s="152">
-        <v>753830.53</v>
-      </c>
-      <c r="D79" s="120" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="154" t="s">
-        <v>173</v>
-      </c>
-      <c r="B80" s="143"/>
-      <c r="C80" s="152">
-        <v>10000</v>
-      </c>
-      <c r="D80" s="142" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="154" t="s">
-        <v>182</v>
-      </c>
-      <c r="B81" s="143"/>
-      <c r="C81" s="152">
-        <v>8760.52</v>
-      </c>
-      <c r="D81" s="122" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="170" t="s">
-        <v>166</v>
-      </c>
-      <c r="B82" s="171"/>
-      <c r="C82" s="152">
+    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="166" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="167"/>
+      <c r="C82" s="144">
         <v>34000</v>
       </c>
       <c r="D82" s="122" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E82" s="39"/>
       <c r="F82" s="39"/>
     </row>
-    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="177" t="s">
-        <v>163</v>
-      </c>
-      <c r="B83" s="178"/>
-      <c r="C83" s="139">
+    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="173" t="s">
+        <v>161</v>
+      </c>
+      <c r="B83" s="174"/>
+      <c r="C83" s="138">
         <v>0</v>
       </c>
       <c r="D83" s="122"/>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="25" t="s">
         <v>11</v>
       </c>
@@ -2763,35 +2766,36 @@
         <v>858510.19000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B85" s="148"/>
+      <c r="B85" s="147"/>
       <c r="C85" s="19"/>
       <c r="D85" s="87"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B86" s="80"/>
-      <c r="C86" s="152">
+      <c r="C86" s="144">
         <v>65343</v>
       </c>
       <c r="D86" s="91"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="80" t="s">
         <v>126</v>
       </c>
       <c r="B87" s="80"/>
-      <c r="C87" s="152">
-        <v>149249.14000000001</v>
+      <c r="C87" s="144">
+        <f>65.19+149249.14</f>
+        <v>149314.33000000002</v>
       </c>
       <c r="D87" s="89"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="44" t="s">
         <v>34</v>
       </c>
@@ -2799,33 +2803,33 @@
       <c r="C88" s="92"/>
       <c r="D88" s="84">
         <f>SUM(C86:C87)</f>
-        <v>214592.14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>214657.33000000002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="80"/>
       <c r="D89" s="93"/>
     </row>
-    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="174" t="s">
-        <v>143</v>
-      </c>
-      <c r="B90" s="175"/>
-      <c r="C90" s="176"/>
+    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="170" t="s">
+        <v>142</v>
+      </c>
+      <c r="B90" s="171"/>
+      <c r="C90" s="172"/>
       <c r="D90" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1"/>
       <c r="C91" s="95"/>
       <c r="D91" s="96"/>
       <c r="E91" s="39"/>
     </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
         <v>30</v>
       </c>
@@ -2833,21 +2837,21 @@
       <c r="C92" s="97"/>
       <c r="D92" s="98">
         <f>(SUM(D33:D90))</f>
-        <v>12693770.43</v>
+        <v>12704700.589999998</v>
       </c>
       <c r="E92" s="39"/>
       <c r="F92" s="39"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C93" s="95"/>
       <c r="D93" s="95"/>
       <c r="F93" s="117"/>
     </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C94" s="95"/>
       <c r="D94" s="95"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="11" t="s">
         <v>40</v>
       </c>
@@ -2855,25 +2859,25 @@
       <c r="C95" s="99"/>
       <c r="D95" s="100"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="184"/>
-      <c r="B96" s="185"/>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="180"/>
+      <c r="B96" s="181"/>
       <c r="C96" s="88"/>
       <c r="D96" s="86"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="184"/>
-      <c r="B97" s="185"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="180"/>
+      <c r="B97" s="181"/>
       <c r="C97" s="88"/>
       <c r="D97" s="86"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="103"/>
       <c r="B98" s="104"/>
       <c r="C98" s="88"/>
       <c r="D98" s="86"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="42"/>
       <c r="B99" s="41"/>
       <c r="C99" s="49"/>
@@ -2882,18 +2886,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="21"/>
-      <c r="D102" s="125"/>
-    </row>
-    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D102" s="125">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
         <v>42</v>
       </c>
@@ -2901,30 +2907,30 @@
       <c r="C104" s="4"/>
       <c r="D104" s="58">
         <f>D99+D102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="78" t="s">
         <v>31</v>
       </c>
       <c r="B106" s="79">
         <f>D92</f>
-        <v>12693770.43</v>
+        <v>12704700.589999998</v>
       </c>
       <c r="C106" s="39"/>
     </row>
-    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="78" t="s">
         <v>32</v>
       </c>
       <c r="B107" s="79">
         <f>D92-D90</f>
-        <v>11397200.279999999</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>11408130.439999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="78" t="s">
         <v>43</v>
       </c>
@@ -2933,59 +2939,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="78" t="s">
         <v>88</v>
       </c>
       <c r="B109" s="79">
         <f>D104</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="183" t="s">
-        <v>164</v>
-      </c>
-      <c r="B112" s="183"/>
-      <c r="C112" s="183"/>
-      <c r="D112" s="183"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="183"/>
-      <c r="B113" s="183"/>
-      <c r="C113" s="183"/>
-      <c r="D113" s="183"/>
-    </row>
-    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="183"/>
-      <c r="B114" s="183"/>
-      <c r="C114" s="183"/>
-      <c r="D114" s="183"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" s="179" t="s">
+        <v>162</v>
+      </c>
+      <c r="B112" s="179"/>
+      <c r="C112" s="179"/>
+      <c r="D112" s="179"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" s="179"/>
+      <c r="B113" s="179"/>
+      <c r="C113" s="179"/>
+      <c r="D113" s="179"/>
+    </row>
+    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="179"/>
+      <c r="B114" s="179"/>
+      <c r="C114" s="179"/>
+      <c r="D114" s="179"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B116" s="35"/>
     </row>
-    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B117" s="105">
-        <v>5322816.5199999996</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7139335.7599999998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B118" s="36">
-        <f>PRORRATEO!H34</f>
-        <v>11998798.140000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f>PRORRATEO!H35</f>
+        <v>12003298.140000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="16" t="s">
         <v>90</v>
       </c>
@@ -2994,40 +3000,40 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B120" s="119">
         <v>-10167</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B121" s="119">
         <v>-240000</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B122" s="119">
         <v>-260000</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="34" t="s">
         <v>44</v>
       </c>
       <c r="B123" s="119">
         <f>-B107</f>
-        <v>-11397200.279999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+        <v>-11408130.439999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="17" t="s">
         <v>45</v>
       </c>
@@ -3036,46 +3042,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B125" s="105">
         <f>SUM(B117:B124)</f>
-        <v>5914247.3800000008</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7724336.4600000009</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="37"/>
       <c r="C126" s="39"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="182" t="s">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" s="178" t="s">
         <v>78</v>
       </c>
-      <c r="B128" s="182"/>
-    </row>
-    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="182"/>
-      <c r="B129" s="182"/>
-    </row>
-    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="178"/>
+    </row>
+    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="178"/>
+      <c r="B129" s="178"/>
+    </row>
+    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="101" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B130" s="29">
         <v>240000</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="101" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B131" s="29">
         <v>260000</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="40" t="s">
         <v>11</v>
       </c>
@@ -3084,32 +3090,32 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L133" s="8"/>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="181"/>
-      <c r="B134" s="181"/>
-      <c r="C134" s="181"/>
-      <c r="D134" s="181"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="181"/>
-      <c r="B135" s="181"/>
-      <c r="C135" s="181"/>
-      <c r="D135" s="181"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="181"/>
-      <c r="B136" s="181"/>
-      <c r="C136" s="181"/>
-      <c r="D136" s="181"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="181"/>
-      <c r="B137" s="181"/>
-      <c r="C137" s="181"/>
-      <c r="D137" s="181"/>
+    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="177"/>
+      <c r="B134" s="177"/>
+      <c r="C134" s="177"/>
+      <c r="D134" s="177"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A135" s="177"/>
+      <c r="B135" s="177"/>
+      <c r="C135" s="177"/>
+      <c r="D135" s="177"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A136" s="177"/>
+      <c r="B136" s="177"/>
+      <c r="C136" s="177"/>
+      <c r="D136" s="177"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A137" s="177"/>
+      <c r="B137" s="177"/>
+      <c r="C137" s="177"/>
+      <c r="D137" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3140,168 +3146,168 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S43"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" customWidth="1"/>
+    <col min="3" max="3" width="4.36328125" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.08984375" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6328125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" customWidth="1"/>
+    <col min="11" max="11" width="11.08984375" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" customWidth="1"/>
+    <col min="14" max="14" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" customWidth="1"/>
+    <col min="16" max="16" width="14.08984375" customWidth="1"/>
+    <col min="17" max="17" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6"/>
-      <c r="B1" s="186" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
+      <c r="B1" s="182" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
+      <c r="G1" s="182"/>
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
+      <c r="I2" s="182"/>
+      <c r="J2" s="182"/>
+      <c r="K2" s="182"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="140">
+      <c r="O2" s="139">
         <v>10000000</v>
       </c>
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6"/>
-      <c r="B3" s="187"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
-      <c r="J3" s="187"/>
-      <c r="K3" s="187"/>
+      <c r="B3" s="183"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="141">
-        <v>1000000</v>
+      <c r="O3" s="140">
+        <v>2000000</v>
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="200" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" s="199" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="201" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="190" t="s">
+      <c r="D4" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="190" t="s">
+      <c r="E4" s="186" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="190" t="s">
+      <c r="F4" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="190" t="s">
+      <c r="G4" s="186" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="190" t="s">
+      <c r="H4" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="190" t="s">
+      <c r="I4" s="186" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="195" t="s">
+      <c r="J4" s="191" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="192" t="s">
+      <c r="K4" s="188" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="192" t="s">
+      <c r="L4" s="188" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="192" t="s">
+      <c r="M4" s="188" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="198" t="s">
+      <c r="N4" s="194" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="188" t="s">
+      <c r="P4" s="184" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="201"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="193"/>
-      <c r="L5" s="197"/>
-      <c r="M5" s="193"/>
-      <c r="N5" s="199"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="200"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="187"/>
+      <c r="J5" s="192"/>
+      <c r="K5" s="189"/>
+      <c r="L5" s="193"/>
+      <c r="M5" s="189"/>
+      <c r="N5" s="195"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="189"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="185"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3321,7 +3327,7 @@
       <c r="G6" s="60">
         <v>502700.01</v>
       </c>
-      <c r="H6" s="156">
+      <c r="H6" s="61">
         <f>G6</f>
         <v>502700.01</v>
       </c>
@@ -3336,7 +3342,7 @@
       </c>
       <c r="L6" s="64">
         <f>O$3*F6%</f>
-        <v>45700.000000000007</v>
+        <v>91400.000000000015</v>
       </c>
       <c r="M6" s="64">
         <f>O$2*F6%</f>
@@ -3346,78 +3352,78 @@
         <v>0</v>
       </c>
       <c r="O6" s="66">
-        <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>502700.01</v>
+        <f t="shared" ref="O6:O34" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
+        <v>548400.01</v>
       </c>
       <c r="P6" s="67">
-        <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>517781.01</v>
+        <f t="shared" ref="P6:P34" si="1">ROUND(O6*3%,0) + O6</f>
+        <v>564852.01</v>
       </c>
       <c r="Q6" s="39">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="159">
+      <c r="B7" s="152">
         <v>2</v>
       </c>
-      <c r="C7" s="159" t="s">
+      <c r="C7" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="159" t="s">
+      <c r="D7" s="152" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="166"/>
-      <c r="F7" s="160">
+      <c r="E7" s="159"/>
+      <c r="F7" s="153">
         <v>3.07</v>
       </c>
       <c r="G7" s="61">
         <v>347831.02</v>
       </c>
-      <c r="H7" s="156">
+      <c r="H7" s="61">
         <f>G7</f>
         <v>347831.02</v>
       </c>
       <c r="I7" s="62"/>
-      <c r="J7" s="161">
-        <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="161">
-        <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="162">
-        <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
-        <v>30699.999999999996</v>
-      </c>
-      <c r="M7" s="162">
-        <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
+      <c r="J7" s="154">
+        <f t="shared" ref="J7:J32" si="2">G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="154">
+        <f t="shared" ref="K7:K33" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="155">
+        <f t="shared" ref="L7:L34" si="4">O$3*F7%</f>
+        <v>61399.999999999993</v>
+      </c>
+      <c r="M7" s="155">
+        <f t="shared" ref="M7:M34" si="5">O$2*F7%</f>
         <v>307000</v>
       </c>
-      <c r="N7" s="163">
-        <v>0</v>
-      </c>
-      <c r="O7" s="164">
+      <c r="N7" s="156">
+        <v>0</v>
+      </c>
+      <c r="O7" s="157">
         <f t="shared" si="0"/>
-        <v>337700.02</v>
-      </c>
-      <c r="P7" s="165">
+        <v>368400.02</v>
+      </c>
+      <c r="P7" s="158">
         <f t="shared" si="1"/>
-        <v>347831.02</v>
+        <v>379452.02</v>
       </c>
       <c r="Q7" s="39">
         <f>Q6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3428,7 +3434,7 @@
         <v>53</v>
       </c>
       <c r="D8" s="127" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E8" s="128"/>
       <c r="F8" s="129">
@@ -3437,22 +3443,21 @@
       <c r="G8" s="130">
         <v>1015765.03</v>
       </c>
-      <c r="H8" s="157">
-        <f>400000+500500</f>
-        <v>900500</v>
+      <c r="H8" s="130">
+        <v>505000</v>
       </c>
       <c r="I8" s="131"/>
       <c r="J8" s="132">
         <f t="shared" si="2"/>
-        <v>115265.03000000003</v>
+        <v>510765.03</v>
       </c>
       <c r="K8" s="132">
         <f t="shared" si="3"/>
-        <v>3400.3183850000009</v>
+        <v>15067.568385000002</v>
       </c>
       <c r="L8" s="133">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>91000</v>
       </c>
       <c r="M8" s="133">
         <f t="shared" si="5"/>
@@ -3463,331 +3468,300 @@
       </c>
       <c r="O8" s="135">
         <f t="shared" si="0"/>
-        <v>619165.03</v>
+        <v>1071833.03</v>
       </c>
       <c r="P8" s="136">
         <f t="shared" si="1"/>
-        <v>637740.03</v>
+        <v>1103988.03</v>
       </c>
       <c r="Q8" s="39">
-        <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
+        <f t="shared" ref="Q8:Q33" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="54">
-        <v>4</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="59">
-        <v>3.05</v>
-      </c>
-      <c r="G9" s="60">
-        <v>323930.03999999998</v>
-      </c>
-      <c r="H9" s="156">
-        <v>350000</v>
-      </c>
-      <c r="I9" s="62"/>
-      <c r="J9" s="63">
-        <f t="shared" si="2"/>
-        <v>-26069.960000000021</v>
-      </c>
-      <c r="K9" s="63">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="64">
-        <f t="shared" si="4"/>
-        <v>30500</v>
-      </c>
-      <c r="M9" s="64">
-        <f t="shared" si="5"/>
-        <v>305000</v>
-      </c>
-      <c r="N9" s="65">
-        <v>0</v>
-      </c>
-      <c r="O9" s="66">
-        <f t="shared" si="0"/>
-        <v>309430.03999999998</v>
-      </c>
-      <c r="P9" s="67">
-        <f t="shared" si="1"/>
-        <v>318713.03999999998</v>
-      </c>
-      <c r="Q9" s="39">
-        <f t="shared" si="6"/>
-        <v>0.04</v>
-      </c>
-      <c r="R9" t="s">
-        <v>141</v>
-      </c>
-      <c r="S9" s="39"/>
-    </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="B9" s="196" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="197"/>
+      <c r="D9" s="198"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="130">
+        <v>400000</v>
+      </c>
+      <c r="H9" s="130">
+        <v>400000</v>
+      </c>
+      <c r="I9" s="131"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="134"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="136"/>
+      <c r="Q9" s="39"/>
+    </row>
+    <row r="10" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E10" s="55"/>
       <c r="F10" s="59">
-        <v>4.55</v>
+        <v>3.05</v>
       </c>
       <c r="G10" s="60">
-        <v>515626.05</v>
-      </c>
-      <c r="H10" s="61"/>
+        <v>323930.03999999998</v>
+      </c>
+      <c r="H10" s="61">
+        <v>350000</v>
+      </c>
       <c r="I10" s="62"/>
       <c r="J10" s="63">
         <f t="shared" si="2"/>
-        <v>515626.05</v>
+        <v>-26069.960000000021</v>
       </c>
       <c r="K10" s="63">
         <f t="shared" si="3"/>
-        <v>15210.968475000001</v>
+        <v>0</v>
       </c>
       <c r="L10" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>61000</v>
       </c>
       <c r="M10" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>305000</v>
       </c>
       <c r="N10" s="65">
         <v>0</v>
       </c>
       <c r="O10" s="66">
         <f t="shared" si="0"/>
-        <v>1031337.05</v>
+        <v>339930.04</v>
       </c>
       <c r="P10" s="67">
         <f t="shared" si="1"/>
-        <v>1062277.05</v>
+        <v>350128.04</v>
       </c>
       <c r="Q10" s="39">
-        <f t="shared" si="6"/>
-        <v>0.05</v>
+        <f>Q8+0.01</f>
+        <v>0.04</v>
+      </c>
+      <c r="R10" t="s">
+        <v>140</v>
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="54"/>
+        <v>98</v>
+      </c>
+      <c r="E11" s="55"/>
       <c r="F11" s="59">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="G11" s="60">
-        <v>335500.06</v>
-      </c>
-      <c r="H11" s="156">
-        <f>G11</f>
-        <v>335500.06</v>
-      </c>
+        <v>515626.05</v>
+      </c>
+      <c r="H11" s="61"/>
       <c r="I11" s="62"/>
       <c r="J11" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>515626.05</v>
       </c>
       <c r="K11" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15210.968475000001</v>
       </c>
       <c r="L11" s="64">
         <f t="shared" si="4"/>
-        <v>30500</v>
+        <v>91000</v>
       </c>
       <c r="M11" s="64">
         <f t="shared" si="5"/>
-        <v>305000</v>
+        <v>455000</v>
       </c>
       <c r="N11" s="65">
         <v>0</v>
       </c>
       <c r="O11" s="66">
         <f t="shared" si="0"/>
-        <v>335500.06</v>
+        <v>1076837.05</v>
       </c>
       <c r="P11" s="67">
         <f t="shared" si="1"/>
-        <v>345565.06</v>
+        <v>1109142.05</v>
       </c>
       <c r="Q11" s="39">
         <f t="shared" si="6"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.05</v>
+      </c>
+      <c r="S11" s="39"/>
+    </row>
+    <row r="12" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="159">
+      <c r="B12" s="54">
+        <v>6</v>
+      </c>
+      <c r="C12" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="54"/>
+      <c r="F12" s="59">
+        <v>3.05</v>
+      </c>
+      <c r="G12" s="60">
+        <v>335500.06</v>
+      </c>
+      <c r="H12" s="61">
+        <f>G12</f>
+        <v>335500.06</v>
+      </c>
+      <c r="I12" s="62"/>
+      <c r="J12" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="63">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="64">
+        <f t="shared" si="4"/>
+        <v>61000</v>
+      </c>
+      <c r="M12" s="64">
+        <f t="shared" si="5"/>
+        <v>305000</v>
+      </c>
+      <c r="N12" s="65">
+        <v>0</v>
+      </c>
+      <c r="O12" s="66">
+        <f t="shared" si="0"/>
+        <v>366000.06</v>
+      </c>
+      <c r="P12" s="67">
+        <f t="shared" si="1"/>
+        <v>376980.06</v>
+      </c>
+      <c r="Q12" s="39">
+        <f t="shared" si="6"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="152">
         <v>7</v>
       </c>
-      <c r="C12" s="159" t="s">
+      <c r="C13" s="152" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="159" t="s">
+      <c r="D13" s="152" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="159"/>
-      <c r="F12" s="160">
+      <c r="E13" s="152"/>
+      <c r="F13" s="153">
         <v>4.55</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G13" s="61">
         <v>1011647.07</v>
       </c>
-      <c r="H12" s="156">
+      <c r="H13" s="61">
         <f>240000+260000+501000+10647</f>
         <v>1011647</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="161">
+      <c r="I13" s="62"/>
+      <c r="J13" s="154">
         <f t="shared" si="2"/>
         <v>6.9999999948777258E-2</v>
       </c>
-      <c r="K12" s="161">
+      <c r="K13" s="154">
         <f t="shared" si="3"/>
         <v>2.0649999984889292E-3</v>
       </c>
-      <c r="L12" s="162">
+      <c r="L13" s="155">
         <f t="shared" si="4"/>
-        <v>45500</v>
-      </c>
-      <c r="M12" s="162">
+        <v>91000</v>
+      </c>
+      <c r="M13" s="155">
         <f t="shared" si="5"/>
         <v>455000</v>
       </c>
-      <c r="N12" s="163">
-        <v>0</v>
-      </c>
-      <c r="O12" s="164">
+      <c r="N13" s="156">
+        <v>0</v>
+      </c>
+      <c r="O13" s="157">
         <f t="shared" si="0"/>
-        <v>500500.07</v>
-      </c>
-      <c r="P12" s="165">
+        <v>546000.06999999995</v>
+      </c>
+      <c r="P13" s="158">
         <f t="shared" si="1"/>
-        <v>515515.07</v>
-      </c>
-      <c r="Q12" s="39">
+        <v>562380.06999999995</v>
+      </c>
+      <c r="Q13" s="39">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R12" s="117"/>
-      <c r="S12" s="116"/>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="54">
-        <v>8</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="59">
-        <v>3.05</v>
-      </c>
-      <c r="G13" s="60">
-        <v>325702.08</v>
-      </c>
-      <c r="H13" s="156">
-        <v>335473</v>
-      </c>
-      <c r="I13" s="62"/>
-      <c r="J13" s="63">
-        <f t="shared" si="2"/>
-        <v>-9770.9199999999837</v>
-      </c>
-      <c r="K13" s="63">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="64">
-        <f t="shared" si="4"/>
-        <v>30500</v>
-      </c>
-      <c r="M13" s="64">
-        <f t="shared" si="5"/>
-        <v>305000</v>
-      </c>
-      <c r="N13" s="65">
-        <v>0</v>
-      </c>
-      <c r="O13" s="66">
-        <f t="shared" si="0"/>
-        <v>325729.08</v>
-      </c>
-      <c r="P13" s="67">
-        <f t="shared" si="1"/>
-        <v>335501.08</v>
-      </c>
-      <c r="Q13" s="39">
-        <f t="shared" si="6"/>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="117"/>
+      <c r="S13" s="116"/>
+    </row>
+    <row r="14" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="54">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="59">
-        <v>4.5599999999999996</v>
+        <v>3.05</v>
       </c>
       <c r="G14" s="60">
-        <v>498800.09</v>
-      </c>
-      <c r="H14" s="158">
-        <v>514000</v>
+        <v>325702.08</v>
+      </c>
+      <c r="H14" s="61">
+        <v>335473</v>
       </c>
       <c r="I14" s="62"/>
       <c r="J14" s="63">
         <f t="shared" si="2"/>
-        <v>-15199.909999999974</v>
+        <v>-9770.9199999999837</v>
       </c>
       <c r="K14" s="63">
         <f t="shared" si="3"/>
@@ -3795,59 +3769,55 @@
       </c>
       <c r="L14" s="64">
         <f t="shared" si="4"/>
-        <v>45599.999999999993</v>
+        <v>61000</v>
       </c>
       <c r="M14" s="64">
         <f t="shared" si="5"/>
-        <v>455999.99999999994</v>
+        <v>305000</v>
       </c>
       <c r="N14" s="65">
         <v>0</v>
       </c>
       <c r="O14" s="66">
         <f t="shared" si="0"/>
-        <v>486400.09</v>
+        <v>356229.08</v>
       </c>
       <c r="P14" s="67">
         <f t="shared" si="1"/>
-        <v>500992.09</v>
+        <v>366916.08</v>
       </c>
       <c r="Q14" s="39">
         <f t="shared" si="6"/>
-        <v>0.09</v>
-      </c>
-      <c r="R14" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="59">
-        <v>3.05</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G15" s="60">
-        <v>335500.09999999998</v>
-      </c>
-      <c r="H15" s="156">
-        <f>G15</f>
-        <v>335500.09999999998</v>
+        <v>498800.09</v>
+      </c>
+      <c r="H15" s="162">
+        <v>514000</v>
       </c>
       <c r="I15" s="62"/>
       <c r="J15" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-15199.909999999974</v>
       </c>
       <c r="K15" s="63">
         <f t="shared" si="3"/>
@@ -3855,54 +3825,54 @@
       </c>
       <c r="L15" s="64">
         <f t="shared" si="4"/>
-        <v>30500</v>
+        <v>91199.999999999985</v>
       </c>
       <c r="M15" s="64">
         <f t="shared" si="5"/>
-        <v>305000</v>
+        <v>455999.99999999994</v>
       </c>
       <c r="N15" s="65">
         <v>0</v>
       </c>
       <c r="O15" s="66">
         <f t="shared" si="0"/>
-        <v>335500.09999999998</v>
+        <v>532000.09</v>
       </c>
       <c r="P15" s="67">
         <f t="shared" si="1"/>
-        <v>345565.1</v>
+        <v>547960.09</v>
       </c>
       <c r="Q15" s="39">
         <f t="shared" si="6"/>
-        <v>9.9999999999999992E-2</v>
+        <v>0.09</v>
       </c>
       <c r="R15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="54">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" s="55"/>
       <c r="F16" s="59">
-        <v>4.55</v>
+        <v>3.05</v>
       </c>
       <c r="G16" s="60">
-        <v>485485.11</v>
-      </c>
-      <c r="H16" s="156">
+        <v>335500.09999999998</v>
+      </c>
+      <c r="H16" s="61">
         <f>G16</f>
-        <v>485485.11</v>
+        <v>335500.09999999998</v>
       </c>
       <c r="I16" s="62"/>
       <c r="J16" s="63">
@@ -3915,165 +3885,168 @@
       </c>
       <c r="L16" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>61000</v>
       </c>
       <c r="M16" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>305000</v>
       </c>
       <c r="N16" s="65">
         <v>0</v>
       </c>
       <c r="O16" s="66">
         <f t="shared" si="0"/>
-        <v>500500.11</v>
+        <v>366000.1</v>
       </c>
       <c r="P16" s="67">
         <f t="shared" si="1"/>
-        <v>515515.11</v>
+        <v>376980.1</v>
       </c>
       <c r="Q16" s="39">
         <f t="shared" si="6"/>
-        <v>0.10999999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="R16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" s="55"/>
       <c r="F17" s="59">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="G17" s="60">
-        <v>762336.12</v>
-      </c>
-      <c r="H17" s="156">
-        <f>300000+5000</f>
-        <v>305000</v>
+        <v>485485.11</v>
+      </c>
+      <c r="H17" s="61">
+        <f>G17</f>
+        <v>485485.11</v>
       </c>
       <c r="I17" s="62"/>
       <c r="J17" s="63">
         <f t="shared" si="2"/>
-        <v>457336.12</v>
+        <v>0</v>
       </c>
       <c r="K17" s="63">
         <f t="shared" si="3"/>
-        <v>13491.41554</v>
+        <v>0</v>
       </c>
       <c r="L17" s="64">
         <f t="shared" si="4"/>
-        <v>30500</v>
+        <v>91000</v>
       </c>
       <c r="M17" s="64">
         <f t="shared" si="5"/>
-        <v>305000</v>
+        <v>455000</v>
       </c>
       <c r="N17" s="65">
         <v>0</v>
       </c>
       <c r="O17" s="66">
         <f t="shared" si="0"/>
-        <v>806328.12</v>
+        <v>546000.11</v>
       </c>
       <c r="P17" s="67">
         <f t="shared" si="1"/>
-        <v>830518.12</v>
+        <v>562380.11</v>
       </c>
       <c r="Q17" s="39">
         <f t="shared" si="6"/>
-        <v>0.11999999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.10999999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="54">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E18" s="55"/>
       <c r="F18" s="59">
-        <v>4.55</v>
+        <v>3.05</v>
       </c>
       <c r="G18" s="60">
-        <v>500500.13</v>
-      </c>
-      <c r="H18" s="156">
-        <f>G18</f>
-        <v>500500.13</v>
+        <v>762336.12</v>
+      </c>
+      <c r="H18" s="61">
+        <f>300000+5000</f>
+        <v>305000</v>
       </c>
       <c r="I18" s="62"/>
       <c r="J18" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>457336.12</v>
       </c>
       <c r="K18" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13491.41554</v>
       </c>
       <c r="L18" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>61000</v>
       </c>
       <c r="M18" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>305000</v>
       </c>
       <c r="N18" s="65">
         <v>0</v>
       </c>
       <c r="O18" s="66">
         <f t="shared" si="0"/>
-        <v>500500.13</v>
+        <v>836828.12</v>
       </c>
       <c r="P18" s="67">
         <f t="shared" si="1"/>
-        <v>515515.13</v>
+        <v>861933.12</v>
       </c>
       <c r="Q18" s="39">
         <f t="shared" si="6"/>
-        <v>0.12999999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.11999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="54">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E19" s="55"/>
       <c r="F19" s="59">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="G19" s="60">
-        <v>349800.14</v>
-      </c>
-      <c r="H19" s="156">
+        <v>500500.13</v>
+      </c>
+      <c r="H19" s="61">
         <f>G19</f>
-        <v>349800.14</v>
+        <v>500500.13</v>
       </c>
       <c r="I19" s="62"/>
       <c r="J19" s="63">
@@ -4086,51 +4059,51 @@
       </c>
       <c r="L19" s="64">
         <f t="shared" si="4"/>
-        <v>31800.000000000004</v>
+        <v>91000</v>
       </c>
       <c r="M19" s="64">
         <f t="shared" si="5"/>
-        <v>318000</v>
+        <v>455000</v>
       </c>
       <c r="N19" s="65">
         <v>0</v>
       </c>
       <c r="O19" s="66">
         <f t="shared" si="0"/>
-        <v>349800.14</v>
+        <v>546000.13</v>
       </c>
       <c r="P19" s="67">
         <f t="shared" si="1"/>
-        <v>360294.14</v>
+        <v>562380.13</v>
       </c>
       <c r="Q19" s="39">
         <f t="shared" si="6"/>
-        <v>0.13999999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.12999999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="54">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="55"/>
       <c r="F20" s="59">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="G20" s="60">
-        <v>500500.15</v>
-      </c>
-      <c r="H20" s="156">
+        <v>349800.14</v>
+      </c>
+      <c r="H20" s="61">
         <f>G20</f>
-        <v>500500.15</v>
+        <v>349800.14</v>
       </c>
       <c r="I20" s="62"/>
       <c r="J20" s="63">
@@ -4143,55 +4116,56 @@
       </c>
       <c r="L20" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>63600.000000000007</v>
       </c>
       <c r="M20" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>318000</v>
       </c>
       <c r="N20" s="65">
         <v>0</v>
       </c>
       <c r="O20" s="66">
         <f t="shared" si="0"/>
-        <v>500500.15</v>
+        <v>381600.14</v>
       </c>
       <c r="P20" s="67">
         <f t="shared" si="1"/>
-        <v>515515.15</v>
+        <v>393048.14</v>
       </c>
       <c r="Q20" s="39">
         <f t="shared" si="6"/>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.13999999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="54">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="54"/>
+        <v>108</v>
+      </c>
+      <c r="E21" s="55"/>
       <c r="F21" s="59">
-        <v>3.17</v>
+        <v>4.55</v>
       </c>
       <c r="G21" s="60">
-        <v>348154.16</v>
-      </c>
-      <c r="H21" s="156">
-        <v>350000</v>
+        <v>500500.15</v>
+      </c>
+      <c r="H21" s="61">
+        <f>G21</f>
+        <v>500500.15</v>
       </c>
       <c r="I21" s="62"/>
       <c r="J21" s="63">
         <f t="shared" si="2"/>
-        <v>-1845.8400000000256</v>
+        <v>0</v>
       </c>
       <c r="K21" s="63">
         <f t="shared" si="3"/>
@@ -4199,60 +4173,55 @@
       </c>
       <c r="L21" s="64">
         <f t="shared" si="4"/>
-        <v>31700</v>
+        <v>91000</v>
       </c>
       <c r="M21" s="64">
         <f t="shared" si="5"/>
-        <v>317000</v>
+        <v>455000</v>
       </c>
       <c r="N21" s="65">
         <v>0</v>
       </c>
       <c r="O21" s="66">
         <f t="shared" si="0"/>
-        <v>346854.16</v>
+        <v>546000.15</v>
       </c>
       <c r="P21" s="67">
         <f t="shared" si="1"/>
-        <v>357260.16</v>
+        <v>562380.15</v>
       </c>
       <c r="Q21" s="39">
         <f t="shared" si="6"/>
-        <v>0.16</v>
-      </c>
-      <c r="R21" t="s">
-        <v>148</v>
-      </c>
-      <c r="S21" s="38"/>
-    </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="54">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="55"/>
+        <v>109</v>
+      </c>
+      <c r="E22" s="54"/>
       <c r="F22" s="59">
-        <v>4.55</v>
-      </c>
-      <c r="G22" s="61">
-        <v>1015765.17</v>
-      </c>
-      <c r="H22" s="156">
-        <f>1046238.17</f>
-        <v>1046238.17</v>
+        <v>3.17</v>
+      </c>
+      <c r="G22" s="60">
+        <v>348154.16</v>
+      </c>
+      <c r="H22" s="61">
+        <v>350000</v>
       </c>
       <c r="I22" s="62"/>
       <c r="J22" s="63">
         <f t="shared" si="2"/>
-        <v>-30473</v>
+        <v>-1845.8400000000256</v>
       </c>
       <c r="K22" s="63">
         <f t="shared" si="3"/>
@@ -4260,56 +4229,60 @@
       </c>
       <c r="L22" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>63400</v>
       </c>
       <c r="M22" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>317000</v>
       </c>
       <c r="N22" s="65">
         <v>0</v>
       </c>
       <c r="O22" s="66">
         <f t="shared" si="0"/>
-        <v>470027.17</v>
+        <v>378554.16</v>
       </c>
       <c r="P22" s="67">
         <f t="shared" si="1"/>
-        <v>484128.17</v>
+        <v>389911.16</v>
       </c>
       <c r="Q22" s="39">
         <f t="shared" si="6"/>
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.16</v>
+      </c>
+      <c r="R22" t="s">
+        <v>147</v>
+      </c>
+      <c r="S22" s="38"/>
+    </row>
+    <row r="23" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="54">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D23" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="54"/>
+        <v>110</v>
+      </c>
+      <c r="E23" s="55"/>
       <c r="F23" s="59">
-        <v>3.17</v>
-      </c>
-      <c r="G23" s="60">
-        <v>348700.18</v>
-      </c>
-      <c r="H23" s="156">
-        <f>G23</f>
-        <v>348700.18</v>
+        <v>4.55</v>
+      </c>
+      <c r="G23" s="61">
+        <v>1015765.17</v>
+      </c>
+      <c r="H23" s="61">
+        <f>1046238.17</f>
+        <v>1046238.17</v>
       </c>
       <c r="I23" s="62"/>
       <c r="J23" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-30473</v>
       </c>
       <c r="K23" s="63">
         <f t="shared" si="3"/>
@@ -4317,51 +4290,51 @@
       </c>
       <c r="L23" s="64">
         <f t="shared" si="4"/>
-        <v>31700</v>
+        <v>91000</v>
       </c>
       <c r="M23" s="64">
         <f t="shared" si="5"/>
-        <v>317000</v>
+        <v>455000</v>
       </c>
       <c r="N23" s="65">
         <v>0</v>
       </c>
       <c r="O23" s="66">
         <f t="shared" si="0"/>
-        <v>348700.18</v>
+        <v>515527.17</v>
       </c>
       <c r="P23" s="67">
         <f t="shared" si="1"/>
-        <v>359161.18</v>
+        <v>530993.16999999993</v>
       </c>
       <c r="Q23" s="39">
         <f t="shared" si="6"/>
-        <v>0.18000000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="54">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="55"/>
+        <v>111</v>
+      </c>
+      <c r="E24" s="54"/>
       <c r="F24" s="59">
-        <v>4.55</v>
+        <v>3.17</v>
       </c>
       <c r="G24" s="60">
-        <v>500500.19</v>
-      </c>
-      <c r="H24" s="156">
+        <v>348700.18</v>
+      </c>
+      <c r="H24" s="61">
         <f>G24</f>
-        <v>500500.19</v>
+        <v>348700.18</v>
       </c>
       <c r="I24" s="62"/>
       <c r="J24" s="63">
@@ -4374,51 +4347,51 @@
       </c>
       <c r="L24" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>63400</v>
       </c>
       <c r="M24" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>317000</v>
       </c>
       <c r="N24" s="65">
         <v>0</v>
       </c>
       <c r="O24" s="66">
         <f t="shared" si="0"/>
-        <v>500500.19</v>
+        <v>380400.18</v>
       </c>
       <c r="P24" s="67">
         <f t="shared" si="1"/>
-        <v>515515.19</v>
+        <v>391812.18</v>
       </c>
       <c r="Q24" s="39">
         <f t="shared" si="6"/>
-        <v>0.19000000000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="54">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="54"/>
+        <v>112</v>
+      </c>
+      <c r="E25" s="55"/>
       <c r="F25" s="59">
-        <v>3.17</v>
-      </c>
-      <c r="G25" s="61">
-        <v>348700.2</v>
-      </c>
-      <c r="H25" s="156">
+        <v>4.55</v>
+      </c>
+      <c r="G25" s="60">
+        <v>500500.19</v>
+      </c>
+      <c r="H25" s="61">
         <f>G25</f>
-        <v>348700.2</v>
+        <v>500500.19</v>
       </c>
       <c r="I25" s="62"/>
       <c r="J25" s="63">
@@ -4431,54 +4404,51 @@
       </c>
       <c r="L25" s="64">
         <f t="shared" si="4"/>
-        <v>31700</v>
+        <v>91000</v>
       </c>
       <c r="M25" s="64">
         <f t="shared" si="5"/>
-        <v>317000</v>
+        <v>455000</v>
       </c>
       <c r="N25" s="65">
         <v>0</v>
       </c>
       <c r="O25" s="66">
         <f t="shared" si="0"/>
-        <v>348700.2</v>
+        <v>546000.18999999994</v>
       </c>
       <c r="P25" s="67">
         <f t="shared" si="1"/>
-        <v>359161.2</v>
+        <v>562380.18999999994</v>
       </c>
       <c r="Q25" s="39">
         <f t="shared" si="6"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="S25" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.19000000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="54">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="55"/>
+        <v>113</v>
+      </c>
+      <c r="E26" s="54"/>
       <c r="F26" s="59">
-        <v>4.55</v>
-      </c>
-      <c r="G26" s="60">
-        <v>500500.21</v>
-      </c>
-      <c r="H26" s="156">
+        <v>3.17</v>
+      </c>
+      <c r="G26" s="61">
+        <v>348700.2</v>
+      </c>
+      <c r="H26" s="61">
         <f>G26</f>
-        <v>500500.21</v>
+        <v>348700.2</v>
       </c>
       <c r="I26" s="62"/>
       <c r="J26" s="63">
@@ -4491,56 +4461,59 @@
       </c>
       <c r="L26" s="64">
         <f t="shared" si="4"/>
-        <v>45500</v>
+        <v>63400</v>
       </c>
       <c r="M26" s="64">
         <f t="shared" si="5"/>
-        <v>455000</v>
+        <v>317000</v>
       </c>
       <c r="N26" s="65">
         <v>0</v>
       </c>
       <c r="O26" s="66">
         <f t="shared" si="0"/>
-        <v>500500.21</v>
+        <v>380400.2</v>
       </c>
       <c r="P26" s="67">
         <f t="shared" si="1"/>
-        <v>515515.21</v>
+        <v>391812.2</v>
       </c>
       <c r="Q26" s="39">
         <f t="shared" si="6"/>
-        <v>0.21000000000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="S26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="54">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E27" s="55"/>
       <c r="F27" s="59">
-        <v>3.17</v>
+        <v>4.55</v>
       </c>
       <c r="G27" s="60">
-        <v>-168789.78</v>
-      </c>
-      <c r="H27" s="156">
-        <f>381870.22</f>
-        <v>381870.22</v>
+        <v>500500.21</v>
+      </c>
+      <c r="H27" s="61">
+        <f>G27</f>
+        <v>500500.21</v>
       </c>
       <c r="I27" s="62"/>
       <c r="J27" s="63">
         <f t="shared" si="2"/>
-        <v>-550660</v>
+        <v>0</v>
       </c>
       <c r="K27" s="63">
         <f t="shared" si="3"/>
@@ -4548,56 +4521,56 @@
       </c>
       <c r="L27" s="64">
         <f t="shared" si="4"/>
-        <v>31700</v>
+        <v>91000</v>
       </c>
       <c r="M27" s="64">
         <f t="shared" si="5"/>
-        <v>317000</v>
+        <v>455000</v>
       </c>
       <c r="N27" s="65">
         <v>0</v>
       </c>
       <c r="O27" s="66">
         <f t="shared" si="0"/>
-        <v>-201959.78</v>
+        <v>546000.21</v>
       </c>
       <c r="P27" s="67">
         <f t="shared" si="1"/>
-        <v>-208018.78</v>
+        <v>562380.21</v>
       </c>
       <c r="Q27" s="39">
         <f t="shared" si="6"/>
-        <v>0.22000000000000006</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.21000000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" s="55"/>
       <c r="F28" s="59">
-        <v>4.66</v>
+        <v>3.17</v>
       </c>
       <c r="G28" s="60">
-        <v>512600.23</v>
-      </c>
-      <c r="H28" s="156">
-        <f>G28</f>
-        <v>512600.23</v>
+        <v>-168789.78</v>
+      </c>
+      <c r="H28" s="61">
+        <f>381870.22</f>
+        <v>381870.22</v>
       </c>
       <c r="I28" s="62"/>
       <c r="J28" s="63">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-550660</v>
       </c>
       <c r="K28" s="63">
         <f t="shared" si="3"/>
@@ -4605,51 +4578,51 @@
       </c>
       <c r="L28" s="64">
         <f t="shared" si="4"/>
-        <v>46600</v>
+        <v>63400</v>
       </c>
       <c r="M28" s="64">
         <f t="shared" si="5"/>
-        <v>466000</v>
+        <v>317000</v>
       </c>
       <c r="N28" s="65">
         <v>0</v>
       </c>
       <c r="O28" s="66">
         <f t="shared" si="0"/>
-        <v>512600.23</v>
+        <v>-170259.78</v>
       </c>
       <c r="P28" s="67">
         <f t="shared" si="1"/>
-        <v>527978.23</v>
+        <v>-175367.78</v>
       </c>
       <c r="Q28" s="39">
         <f t="shared" si="6"/>
-        <v>0.23000000000000007</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.22000000000000006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="54">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="54" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E29" s="55"/>
       <c r="F29" s="59">
-        <v>3.21</v>
+        <v>4.66</v>
       </c>
       <c r="G29" s="60">
-        <v>353100.24</v>
-      </c>
-      <c r="H29" s="156">
+        <v>512600.23</v>
+      </c>
+      <c r="H29" s="61">
         <f>G29</f>
-        <v>353100.24</v>
+        <v>512600.23</v>
       </c>
       <c r="I29" s="62"/>
       <c r="J29" s="63">
@@ -4662,51 +4635,51 @@
       </c>
       <c r="L29" s="64">
         <f t="shared" si="4"/>
-        <v>32099.999999999996</v>
+        <v>93200</v>
       </c>
       <c r="M29" s="64">
         <f t="shared" si="5"/>
-        <v>320999.99999999994</v>
+        <v>466000</v>
       </c>
       <c r="N29" s="65">
         <v>0</v>
       </c>
       <c r="O29" s="66">
         <f t="shared" si="0"/>
-        <v>353100.24</v>
+        <v>559200.23</v>
       </c>
       <c r="P29" s="67">
         <f t="shared" si="1"/>
-        <v>363693.24</v>
+        <v>575976.23</v>
       </c>
       <c r="Q29" s="39">
         <f t="shared" si="6"/>
-        <v>0.24000000000000007</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.23000000000000007</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B30" s="54">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="54"/>
+        <v>117</v>
+      </c>
+      <c r="E30" s="55"/>
       <c r="F30" s="59">
-        <v>4.6900000000000004</v>
+        <v>3.21</v>
       </c>
       <c r="G30" s="60">
-        <v>500423.25</v>
-      </c>
-      <c r="H30" s="156">
+        <v>353100.24</v>
+      </c>
+      <c r="H30" s="61">
         <f>G30</f>
-        <v>500423.25</v>
+        <v>353100.24</v>
       </c>
       <c r="I30" s="62"/>
       <c r="J30" s="63">
@@ -4719,54 +4692,51 @@
       </c>
       <c r="L30" s="64">
         <f t="shared" si="4"/>
-        <v>46900.000000000007</v>
+        <v>64199.999999999993</v>
       </c>
       <c r="M30" s="64">
         <f t="shared" si="5"/>
-        <v>469000.00000000006</v>
+        <v>320999.99999999994</v>
       </c>
       <c r="N30" s="65">
         <v>0</v>
       </c>
       <c r="O30" s="66">
         <f t="shared" si="0"/>
-        <v>515900.25</v>
+        <v>385200.24</v>
       </c>
       <c r="P30" s="67">
         <f t="shared" si="1"/>
-        <v>531377.25</v>
+        <v>396756.24</v>
       </c>
       <c r="Q30" s="39">
         <f t="shared" si="6"/>
-        <v>0.25000000000000006</v>
-      </c>
-      <c r="R30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.24000000000000007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="54">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E31" s="54"/>
       <c r="F31" s="59">
-        <v>3.02</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="G31" s="60">
-        <v>363600.26</v>
-      </c>
-      <c r="H31" s="156">
+        <v>500423.25</v>
+      </c>
+      <c r="H31" s="61">
         <f>G31</f>
-        <v>363600.26</v>
+        <v>500423.25</v>
       </c>
       <c r="I31" s="62"/>
       <c r="J31" s="63">
@@ -4779,271 +4749,331 @@
       </c>
       <c r="L31" s="64">
         <f t="shared" si="4"/>
-        <v>30200</v>
+        <v>93800.000000000015</v>
       </c>
       <c r="M31" s="64">
         <f t="shared" si="5"/>
-        <v>302000</v>
+        <v>469000.00000000006</v>
       </c>
       <c r="N31" s="65">
-        <v>31400</v>
+        <v>0</v>
       </c>
       <c r="O31" s="66">
         <f t="shared" si="0"/>
-        <v>363600.26</v>
+        <v>562800.25</v>
       </c>
       <c r="P31" s="67">
         <f t="shared" si="1"/>
-        <v>374508.26</v>
-      </c>
-      <c r="Q31" s="111">
+        <v>579684.25</v>
+      </c>
+      <c r="Q31" s="39">
+        <f t="shared" si="6"/>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="R31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="54">
+        <v>26</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="54"/>
+      <c r="F32" s="59">
+        <v>3.02</v>
+      </c>
+      <c r="G32" s="60">
+        <v>363600.26</v>
+      </c>
+      <c r="H32" s="61">
+        <f>G32</f>
+        <v>363600.26</v>
+      </c>
+      <c r="I32" s="62"/>
+      <c r="J32" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="63">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="64">
+        <f t="shared" si="4"/>
+        <v>60400</v>
+      </c>
+      <c r="M32" s="64">
+        <f t="shared" si="5"/>
+        <v>302000</v>
+      </c>
+      <c r="N32" s="65">
+        <v>31400</v>
+      </c>
+      <c r="O32" s="66">
+        <f t="shared" si="0"/>
+        <v>393800.26</v>
+      </c>
+      <c r="P32" s="67">
+        <f t="shared" si="1"/>
+        <v>405614.26</v>
+      </c>
+      <c r="Q32" s="111">
         <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="116"/>
-      <c r="S31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="R32" s="116"/>
+      <c r="S32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="54">
+      <c r="B33" s="54">
         <v>27</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C33" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D33" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="E32" s="55"/>
-      <c r="F32" s="59">
+      <c r="E33" s="55"/>
+      <c r="F33" s="59">
         <v>0.16</v>
       </c>
-      <c r="G32" s="60">
+      <c r="G33" s="60">
         <v>17600.27</v>
       </c>
-      <c r="H32" s="156">
+      <c r="H33" s="61">
         <v>18128.27</v>
       </c>
-      <c r="I32" s="62"/>
-      <c r="J32" s="63">
-        <f>G32-H32</f>
+      <c r="I33" s="62"/>
+      <c r="J33" s="63">
+        <f>G33-H33</f>
         <v>-528</v>
       </c>
-      <c r="K32" s="63">
+      <c r="K33" s="63">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L32" s="64">
+      <c r="L33" s="64">
         <f t="shared" si="4"/>
-        <v>1600</v>
-      </c>
-      <c r="M32" s="64">
-        <f>O$2*F32%</f>
+        <v>3200</v>
+      </c>
+      <c r="M33" s="64">
+        <f>O$2*F33%</f>
         <v>16000</v>
       </c>
-      <c r="N32" s="65">
-        <v>0</v>
-      </c>
-      <c r="O32" s="66">
+      <c r="N33" s="65">
+        <v>0</v>
+      </c>
+      <c r="O33" s="66">
         <f t="shared" si="0"/>
-        <v>17072.27</v>
-      </c>
-      <c r="P32" s="67">
+        <v>18672.27</v>
+      </c>
+      <c r="P33" s="67">
         <f t="shared" si="1"/>
-        <v>17584.27</v>
-      </c>
-      <c r="Q32" s="39">
+        <v>19232.27</v>
+      </c>
+      <c r="Q33" s="39">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+    <row r="34" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="54"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="68" t="s">
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="H33" s="61" t="str">
-        <f t="shared" ref="H33" si="7">G33</f>
+      <c r="H34" s="61" t="str">
+        <f t="shared" ref="H34" si="7">G34</f>
         <v>162450.31</v>
       </c>
-      <c r="I33" s="69"/>
-      <c r="J33" s="70" t="e">
-        <f t="shared" ref="J33" si="8">G33-H33</f>
+      <c r="I34" s="69"/>
+      <c r="J34" s="70" t="e">
+        <f t="shared" ref="J34" si="8">G34-H34</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K33" s="63" t="e">
-        <f t="shared" ref="K33" si="9">IF(J33&gt;0,J33*3%,0)</f>
+      <c r="K34" s="63" t="e">
+        <f t="shared" ref="K34" si="9">IF(J34&gt;0,J34*3%,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L33" s="64">
+      <c r="L34" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M33" s="71">
+      <c r="M34" s="71">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N33" s="72">
-        <v>0</v>
-      </c>
-      <c r="O33" s="66" t="e">
+      <c r="N34" s="72">
+        <v>0</v>
+      </c>
+      <c r="O34" s="66" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="P33" s="67" t="e">
+      <c r="P34" s="67" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Q33" s="39"/>
-    </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="73"/>
-      <c r="C34" s="74"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76">
-        <f>SUM(F6:F33)</f>
+      <c r="Q34" s="39"/>
+    </row>
+    <row r="35" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="73"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76">
+        <f>SUM(F6:F34)</f>
         <v>99.999999999999972</v>
       </c>
-      <c r="G34" s="45">
-        <f>SUM(G6:G33)</f>
-        <v>12452477.779999999</v>
-      </c>
-      <c r="H34" s="52">
-        <f>SUM(H6:H33)</f>
-        <v>11998798.140000001</v>
-      </c>
-      <c r="I34" s="52">
-        <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52">
-        <f>SUM(L6:L33)</f>
-        <v>1000000</v>
-      </c>
-      <c r="M34" s="52">
-        <f>SUM(M6:M33)</f>
+      <c r="G35" s="45">
+        <f>SUM(G6:G34)</f>
+        <v>12852477.779999999</v>
+      </c>
+      <c r="H35" s="52">
+        <f>SUM(H6:H34)</f>
+        <v>12003298.140000001</v>
+      </c>
+      <c r="I35" s="52">
+        <f t="shared" ref="I35" si="10">SUM(I6:I34)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52">
+        <f>SUM(L6:L34)</f>
+        <v>2000000</v>
+      </c>
+      <c r="M35" s="52">
+        <f>SUM(M6:M34)</f>
         <v>10000000</v>
       </c>
-      <c r="N34" s="52">
-        <f>SUM(N6:N33)</f>
+      <c r="N35" s="52">
+        <f>SUM(N6:N34)</f>
         <v>31400</v>
       </c>
-      <c r="O34" s="77">
-        <f>SUM(O6:O32)</f>
-        <v>11517185.780000001</v>
-      </c>
-      <c r="P34" s="77">
-        <f>SUM(P6:P32)</f>
-        <v>11862701.780000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-    </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="181" t="s">
-        <v>146</v>
-      </c>
-      <c r="E37" s="181"/>
-      <c r="F37" s="181"/>
-      <c r="G37" s="181"/>
-      <c r="H37" s="181"/>
-      <c r="I37" s="181"/>
-      <c r="J37" s="181"/>
-      <c r="K37" s="181"/>
-      <c r="L37" s="181"/>
-      <c r="M37" s="181"/>
-      <c r="N37" s="181"/>
-      <c r="O37" s="181"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="181"/>
-      <c r="E38" s="181"/>
-      <c r="F38" s="181"/>
-      <c r="G38" s="181"/>
-      <c r="H38" s="181"/>
-      <c r="I38" s="181"/>
-      <c r="J38" s="181"/>
-      <c r="K38" s="181"/>
-      <c r="L38" s="181"/>
-      <c r="M38" s="181"/>
-      <c r="N38" s="181"/>
-      <c r="O38" s="181"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="181"/>
-      <c r="E39" s="181"/>
-      <c r="F39" s="181"/>
-      <c r="G39" s="181"/>
-      <c r="H39" s="181"/>
-      <c r="I39" s="181"/>
-      <c r="J39" s="181"/>
-      <c r="K39" s="181"/>
-      <c r="L39" s="181"/>
-      <c r="M39" s="181"/>
-      <c r="N39" s="181"/>
-      <c r="O39" s="181"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="181"/>
-      <c r="E40" s="181"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="181"/>
-      <c r="H40" s="181"/>
-      <c r="I40" s="181"/>
-      <c r="J40" s="181"/>
-      <c r="K40" s="181"/>
-      <c r="L40" s="181"/>
-      <c r="M40" s="181"/>
-      <c r="N40" s="181"/>
-      <c r="O40" s="181"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="181"/>
-      <c r="E41" s="181"/>
-      <c r="F41" s="181"/>
-      <c r="G41" s="181"/>
-      <c r="H41" s="181"/>
-      <c r="I41" s="181"/>
-      <c r="J41" s="181"/>
-      <c r="K41" s="181"/>
-      <c r="L41" s="181"/>
-      <c r="M41" s="181"/>
-      <c r="N41" s="181"/>
-      <c r="O41" s="181"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="181"/>
-      <c r="E42" s="181"/>
-      <c r="F42" s="181"/>
-      <c r="G42" s="181"/>
-      <c r="H42" s="181"/>
-      <c r="I42" s="181"/>
-      <c r="J42" s="181"/>
-      <c r="K42" s="181"/>
-      <c r="L42" s="181"/>
-      <c r="M42" s="181"/>
-      <c r="N42" s="181"/>
-      <c r="O42" s="181"/>
+      <c r="O35" s="77">
+        <f>SUM(O6:O33)</f>
+        <v>12924353.779999999</v>
+      </c>
+      <c r="P35" s="77">
+        <f>SUM(P6:P33)</f>
+        <v>13312084.779999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+    </row>
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D38" s="177" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="177"/>
+      <c r="I38" s="177"/>
+      <c r="J38" s="177"/>
+      <c r="K38" s="177"/>
+      <c r="L38" s="177"/>
+      <c r="M38" s="177"/>
+      <c r="N38" s="177"/>
+      <c r="O38" s="177"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D39" s="177"/>
+      <c r="E39" s="177"/>
+      <c r="F39" s="177"/>
+      <c r="G39" s="177"/>
+      <c r="H39" s="177"/>
+      <c r="I39" s="177"/>
+      <c r="J39" s="177"/>
+      <c r="K39" s="177"/>
+      <c r="L39" s="177"/>
+      <c r="M39" s="177"/>
+      <c r="N39" s="177"/>
+      <c r="O39" s="177"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D40" s="177"/>
+      <c r="E40" s="177"/>
+      <c r="F40" s="177"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="177"/>
+      <c r="I40" s="177"/>
+      <c r="J40" s="177"/>
+      <c r="K40" s="177"/>
+      <c r="L40" s="177"/>
+      <c r="M40" s="177"/>
+      <c r="N40" s="177"/>
+      <c r="O40" s="177"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D41" s="177"/>
+      <c r="E41" s="177"/>
+      <c r="F41" s="177"/>
+      <c r="G41" s="177"/>
+      <c r="H41" s="177"/>
+      <c r="I41" s="177"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="177"/>
+      <c r="L41" s="177"/>
+      <c r="M41" s="177"/>
+      <c r="N41" s="177"/>
+      <c r="O41" s="177"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D42" s="177"/>
+      <c r="E42" s="177"/>
+      <c r="F42" s="177"/>
+      <c r="G42" s="177"/>
+      <c r="H42" s="177"/>
+      <c r="I42" s="177"/>
+      <c r="J42" s="177"/>
+      <c r="K42" s="177"/>
+      <c r="L42" s="177"/>
+      <c r="M42" s="177"/>
+      <c r="N42" s="177"/>
+      <c r="O42" s="177"/>
+    </row>
+    <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D43" s="177"/>
+      <c r="E43" s="177"/>
+      <c r="F43" s="177"/>
+      <c r="G43" s="177"/>
+      <c r="H43" s="177"/>
+      <c r="I43" s="177"/>
+      <c r="J43" s="177"/>
+      <c r="K43" s="177"/>
+      <c r="L43" s="177"/>
+      <c r="M43" s="177"/>
+      <c r="N43" s="177"/>
+      <c r="O43" s="177"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
@@ -5051,7 +5081,7 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
-    <mergeCell ref="D37:O42"/>
+    <mergeCell ref="D38:O43"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="K4:K5"/>
@@ -5061,6 +5091,7 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5070,16 +5101,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C3:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="149" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="150" t="s">
-        <v>159</v>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C3" s="148" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C6" s="149" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7C1E63-AE58-4620-8082-6766F71134F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316AD445-8239-4C73-BA82-243C79FCBBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -21,25 +21,17 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$133</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="187">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -413,13 +405,6 @@
     <t>TELEFONO : 11-5320-2676 - MAIL: colombres360@gmail.com - OFICINA CON CITA PREVIA - DR MELO 2958 8° PISO</t>
   </si>
   <si>
-    <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360
-Banco: SUPERVIELLE
-C.U.I.T.   30-71003865-8
-CBU: 02700151 10040979780018
-Nº de cuenta: 04097978-001</t>
-  </si>
-  <si>
     <t xml:space="preserve">METROGAS - Cliente 30008873781 </t>
   </si>
   <si>
@@ -475,9 +460,6 @@
   </si>
   <si>
     <t>MAGRO LAUTARO - MAGRO DANIELA</t>
-  </si>
-  <si>
-    <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360 Banco: SUPERVIELLE Sucursal: Lomas de Zamora CBU: 02700151 10040979780018 Nº de cuenta: 04097978-001 Código de Pago Electrónico: abonar con los centavos de la UF</t>
   </si>
   <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
@@ -608,6 +590,13 @@
   </si>
   <si>
     <t>2-A - MAGRO LAUTARO - MAGRO DANIELA - CUOTA 1/6 PLAN DE PAGOS</t>
+  </si>
+  <si>
+    <t>Banco Santander
+Tipo de cuenta: Cuenta corriente en pesos
+Número de cuenta: 039-0234504
+CBU: 0720039720000002345040
+Alias: ALFA.CETRO.AMOROSAS</t>
   </si>
 </sst>
 </file>
@@ -615,11 +604,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -1250,8 +1239,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1261,21 +1250,21 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1283,40 +1272,40 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1327,68 +1316,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1399,7 +1388,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1413,15 +1402,15 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1434,17 +1423,17 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="12" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="12" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="12" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,7 +1443,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1469,22 +1458,68 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1494,53 +1529,26 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1554,9 +1562,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1566,9 +1571,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1593,25 +1595,12 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1677,9 +1666,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1717,9 +1706,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1752,9 +1741,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1787,9 +1793,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1964,19 +1987,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L137"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.6328125" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
         <v>122</v>
       </c>
@@ -1984,7 +2007,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="109" t="s">
         <v>123</v>
       </c>
@@ -1992,84 +2015,84 @@
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
     </row>
-    <row r="3" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="109" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="168" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="168"/>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="204" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="204"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="168"/>
-      <c r="B5" s="168"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="204"/>
+      <c r="B5" s="204"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="168"/>
-      <c r="B6" s="168"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="204"/>
+      <c r="B6" s="204"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="168"/>
-      <c r="B7" s="168"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="204"/>
+      <c r="B7" s="204"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="165" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="165"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="165"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="169" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="181" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="181"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="181"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="182" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="169"/>
-      <c r="C14" s="169"/>
-      <c r="D14" s="169"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="169"/>
-      <c r="B15" s="169"/>
-      <c r="C15" s="169"/>
-      <c r="D15" s="169"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="169"/>
-      <c r="B16" s="169"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="169"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="169"/>
-      <c r="B17" s="169"/>
-      <c r="C17" s="169"/>
-      <c r="D17" s="169"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="182"/>
+      <c r="C14" s="182"/>
+      <c r="D14" s="182"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="182"/>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="182"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="182"/>
+      <c r="B17" s="182"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2100,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>80</v>
       </c>
@@ -2085,12 +2108,12 @@
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C23" s="137">
         <v>1497939.7</v>
@@ -2098,7 +2121,7 @@
       <c r="D23" s="80"/>
       <c r="G23" s="160"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
@@ -2108,7 +2131,7 @@
       </c>
       <c r="D24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -2119,9 +2142,9 @@
       <c r="D25" s="80"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="137">
@@ -2130,7 +2153,7 @@
       <c r="D26" s="80"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="s">
         <v>82</v>
       </c>
@@ -2142,12 +2165,12 @@
       <c r="D27" s="47"/>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C28" s="137">
         <v>1232039.3</v>
@@ -2155,7 +2178,7 @@
       <c r="D28" s="80"/>
       <c r="G28" s="14"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
@@ -2166,7 +2189,7 @@
       <c r="D29" s="80"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -2177,9 +2200,9 @@
       <c r="D30" s="80"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="151">
@@ -2188,7 +2211,7 @@
       <c r="D31" s="80"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
         <v>82</v>
       </c>
@@ -2198,22 +2221,22 @@
         <v>1598022.7</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="163"/>
-      <c r="G32" s="164"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F32" s="179"/>
+      <c r="G32" s="180"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C33" s="137">
         <v>554812.06999999995</v>
       </c>
       <c r="D33" s="113"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
@@ -2223,7 +2246,7 @@
       </c>
       <c r="D34" s="113"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
@@ -2233,13 +2256,13 @@
       </c>
       <c r="D35" s="113"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="151"/>
       <c r="D36" s="113"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
         <v>82</v>
       </c>
@@ -2250,19 +2273,19 @@
       </c>
       <c r="D37" s="81"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C38" s="137">
         <v>1578850.12</v>
       </c>
       <c r="D38" s="80"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>84</v>
       </c>
@@ -2272,7 +2295,7 @@
       </c>
       <c r="D39" s="80"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>83</v>
       </c>
@@ -2283,13 +2306,13 @@
       <c r="D40" s="80"/>
       <c r="G40" s="160"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="137"/>
       <c r="D41" s="80"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
         <v>82</v>
       </c>
@@ -2300,19 +2323,19 @@
       </c>
       <c r="D42" s="47"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C43" s="137">
         <v>1433185.66</v>
       </c>
       <c r="D43" s="113"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
@@ -2322,7 +2345,7 @@
       </c>
       <c r="D44" s="113"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>83</v>
       </c>
@@ -2332,13 +2355,13 @@
       </c>
       <c r="D45" s="113"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="151"/>
       <c r="D46" s="113"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
         <v>82</v>
       </c>
@@ -2349,19 +2372,19 @@
       </c>
       <c r="D47" s="81"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C48" s="137">
         <v>1388921.91</v>
       </c>
       <c r="D48" s="113"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>81</v>
       </c>
@@ -2371,7 +2394,7 @@
       </c>
       <c r="D49" s="113"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>83</v>
       </c>
@@ -2381,13 +2404,13 @@
       </c>
       <c r="D50" s="113"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="151"/>
       <c r="D51" s="113"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
         <v>82</v>
       </c>
@@ -2398,7 +2421,7 @@
       </c>
       <c r="D52" s="81"/>
     </row>
-    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="18" t="s">
         <v>0</v>
       </c>
@@ -2411,7 +2434,7 @@
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>38</v>
       </c>
@@ -2420,7 +2443,7 @@
       <c r="D54" s="83"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="56" t="s">
         <v>39</v>
       </c>
@@ -2429,26 +2452,26 @@
         <v>135000</v>
       </c>
       <c r="D55" s="124" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="115" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B56" s="107" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C56" s="137">
         <v>211800</v>
       </c>
       <c r="D56" s="124" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
         <v>34</v>
       </c>
@@ -2459,7 +2482,7 @@
         <v>346800</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
         <v>77</v>
       </c>
@@ -2467,29 +2490,29 @@
       <c r="C58" s="28"/>
       <c r="D58" s="57"/>
     </row>
-    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="166" t="s">
-        <v>185</v>
-      </c>
-      <c r="B59" s="167"/>
-      <c r="C59" s="203">
+    <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="175" t="s">
+        <v>183</v>
+      </c>
+      <c r="B59" s="176"/>
+      <c r="C59" s="163">
         <v>10864.97</v>
       </c>
       <c r="D59" s="161" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="166" t="s">
-        <v>127</v>
-      </c>
-      <c r="B60" s="167"/>
-      <c r="C60" s="204">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="175" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="176"/>
+      <c r="C60" s="164">
         <v>4203</v>
       </c>
       <c r="D60" s="123"/>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="25" t="s">
         <v>1</v>
       </c>
@@ -2500,7 +2523,7 @@
         <v>15067.97</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
         <v>35</v>
       </c>
@@ -2508,41 +2531,41 @@
       <c r="C62" s="31"/>
       <c r="D62" s="85"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="80" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B63" s="80" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C63" s="138">
         <v>1421002.83</v>
       </c>
       <c r="D63" s="120" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F63" s="116"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="80" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B64" s="80" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C64" s="144">
         <v>16423.96</v>
       </c>
       <c r="D64" s="123" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="80" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B65" s="80" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C65" s="144">
         <v>147815.6</v>
@@ -2552,12 +2575,12 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="80" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C66" s="144">
         <v>399207.23</v>
@@ -2567,7 +2590,7 @@
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
         <v>2</v>
       </c>
@@ -2578,7 +2601,7 @@
         <v>1984449.62</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
         <v>37</v>
       </c>
@@ -2586,65 +2609,65 @@
       <c r="C68" s="31"/>
       <c r="D68" s="85"/>
     </row>
-    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B69" s="80"/>
       <c r="C69" s="144">
         <v>554680.11</v>
       </c>
       <c r="D69" s="120" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B70" s="80"/>
       <c r="C70" s="144"/>
       <c r="D70" s="120"/>
     </row>
-    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B71" s="80"/>
       <c r="C71" s="144">
         <v>20460.259999999998</v>
       </c>
       <c r="D71" s="120" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B72" s="80"/>
       <c r="C72" s="144">
         <v>864000.26</v>
       </c>
       <c r="D72" s="120" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="175" t="s">
-        <v>160</v>
-      </c>
-      <c r="B73" s="176"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="177" t="s">
+        <v>158</v>
+      </c>
+      <c r="B73" s="178"/>
       <c r="C73" s="144">
         <v>204149</v>
       </c>
       <c r="D73" s="120" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="173" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B74" s="174"/>
       <c r="C74" s="144">
@@ -2652,19 +2675,19 @@
       </c>
       <c r="D74" s="122"/>
     </row>
-    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="167"/>
+    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="175" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="176"/>
       <c r="C75" s="144">
         <v>35200</v>
       </c>
       <c r="D75" s="122" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="25" t="s">
         <v>3</v>
       </c>
@@ -2675,7 +2698,7 @@
         <v>1678489.63</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>36</v>
       </c>
@@ -2683,71 +2706,71 @@
       <c r="C77" s="30"/>
       <c r="D77" s="87"/>
     </row>
-    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="146" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B78" s="145"/>
       <c r="C78" s="144">
         <v>51919.14</v>
       </c>
       <c r="D78" s="118" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="166" t="s">
-        <v>165</v>
-      </c>
-      <c r="B79" s="167"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="175" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="176"/>
       <c r="C79" s="144">
         <v>753830.53</v>
       </c>
       <c r="D79" s="120" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="150" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="144">
         <v>10000</v>
       </c>
       <c r="D80" s="141" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="150" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B81" s="142"/>
       <c r="C81" s="144">
         <v>8760.52</v>
       </c>
       <c r="D81" s="122" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="166" t="s">
-        <v>164</v>
-      </c>
-      <c r="B82" s="167"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="175" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="176"/>
       <c r="C82" s="144">
         <v>34000</v>
       </c>
       <c r="D82" s="122" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E82" s="39"/>
       <c r="F82" s="39"/>
     </row>
-    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="173" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B83" s="174"/>
       <c r="C83" s="138">
@@ -2755,7 +2778,7 @@
       </c>
       <c r="D83" s="122"/>
     </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="25" t="s">
         <v>11</v>
       </c>
@@ -2766,7 +2789,7 @@
         <v>858510.19000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="s">
         <v>29</v>
       </c>
@@ -2774,9 +2797,9 @@
       <c r="C85" s="19"/>
       <c r="D85" s="87"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B86" s="80"/>
       <c r="C86" s="144">
@@ -2784,9 +2807,9 @@
       </c>
       <c r="D86" s="91"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="80" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B87" s="80"/>
       <c r="C87" s="144">
@@ -2795,7 +2818,7 @@
       </c>
       <c r="D87" s="89"/>
     </row>
-    <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="44" t="s">
         <v>34</v>
       </c>
@@ -2806,15 +2829,15 @@
         <v>214657.33000000002</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="80"/>
       <c r="D89" s="93"/>
     </row>
-    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="170" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B90" s="171"/>
       <c r="C90" s="172"/>
@@ -2823,13 +2846,13 @@
         <v>1296570.1500000004</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="C91" s="95"/>
       <c r="D91" s="96"/>
       <c r="E91" s="39"/>
     </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>30</v>
       </c>
@@ -2842,16 +2865,16 @@
       <c r="E92" s="39"/>
       <c r="F92" s="39"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C93" s="95"/>
       <c r="D93" s="95"/>
       <c r="F93" s="117"/>
     </row>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C94" s="95"/>
       <c r="D94" s="95"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>40</v>
       </c>
@@ -2859,25 +2882,25 @@
       <c r="C95" s="99"/>
       <c r="D95" s="100"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="180"/>
-      <c r="B96" s="181"/>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="168"/>
+      <c r="B96" s="169"/>
       <c r="C96" s="88"/>
       <c r="D96" s="86"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="180"/>
-      <c r="B97" s="181"/>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="168"/>
+      <c r="B97" s="169"/>
       <c r="C97" s="88"/>
       <c r="D97" s="86"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="103"/>
       <c r="B98" s="104"/>
       <c r="C98" s="88"/>
       <c r="D98" s="86"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="42"/>
       <c r="B99" s="41"/>
       <c r="C99" s="49"/>
@@ -2886,9 +2909,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="20" t="s">
         <v>41</v>
       </c>
@@ -2898,8 +2921,8 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>42</v>
       </c>
@@ -2910,8 +2933,8 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="78" t="s">
         <v>31</v>
       </c>
@@ -2921,7 +2944,7 @@
       </c>
       <c r="C106" s="39"/>
     </row>
-    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="78" t="s">
         <v>32</v>
       </c>
@@ -2930,7 +2953,7 @@
         <v>11408130.439999998</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="78" t="s">
         <v>43</v>
       </c>
@@ -2939,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="78" t="s">
         <v>88</v>
       </c>
@@ -2948,33 +2971,33 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" s="179" t="s">
-        <v>162</v>
-      </c>
-      <c r="B112" s="179"/>
-      <c r="C112" s="179"/>
-      <c r="D112" s="179"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" s="179"/>
-      <c r="B113" s="179"/>
-      <c r="C113" s="179"/>
-      <c r="D113" s="179"/>
-    </row>
-    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="179"/>
-      <c r="B114" s="179"/>
-      <c r="C114" s="179"/>
-      <c r="D114" s="179"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="167" t="s">
+        <v>160</v>
+      </c>
+      <c r="B112" s="167"/>
+      <c r="C112" s="167"/>
+      <c r="D112" s="167"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="167"/>
+      <c r="B113" s="167"/>
+      <c r="C113" s="167"/>
+      <c r="D113" s="167"/>
+    </row>
+    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="167"/>
+      <c r="B114" s="167"/>
+      <c r="C114" s="167"/>
+      <c r="D114" s="167"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="15" t="s">
         <v>79</v>
       </c>
       <c r="B116" s="35"/>
     </row>
-    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="23" t="s">
         <v>33</v>
       </c>
@@ -2982,7 +3005,7 @@
         <v>7139335.7599999998</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
         <v>91</v>
       </c>
@@ -2991,7 +3014,7 @@
         <v>12003298.140000001</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
         <v>90</v>
       </c>
@@ -3000,31 +3023,31 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B120" s="119">
         <v>-10167</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B121" s="119">
         <v>-240000</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B122" s="119">
         <v>-260000</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="34" t="s">
         <v>44</v>
       </c>
@@ -3033,7 +3056,7 @@
         <v>-11408130.439999998</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
         <v>45</v>
       </c>
@@ -3042,7 +3065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="22" t="s">
         <v>11</v>
       </c>
@@ -3051,37 +3074,37 @@
         <v>7724336.4600000009</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="37"/>
       <c r="C126" s="39"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" s="178" t="s">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="166" t="s">
         <v>78</v>
       </c>
-      <c r="B128" s="178"/>
-    </row>
-    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="178"/>
-      <c r="B129" s="178"/>
-    </row>
-    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B128" s="166"/>
+    </row>
+    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="166"/>
+      <c r="B129" s="166"/>
+    </row>
+    <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="101" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B130" s="29">
         <v>240000</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="101" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B131" s="29">
         <v>260000</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="40" t="s">
         <v>11</v>
       </c>
@@ -3090,40 +3113,41 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L133" s="8"/>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="177"/>
-      <c r="B134" s="177"/>
-      <c r="C134" s="177"/>
-      <c r="D134" s="177"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A135" s="177"/>
-      <c r="B135" s="177"/>
-      <c r="C135" s="177"/>
-      <c r="D135" s="177"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A136" s="177"/>
-      <c r="B136" s="177"/>
-      <c r="C136" s="177"/>
-      <c r="D136" s="177"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A137" s="177"/>
-      <c r="B137" s="177"/>
-      <c r="C137" s="177"/>
-      <c r="D137" s="177"/>
+    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="165"/>
+      <c r="B134" s="165"/>
+      <c r="C134" s="165"/>
+      <c r="D134" s="165"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" s="165"/>
+      <c r="B135" s="165"/>
+      <c r="C135" s="165"/>
+      <c r="D135" s="165"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" s="165"/>
+      <c r="B136" s="165"/>
+      <c r="C136" s="165"/>
+      <c r="D136" s="165"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" s="165"/>
+      <c r="B137" s="165"/>
+      <c r="C137" s="165"/>
+      <c r="D137" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A134:D137"/>
-    <mergeCell ref="A128:B129"/>
-    <mergeCell ref="A112:D114"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A14:D17"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A82:B82"/>
@@ -3131,12 +3155,11 @@
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A75:B75"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A134:D137"/>
+    <mergeCell ref="A128:B129"/>
+    <mergeCell ref="A112:D114"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3147,61 +3170,66 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.54296875" customWidth="1"/>
-    <col min="3" max="3" width="4.36328125" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="5" max="5" width="9.08984375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6328125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" customWidth="1"/>
-    <col min="11" max="11" width="11.08984375" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" customWidth="1"/>
-    <col min="14" max="14" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.36328125" customWidth="1"/>
-    <col min="16" max="16" width="14.08984375" customWidth="1"/>
-    <col min="17" max="17" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="182" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
+      <c r="B1" s="189" t="str">
+        <f>RESUMEN!A4</f>
+        <v>Banco Santander
+Tipo de cuenta: Cuenta corriente en pesos
+Número de cuenta: 039-0234504
+CBU: 0720039720000002345040
+Alias: ALFA.CETRO.AMOROSAS</v>
+      </c>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+      <c r="J1" s="189"/>
+      <c r="K1" s="189"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
+      <c r="K2" s="189"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3213,18 +3241,18 @@
       <c r="P2" s="46"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="183"/>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3235,79 +3263,79 @@
       </c>
       <c r="P3" s="50"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="199" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="201" t="s">
+      <c r="B4" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="186" t="s">
+      <c r="C4" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="186" t="s">
+      <c r="D4" s="187" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="186" t="s">
+      <c r="E4" s="187" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="186" t="s">
+      <c r="F4" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="186" t="s">
+      <c r="G4" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="186" t="s">
+      <c r="H4" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="186" t="s">
+      <c r="I4" s="187" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="191" t="s">
+      <c r="J4" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="188" t="s">
+      <c r="K4" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="188" t="s">
+      <c r="L4" s="194" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="188" t="s">
+      <c r="M4" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="194" t="s">
+      <c r="N4" s="199" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="184" t="s">
+      <c r="P4" s="191" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="200"/>
-      <c r="B5" s="202"/>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="187"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="190"/>
-      <c r="I5" s="187"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="193"/>
-      <c r="M5" s="189"/>
-      <c r="N5" s="195"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="184"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="197"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="195"/>
+      <c r="N5" s="200"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="185"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P5" s="192"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3363,7 +3391,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3420,10 +3448,10 @@
         <v>0.02</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3434,7 +3462,7 @@
         <v>53</v>
       </c>
       <c r="D8" s="127" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E8" s="128"/>
       <c r="F8" s="129">
@@ -3479,13 +3507,13 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="196" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
+      <c r="B9" s="201" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="202"/>
+      <c r="D9" s="203"/>
       <c r="E9" s="128"/>
       <c r="F9" s="129"/>
       <c r="G9" s="130">
@@ -3504,7 +3532,7 @@
       <c r="P9" s="136"/>
       <c r="Q9" s="39"/>
     </row>
-    <row r="10" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3560,11 +3588,11 @@
         <v>0.04</v>
       </c>
       <c r="R10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S10" s="39"/>
     </row>
-    <row r="11" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -3619,7 +3647,7 @@
       </c>
       <c r="S11" s="39"/>
     </row>
-    <row r="12" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -3676,7 +3704,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -3735,7 +3763,7 @@
       <c r="R13" s="117"/>
       <c r="S13" s="116"/>
     </row>
-    <row r="14" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3791,7 +3819,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -3847,10 +3875,10 @@
         <v>0.09</v>
       </c>
       <c r="R15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3907,10 +3935,10 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
@@ -3967,7 +3995,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -4024,7 +4052,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -4081,7 +4109,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -4138,7 +4166,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
@@ -4195,7 +4223,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4251,11 +4279,11 @@
         <v>0.16</v>
       </c>
       <c r="R22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="S22" s="38"/>
     </row>
-    <row r="23" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>20</v>
       </c>
@@ -4312,7 +4340,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4369,7 +4397,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
@@ -4426,7 +4454,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
@@ -4483,10 +4511,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="S26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
@@ -4543,7 +4571,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
@@ -4600,7 +4628,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
@@ -4657,7 +4685,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4714,7 +4742,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4771,10 +4799,10 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="R31" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4832,10 +4860,10 @@
       </c>
       <c r="R32" s="116"/>
       <c r="S32" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4891,7 +4919,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>27</v>
       </c>
@@ -4937,7 +4965,7 @@
       </c>
       <c r="Q34" s="39"/>
     </row>
-    <row r="35" spans="1:17" ht="17.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="73"/>
       <c r="C35" s="74"/>
       <c r="D35" s="75"/>
@@ -4981,104 +5009,99 @@
         <v>13312084.779999999</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="43"/>
       <c r="E36" s="43"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="177" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="177"/>
-      <c r="F38" s="177"/>
-      <c r="G38" s="177"/>
-      <c r="H38" s="177"/>
-      <c r="I38" s="177"/>
-      <c r="J38" s="177"/>
-      <c r="K38" s="177"/>
-      <c r="L38" s="177"/>
-      <c r="M38" s="177"/>
-      <c r="N38" s="177"/>
-      <c r="O38" s="177"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D39" s="177"/>
-      <c r="E39" s="177"/>
-      <c r="F39" s="177"/>
-      <c r="G39" s="177"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="177"/>
-      <c r="J39" s="177"/>
-      <c r="K39" s="177"/>
-      <c r="L39" s="177"/>
-      <c r="M39" s="177"/>
-      <c r="N39" s="177"/>
-      <c r="O39" s="177"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="177"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="177"/>
-      <c r="G40" s="177"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="177"/>
-      <c r="J40" s="177"/>
-      <c r="K40" s="177"/>
-      <c r="L40" s="177"/>
-      <c r="M40" s="177"/>
-      <c r="N40" s="177"/>
-      <c r="O40" s="177"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D41" s="177"/>
-      <c r="E41" s="177"/>
-      <c r="F41" s="177"/>
-      <c r="G41" s="177"/>
-      <c r="H41" s="177"/>
-      <c r="I41" s="177"/>
-      <c r="J41" s="177"/>
-      <c r="K41" s="177"/>
-      <c r="L41" s="177"/>
-      <c r="M41" s="177"/>
-      <c r="N41" s="177"/>
-      <c r="O41" s="177"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="177"/>
-      <c r="E42" s="177"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="177"/>
-      <c r="H42" s="177"/>
-      <c r="I42" s="177"/>
-      <c r="J42" s="177"/>
-      <c r="K42" s="177"/>
-      <c r="L42" s="177"/>
-      <c r="M42" s="177"/>
-      <c r="N42" s="177"/>
-      <c r="O42" s="177"/>
-    </row>
-    <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="177"/>
-      <c r="E43" s="177"/>
-      <c r="F43" s="177"/>
-      <c r="G43" s="177"/>
-      <c r="H43" s="177"/>
-      <c r="I43" s="177"/>
-      <c r="J43" s="177"/>
-      <c r="K43" s="177"/>
-      <c r="L43" s="177"/>
-      <c r="M43" s="177"/>
-      <c r="N43" s="177"/>
-      <c r="O43" s="177"/>
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="165" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="165"/>
+      <c r="F38" s="165"/>
+      <c r="G38" s="165"/>
+      <c r="H38" s="165"/>
+      <c r="I38" s="165"/>
+      <c r="J38" s="165"/>
+      <c r="K38" s="165"/>
+      <c r="L38" s="165"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="165"/>
+      <c r="O38" s="165"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="165"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="165"/>
+      <c r="G39" s="165"/>
+      <c r="H39" s="165"/>
+      <c r="I39" s="165"/>
+      <c r="J39" s="165"/>
+      <c r="K39" s="165"/>
+      <c r="L39" s="165"/>
+      <c r="M39" s="165"/>
+      <c r="N39" s="165"/>
+      <c r="O39" s="165"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="165"/>
+      <c r="E40" s="165"/>
+      <c r="F40" s="165"/>
+      <c r="G40" s="165"/>
+      <c r="H40" s="165"/>
+      <c r="I40" s="165"/>
+      <c r="J40" s="165"/>
+      <c r="K40" s="165"/>
+      <c r="L40" s="165"/>
+      <c r="M40" s="165"/>
+      <c r="N40" s="165"/>
+      <c r="O40" s="165"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="165"/>
+      <c r="E41" s="165"/>
+      <c r="F41" s="165"/>
+      <c r="G41" s="165"/>
+      <c r="H41" s="165"/>
+      <c r="I41" s="165"/>
+      <c r="J41" s="165"/>
+      <c r="K41" s="165"/>
+      <c r="L41" s="165"/>
+      <c r="M41" s="165"/>
+      <c r="N41" s="165"/>
+      <c r="O41" s="165"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="165"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="165"/>
+      <c r="I42" s="165"/>
+      <c r="J42" s="165"/>
+      <c r="K42" s="165"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+    </row>
+    <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" s="165"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="165"/>
+      <c r="G43" s="165"/>
+      <c r="H43" s="165"/>
+      <c r="I43" s="165"/>
+      <c r="J43" s="165"/>
+      <c r="K43" s="165"/>
+      <c r="L43" s="165"/>
+      <c r="M43" s="165"/>
+      <c r="N43" s="165"/>
+      <c r="O43" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D38:O43"/>
@@ -5092,6 +5115,11 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -5101,16 +5129,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
   <dimension ref="C3:C6"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" s="148" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" s="149" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
+++ b/2026/COLOMBRES/Febrero/Febrero COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\COLOMBRES\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316AD445-8239-4C73-BA82-243C79FCBBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5DD5B6-D9BC-484D-99E8-84FF90FC31D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$132</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="187">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -1478,6 +1478,48 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1493,44 +1535,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1543,60 +1597,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1986,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2024,68 +2024,68 @@
       <c r="D3" s="109"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="204" t="s">
+      <c r="A4" s="170" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="204"/>
+      <c r="B4" s="170"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="204"/>
-      <c r="B5" s="204"/>
+      <c r="A5" s="170"/>
+      <c r="B5" s="170"/>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="204"/>
-      <c r="B6" s="204"/>
+      <c r="A6" s="170"/>
+      <c r="B6" s="170"/>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="204"/>
-      <c r="B7" s="204"/>
+      <c r="A7" s="170"/>
+      <c r="B7" s="170"/>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="181" t="s">
+      <c r="B9" s="167" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="181"/>
+      <c r="B10" s="167"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="181"/>
+      <c r="B11" s="167"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="182" t="s">
+      <c r="A14" s="171" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
+      <c r="A15" s="171"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
+      <c r="D15" s="171"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
+      <c r="A16" s="171"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
+      <c r="D16" s="171"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
+      <c r="A17" s="171"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="171"/>
+      <c r="D17" s="171"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2221,8 +2221,8 @@
         <v>1598022.7</v>
       </c>
       <c r="D32" s="81"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="180"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="166"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -2491,10 +2491,10 @@
       <c r="D58" s="57"/>
     </row>
     <row r="59" spans="1:7" s="33" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="175" t="s">
+      <c r="A59" s="168" t="s">
         <v>183</v>
       </c>
-      <c r="B59" s="176"/>
+      <c r="B59" s="169"/>
       <c r="C59" s="163">
         <v>10864.97</v>
       </c>
@@ -2503,10 +2503,10 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="175" t="s">
+      <c r="A60" s="168" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="176"/>
+      <c r="B60" s="169"/>
       <c r="C60" s="164">
         <v>4203</v>
       </c>
@@ -2623,412 +2623,412 @@
     </row>
     <row r="70" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="80" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B70" s="80"/>
-      <c r="C70" s="144"/>
-      <c r="D70" s="120"/>
+      <c r="C70" s="144">
+        <v>20460.259999999998</v>
+      </c>
+      <c r="D70" s="120" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="80" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B71" s="80"/>
       <c r="C71" s="144">
-        <v>20460.259999999998</v>
+        <v>864000.26</v>
       </c>
       <c r="D71" s="120" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="80" t="s">
-        <v>136</v>
-      </c>
-      <c r="B72" s="80"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="177" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="178"/>
       <c r="C72" s="144">
-        <v>864000.26</v>
+        <v>204149</v>
       </c>
       <c r="D72" s="120" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="177" t="s">
-        <v>158</v>
-      </c>
-      <c r="B73" s="178"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="175" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" s="176"/>
       <c r="C73" s="144">
-        <v>204149</v>
-      </c>
-      <c r="D73" s="120" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="173" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="174"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="122"/>
+    </row>
+    <row r="74" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="168" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="169"/>
       <c r="C74" s="144">
-        <v>0</v>
-      </c>
-      <c r="D74" s="122"/>
-    </row>
-    <row r="75" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="175" t="s">
-        <v>148</v>
-      </c>
-      <c r="B75" s="176"/>
-      <c r="C75" s="144">
         <v>35200</v>
       </c>
-      <c r="D75" s="122" t="s">
+      <c r="D74" s="122" t="s">
         <v>175</v>
       </c>
     </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="25"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="84">
+        <f>SUM(C69:C74)</f>
+        <v>1678489.63</v>
+      </c>
+    </row>
     <row r="76" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="25" t="s">
-        <v>3</v>
+      <c r="A76" s="24" t="s">
+        <v>36</v>
       </c>
       <c r="B76" s="25"/>
       <c r="C76" s="30"/>
-      <c r="D76" s="84">
-        <f>SUM(C69:C75)</f>
-        <v>1678489.63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B77" s="25"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="87"/>
+      <c r="D76" s="87"/>
+    </row>
+    <row r="77" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="146" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="145"/>
+      <c r="C77" s="144">
+        <v>51919.14</v>
+      </c>
+      <c r="D77" s="118" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="146" t="s">
-        <v>176</v>
-      </c>
-      <c r="B78" s="145"/>
+      <c r="A78" s="168" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" s="169"/>
       <c r="C78" s="144">
-        <v>51919.14</v>
-      </c>
-      <c r="D78" s="118" t="s">
-        <v>175</v>
+        <v>753830.53</v>
+      </c>
+      <c r="D78" s="120" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="175" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="176"/>
+      <c r="A79" s="150" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="142"/>
       <c r="C79" s="144">
-        <v>753830.53</v>
-      </c>
-      <c r="D79" s="120" t="s">
-        <v>164</v>
+        <v>10000</v>
+      </c>
+      <c r="D79" s="141" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="150" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B80" s="142"/>
       <c r="C80" s="144">
-        <v>10000</v>
-      </c>
-      <c r="D80" s="141" t="s">
-        <v>170</v>
+        <v>8760.52</v>
+      </c>
+      <c r="D80" s="122" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="150" t="s">
-        <v>178</v>
-      </c>
-      <c r="B81" s="142"/>
+      <c r="A81" s="168" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="169"/>
       <c r="C81" s="144">
-        <v>8760.52</v>
+        <v>34000</v>
       </c>
       <c r="D81" s="122" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E81" s="39"/>
+      <c r="F81" s="39"/>
+    </row>
+    <row r="82" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="175" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B82" s="176"/>
-      <c r="C82" s="144">
-        <v>34000</v>
-      </c>
-      <c r="D82" s="122" t="s">
-        <v>177</v>
-      </c>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-    </row>
-    <row r="83" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="173" t="s">
-        <v>159</v>
-      </c>
-      <c r="B83" s="174"/>
-      <c r="C83" s="138">
-        <v>0</v>
-      </c>
-      <c r="D83" s="122"/>
+      <c r="C82" s="138">
+        <v>0</v>
+      </c>
+      <c r="D82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="90">
+        <f>SUM(C77:C82)</f>
+        <v>858510.19000000006</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="90">
-        <f>SUM(C78:C83)</f>
-        <v>858510.19000000006</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="24" t="s">
+      <c r="A84" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B85" s="147"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="87"/>
+      <c r="B84" s="147"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="87"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="B85" s="80"/>
+      <c r="C85" s="144">
+        <v>65343</v>
+      </c>
+      <c r="D85" s="91"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="80" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B86" s="80"/>
       <c r="C86" s="144">
-        <v>65343</v>
-      </c>
-      <c r="D86" s="91"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="80" t="s">
-        <v>125</v>
-      </c>
-      <c r="B87" s="80"/>
-      <c r="C87" s="144">
         <f>65.19+149249.14</f>
         <v>149314.33000000002</v>
       </c>
-      <c r="D87" s="89"/>
+      <c r="D86" s="89"/>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B87" s="44"/>
+      <c r="C87" s="92"/>
+      <c r="D87" s="84">
+        <f>SUM(C85:C86)</f>
+        <v>214657.33000000002</v>
+      </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="92"/>
-      <c r="D88" s="84">
-        <f>SUM(C86:C87)</f>
-        <v>214657.33000000002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="80"/>
-      <c r="D89" s="93"/>
-    </row>
-    <row r="90" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="170" t="s">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="93"/>
+    </row>
+    <row r="89" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="172" t="s">
         <v>141</v>
       </c>
-      <c r="B90" s="171"/>
-      <c r="C90" s="172"/>
-      <c r="D90" s="94">
+      <c r="B89" s="173"/>
+      <c r="C89" s="174"/>
+      <c r="D89" s="94">
         <f>10000000-8703429.85</f>
         <v>1296570.1500000004</v>
       </c>
     </row>
+    <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="C90" s="95"/>
+      <c r="D90" s="96"/>
+      <c r="E90" s="39"/>
+    </row>
     <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="C91" s="95"/>
-      <c r="D91" s="96"/>
+      <c r="A91" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" s="10"/>
+      <c r="C91" s="97"/>
+      <c r="D91" s="98">
+        <f>(SUM(D33:D89))</f>
+        <v>12704700.589999998</v>
+      </c>
       <c r="E91" s="39"/>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="97"/>
-      <c r="D92" s="98">
-        <f>(SUM(D33:D90))</f>
-        <v>12704700.589999998</v>
-      </c>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F91" s="39"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C92" s="95"/>
+      <c r="D92" s="95"/>
+      <c r="F92" s="117"/>
+    </row>
+    <row r="93" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C93" s="95"/>
       <c r="D93" s="95"/>
-      <c r="F93" s="117"/>
-    </row>
-    <row r="94" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="95"/>
-      <c r="D94" s="95"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" s="12"/>
+      <c r="C94" s="99"/>
+      <c r="D94" s="100"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" s="12"/>
-      <c r="C95" s="99"/>
-      <c r="D95" s="100"/>
+      <c r="A95" s="182"/>
+      <c r="B95" s="183"/>
+      <c r="C95" s="88"/>
+      <c r="D95" s="86"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="168"/>
-      <c r="B96" s="169"/>
+      <c r="A96" s="182"/>
+      <c r="B96" s="183"/>
       <c r="C96" s="88"/>
       <c r="D96" s="86"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="168"/>
-      <c r="B97" s="169"/>
+      <c r="A97" s="103"/>
+      <c r="B97" s="104"/>
       <c r="C97" s="88"/>
       <c r="D97" s="86"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="103"/>
-      <c r="B98" s="104"/>
-      <c r="C98" s="88"/>
-      <c r="D98" s="86"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="42"/>
-      <c r="B99" s="41"/>
-      <c r="C99" s="49"/>
-      <c r="D99" s="49">
-        <f>SUM(C96:C98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="20" t="s">
+      <c r="A98" s="42"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="49">
+        <f>SUM(C95:C97)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B102" s="20"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="125">
+      <c r="B101" s="20"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="125">
         <v>2000000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="104" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B104" s="10"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="58">
-        <f>D99+D102</f>
+      <c r="B103" s="10"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="58">
+        <f>D98+D101</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B105" s="79">
+        <f>D91</f>
+        <v>12704700.589999998</v>
+      </c>
+      <c r="C105" s="39"/>
+    </row>
     <row r="106" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B106" s="79">
-        <f>D92</f>
-        <v>12704700.589999998</v>
-      </c>
-      <c r="C106" s="39"/>
+        <f>D91-D89</f>
+        <v>11408130.439999998</v>
+      </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="78" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B107" s="79">
-        <f>D92-D90</f>
-        <v>11408130.439999998</v>
+        <f>D103-D101</f>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="78" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="B108" s="79">
-        <f>D104-D102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="B109" s="79">
-        <f>D104</f>
+        <f>D103</f>
         <v>2000000</v>
       </c>
     </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="181" t="s">
+        <v>160</v>
+      </c>
+      <c r="B111" s="181"/>
+      <c r="C111" s="181"/>
+      <c r="D111" s="181"/>
+    </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="167" t="s">
-        <v>160</v>
-      </c>
-      <c r="B112" s="167"/>
-      <c r="C112" s="167"/>
-      <c r="D112" s="167"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="167"/>
-      <c r="B113" s="167"/>
-      <c r="C113" s="167"/>
-      <c r="D113" s="167"/>
-    </row>
-    <row r="114" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="167"/>
-      <c r="B114" s="167"/>
-      <c r="C114" s="167"/>
-      <c r="D114" s="167"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="15" t="s">
+      <c r="A112" s="181"/>
+      <c r="B112" s="181"/>
+      <c r="C112" s="181"/>
+      <c r="D112" s="181"/>
+    </row>
+    <row r="113" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="181"/>
+      <c r="B113" s="181"/>
+      <c r="C113" s="181"/>
+      <c r="D113" s="181"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B116" s="35"/>
-    </row>
-    <row r="117" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="23" t="s">
+      <c r="B115" s="35"/>
+    </row>
+    <row r="116" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B117" s="105">
+      <c r="B116" s="105">
         <v>7139335.7599999998</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="36">
+        <f>PRORRATEO!H35</f>
+        <v>12003298.140000001</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B118" s="36">
-        <f>PRORRATEO!H35</f>
-        <v>12003298.140000001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B119" s="89">
-        <f>B132</f>
+      <c r="B118" s="89">
+        <f>B131</f>
         <v>500000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B119" s="119">
+        <v>-10167</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B120" s="119">
-        <v>-10167</v>
+        <v>-240000</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3036,130 +3036,122 @@
         <v>179</v>
       </c>
       <c r="B121" s="119">
-        <v>-240000</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="17" t="s">
-        <v>179</v>
+        <v>-260000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="34" t="s">
+        <v>44</v>
       </c>
       <c r="B122" s="119">
-        <v>-260000</v>
+        <f>-B106</f>
+        <v>-11408130.439999998</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="B123" s="119">
-        <f>-B107</f>
-        <v>-11408130.439999998</v>
+      <c r="A123" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B123" s="89">
+        <f>-(B107)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B124" s="89">
-        <f>-(B108)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="22" t="s">
+      <c r="A124" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B125" s="105">
-        <f>SUM(B117:B124)</f>
+      <c r="B124" s="105">
+        <f>SUM(B116:B123)</f>
         <v>7724336.4600000009</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="37"/>
-      <c r="C126" s="39"/>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="166" t="s">
+    <row r="125" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="37"/>
+      <c r="C125" s="39"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="180" t="s">
         <v>78</v>
       </c>
-      <c r="B128" s="166"/>
-    </row>
-    <row r="129" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="166"/>
-      <c r="B129" s="166"/>
+      <c r="B127" s="180"/>
+    </row>
+    <row r="128" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="180"/>
+      <c r="B128" s="180"/>
+    </row>
+    <row r="129" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="101" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="29">
+        <v>240000</v>
+      </c>
     </row>
     <row r="130" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="101" t="s">
         <v>153</v>
       </c>
       <c r="B130" s="29">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="101" t="s">
-        <v>153</v>
-      </c>
-      <c r="B131" s="29">
         <v>260000</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="40" t="s">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B132" s="102">
-        <f>SUM(B130:B131)</f>
+      <c r="B131" s="102">
+        <f>SUM(B129:B130)</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L133" s="8"/>
-    </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="165"/>
-      <c r="B134" s="165"/>
-      <c r="C134" s="165"/>
-      <c r="D134" s="165"/>
+    <row r="132" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L132" s="8"/>
+    </row>
+    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="179"/>
+      <c r="B133" s="179"/>
+      <c r="C133" s="179"/>
+      <c r="D133" s="179"/>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" s="179"/>
+      <c r="B134" s="179"/>
+      <c r="C134" s="179"/>
+      <c r="D134" s="179"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="165"/>
-      <c r="B135" s="165"/>
-      <c r="C135" s="165"/>
-      <c r="D135" s="165"/>
+      <c r="A135" s="179"/>
+      <c r="B135" s="179"/>
+      <c r="C135" s="179"/>
+      <c r="D135" s="179"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="165"/>
-      <c r="B136" s="165"/>
-      <c r="C136" s="165"/>
-      <c r="D136" s="165"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="165"/>
-      <c r="B137" s="165"/>
-      <c r="C137" s="165"/>
-      <c r="D137" s="165"/>
+      <c r="A136" s="179"/>
+      <c r="B136" s="179"/>
+      <c r="C136" s="179"/>
+      <c r="D136" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A133:D136"/>
+    <mergeCell ref="A127:B128"/>
+    <mergeCell ref="A111:D113"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A134:D137"/>
-    <mergeCell ref="A128:B129"/>
-    <mergeCell ref="A112:D114"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3195,7 +3187,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="189" t="str">
+      <c r="B1" s="184" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco Santander
 Tipo de cuenta: Cuenta corriente en pesos
@@ -3203,15 +3195,15 @@
 CBU: 0720039720000002345040
 Alias: ALFA.CETRO.AMOROSAS</v>
       </c>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
-      <c r="J1" s="189"/>
-      <c r="K1" s="189"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -3220,16 +3212,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="184"/>
+      <c r="K2" s="184"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3243,16 +3235,16 @@
     </row>
     <row r="3" spans="1:19" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
+      <c r="B3" s="185"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3264,76 +3256,76 @@
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="183" t="s">
+      <c r="A4" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="185" t="s">
+      <c r="B4" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="187" t="s">
+      <c r="C4" s="188" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="187" t="s">
+      <c r="D4" s="188" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="187" t="s">
+      <c r="E4" s="188" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="187" t="s">
+      <c r="F4" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="187" t="s">
+      <c r="G4" s="188" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="187" t="s">
+      <c r="H4" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="187" t="s">
+      <c r="I4" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="196" t="s">
+      <c r="J4" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="194" t="s">
+      <c r="K4" s="190" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="194" t="s">
+      <c r="L4" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="194" t="s">
+      <c r="M4" s="190" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="199" t="s">
+      <c r="N4" s="196" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="191" t="s">
+      <c r="P4" s="186" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="39"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="184"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="193"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="197"/>
-      <c r="K5" s="195"/>
-      <c r="L5" s="198"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="200"/>
+      <c r="A5" s="202"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
+      <c r="I5" s="189"/>
+      <c r="J5" s="194"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="195"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="197"/>
       <c r="O5" s="51" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 13/03</v>
       </c>
-      <c r="P5" s="192"/>
+      <c r="P5" s="187"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3509,11 +3501,11 @@
     </row>
     <row r="9" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="201" t="s">
+      <c r="B9" s="198" t="s">
         <v>185</v>
       </c>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="200"/>
       <c r="E9" s="128"/>
       <c r="F9" s="129"/>
       <c r="G9" s="130">
@@ -5015,93 +5007,98 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="165" t="s">
+      <c r="D38" s="179" t="s">
         <v>143</v>
       </c>
-      <c r="E38" s="165"/>
-      <c r="F38" s="165"/>
-      <c r="G38" s="165"/>
-      <c r="H38" s="165"/>
-      <c r="I38" s="165"/>
-      <c r="J38" s="165"/>
-      <c r="K38" s="165"/>
-      <c r="L38" s="165"/>
-      <c r="M38" s="165"/>
-      <c r="N38" s="165"/>
-      <c r="O38" s="165"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
+      <c r="J38" s="179"/>
+      <c r="K38" s="179"/>
+      <c r="L38" s="179"/>
+      <c r="M38" s="179"/>
+      <c r="N38" s="179"/>
+      <c r="O38" s="179"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="165"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="165"/>
-      <c r="G39" s="165"/>
-      <c r="H39" s="165"/>
-      <c r="I39" s="165"/>
-      <c r="J39" s="165"/>
-      <c r="K39" s="165"/>
-      <c r="L39" s="165"/>
-      <c r="M39" s="165"/>
-      <c r="N39" s="165"/>
-      <c r="O39" s="165"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
+      <c r="F39" s="179"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+      <c r="I39" s="179"/>
+      <c r="J39" s="179"/>
+      <c r="K39" s="179"/>
+      <c r="L39" s="179"/>
+      <c r="M39" s="179"/>
+      <c r="N39" s="179"/>
+      <c r="O39" s="179"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="165"/>
-      <c r="E40" s="165"/>
-      <c r="F40" s="165"/>
-      <c r="G40" s="165"/>
-      <c r="H40" s="165"/>
-      <c r="I40" s="165"/>
-      <c r="J40" s="165"/>
-      <c r="K40" s="165"/>
-      <c r="L40" s="165"/>
-      <c r="M40" s="165"/>
-      <c r="N40" s="165"/>
-      <c r="O40" s="165"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="179"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
+      <c r="J40" s="179"/>
+      <c r="K40" s="179"/>
+      <c r="L40" s="179"/>
+      <c r="M40" s="179"/>
+      <c r="N40" s="179"/>
+      <c r="O40" s="179"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="165"/>
-      <c r="E41" s="165"/>
-      <c r="F41" s="165"/>
-      <c r="G41" s="165"/>
-      <c r="H41" s="165"/>
-      <c r="I41" s="165"/>
-      <c r="J41" s="165"/>
-      <c r="K41" s="165"/>
-      <c r="L41" s="165"/>
-      <c r="M41" s="165"/>
-      <c r="N41" s="165"/>
-      <c r="O41" s="165"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="179"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
+      <c r="J41" s="179"/>
+      <c r="K41" s="179"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="179"/>
+      <c r="N41" s="179"/>
+      <c r="O41" s="179"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="165"/>
-      <c r="E42" s="165"/>
-      <c r="F42" s="165"/>
-      <c r="G42" s="165"/>
-      <c r="H42" s="165"/>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="165"/>
-      <c r="L42" s="165"/>
-      <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
-      <c r="O42" s="165"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
+      <c r="L42" s="179"/>
+      <c r="M42" s="179"/>
+      <c r="N42" s="179"/>
+      <c r="O42" s="179"/>
     </row>
     <row r="43" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="165"/>
-      <c r="E43" s="165"/>
-      <c r="F43" s="165"/>
-      <c r="G43" s="165"/>
-      <c r="H43" s="165"/>
-      <c r="I43" s="165"/>
-      <c r="J43" s="165"/>
-      <c r="K43" s="165"/>
-      <c r="L43" s="165"/>
-      <c r="M43" s="165"/>
-      <c r="N43" s="165"/>
-      <c r="O43" s="165"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="179"/>
+      <c r="F43" s="179"/>
+      <c r="G43" s="179"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
+      <c r="J43" s="179"/>
+      <c r="K43" s="179"/>
+      <c r="L43" s="179"/>
+      <c r="M43" s="179"/>
+      <c r="N43" s="179"/>
+      <c r="O43" s="179"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D38:O43"/>
@@ -5115,11 +5112,6 @@
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
